--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.38</v>
+        <v>4.03</v>
       </c>
       <c r="F14" t="n">
-        <v>10.26</v>
+        <v>9.99</v>
       </c>
       <c r="G14" t="n">
-        <v>313.7</v>
+        <v>324.7</v>
       </c>
       <c r="H14" t="n">
-        <v>32.2</v>
+        <v>25.8</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>-95.31</v>
+        <v>4.94</v>
       </c>
       <c r="K14" t="n">
-        <v>-17.72</v>
+        <v>-117.21</v>
       </c>
       <c r="L14" t="n">
-        <v>96.94</v>
+        <v>117.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:31:24</t>
+          <t>05:31:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.38</v>
+        <v>3.17</v>
       </c>
       <c r="F15" t="n">
-        <v>8.67</v>
+        <v>9.24</v>
       </c>
       <c r="G15" t="n">
-        <v>339.4</v>
+        <v>328.2</v>
       </c>
       <c r="H15" t="n">
-        <v>28.5</v>
+        <v>27.2</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>-96.95999999999999</v>
+        <v>45.09</v>
       </c>
       <c r="K15" t="n">
-        <v>-85.86</v>
+        <v>11.68</v>
       </c>
       <c r="L15" t="n">
-        <v>129.51</v>
+        <v>46.58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:33:12</t>
+          <t>05:33:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>8.81</v>
+        <v>9.98</v>
       </c>
       <c r="G16" t="n">
-        <v>318.3</v>
+        <v>321.7</v>
       </c>
       <c r="H16" t="n">
-        <v>29.4</v>
+        <v>25.2</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>3.82</v>
+        <v>-137.17</v>
       </c>
       <c r="K16" t="n">
-        <v>52.85</v>
+        <v>-139.87</v>
       </c>
       <c r="L16" t="n">
-        <v>52.99</v>
+        <v>195.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:38:10</t>
+          <t>05:38:21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="F17" t="n">
-        <v>8.720000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="G17" t="n">
-        <v>327.4</v>
+        <v>325</v>
       </c>
       <c r="H17" t="n">
-        <v>26.7</v>
+        <v>28.8</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-82.61</v>
+        <v>-46.8</v>
       </c>
       <c r="K17" t="n">
-        <v>72.33</v>
+        <v>1.25</v>
       </c>
       <c r="L17" t="n">
-        <v>109.8</v>
+        <v>46.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:40:04</t>
+          <t>05:40:05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="F18" t="n">
-        <v>8.720000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G18" t="n">
-        <v>322.2</v>
+        <v>329.7</v>
       </c>
       <c r="H18" t="n">
-        <v>25.1</v>
+        <v>21.9</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>13.06</v>
+        <v>-182.72</v>
       </c>
       <c r="K18" t="n">
-        <v>-68.09</v>
+        <v>-143.49</v>
       </c>
       <c r="L18" t="n">
-        <v>69.33</v>
+        <v>232.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:41:09</t>
+          <t>05:42:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.43</v>
+        <v>3.19</v>
       </c>
       <c r="F19" t="n">
-        <v>9.789999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="G19" t="n">
-        <v>324.6</v>
+        <v>330.3</v>
       </c>
       <c r="H19" t="n">
-        <v>26.8</v>
+        <v>19.1</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>191.18</v>
+        <v>425.72</v>
       </c>
       <c r="K19" t="n">
-        <v>162.02</v>
+        <v>-298.94</v>
       </c>
       <c r="L19" t="n">
-        <v>250.6</v>
+        <v>520.1900000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:45:14</t>
+          <t>05:47:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="F20" t="n">
-        <v>9.970000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>322.2</v>
+        <v>327</v>
       </c>
       <c r="H20" t="n">
-        <v>28.4</v>
+        <v>23.9</v>
       </c>
       <c r="I20" t="n">
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-190.79</v>
+        <v>-202.75</v>
       </c>
       <c r="K20" t="n">
-        <v>82.86</v>
+        <v>179.83</v>
       </c>
       <c r="L20" t="n">
-        <v>208</v>
+        <v>271.01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:47:06</t>
+          <t>05:48:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="F21" t="n">
-        <v>8.44</v>
+        <v>9.27</v>
       </c>
       <c r="G21" t="n">
-        <v>332.8</v>
+        <v>336.4</v>
       </c>
       <c r="H21" t="n">
-        <v>26.9</v>
+        <v>20.8</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>77.61</v>
+        <v>191.57</v>
       </c>
       <c r="K21" t="n">
-        <v>104.26</v>
+        <v>-118.53</v>
       </c>
       <c r="L21" t="n">
-        <v>129.97</v>
+        <v>225.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:48:17</t>
+          <t>05:50:06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.09</v>
+        <v>2.99</v>
       </c>
       <c r="F22" t="n">
-        <v>9.51</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>337.7</v>
+        <v>327.1</v>
       </c>
       <c r="H22" t="n">
-        <v>28.5</v>
+        <v>32.5</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>436.59</v>
+        <v>-17.14</v>
       </c>
       <c r="K22" t="n">
-        <v>-108.73</v>
+        <v>258.64</v>
       </c>
       <c r="L22" t="n">
-        <v>449.92</v>
+        <v>259.21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:53:42</t>
+          <t>05:53:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.47</v>
+        <v>3.03</v>
       </c>
       <c r="F23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>328.6</v>
+        <v>312.4</v>
       </c>
       <c r="H23" t="n">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-578.9</v>
+        <v>-76.95999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-9.58</v>
+        <v>207.52</v>
       </c>
       <c r="L23" t="n">
-        <v>578.98</v>
+        <v>221.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:56:00</t>
+          <t>05:54:41</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.16</v>
+        <v>2.29</v>
       </c>
       <c r="F24" t="n">
-        <v>9.32</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>320.7</v>
+        <v>319.7</v>
       </c>
       <c r="H24" t="n">
-        <v>30.2</v>
+        <v>25.8</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-125.78</v>
+        <v>-432.53</v>
       </c>
       <c r="K24" t="n">
-        <v>-246.05</v>
+        <v>195.91</v>
       </c>
       <c r="L24" t="n">
-        <v>276.34</v>
+        <v>474.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:58:23</t>
+          <t>05:56:23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="F25" t="n">
-        <v>9.65</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>330.6</v>
+        <v>325.4</v>
       </c>
       <c r="H25" t="n">
-        <v>25.9</v>
+        <v>20.5</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>230.11</v>
+        <v>-383.84</v>
       </c>
       <c r="K25" t="n">
-        <v>-20.4</v>
+        <v>84.73</v>
       </c>
       <c r="L25" t="n">
-        <v>231.01</v>
+        <v>393.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:04:33</t>
+          <t>06:01:02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="F26" t="n">
-        <v>9.43</v>
+        <v>9.52</v>
       </c>
       <c r="G26" t="n">
-        <v>319.2</v>
+        <v>299.7</v>
       </c>
       <c r="H26" t="n">
-        <v>29.7</v>
+        <v>28.8</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-84.87</v>
+        <v>-533.6</v>
       </c>
       <c r="K26" t="n">
-        <v>135.36</v>
+        <v>-39.31</v>
       </c>
       <c r="L26" t="n">
-        <v>159.76</v>
+        <v>535.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:06:41</t>
+          <t>06:02:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="F27" t="n">
-        <v>9.25</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>322.1</v>
+        <v>324</v>
       </c>
       <c r="H27" t="n">
-        <v>30.5</v>
+        <v>29.5</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>216.69</v>
+        <v>327.99</v>
       </c>
       <c r="K27" t="n">
-        <v>-357.2</v>
+        <v>-486.26</v>
       </c>
       <c r="L27" t="n">
-        <v>417.79</v>
+        <v>586.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:08:43</t>
+          <t>06:04:46</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="F28" t="n">
-        <v>9.25</v>
+        <v>9.24</v>
       </c>
       <c r="G28" t="n">
-        <v>311.6</v>
+        <v>309.9</v>
       </c>
       <c r="H28" t="n">
-        <v>27.1</v>
+        <v>26</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-507.99</v>
+        <v>-535.64</v>
       </c>
       <c r="K28" t="n">
-        <v>204.6</v>
+        <v>221.48</v>
       </c>
       <c r="L28" t="n">
-        <v>547.65</v>
+        <v>579.62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:15:01</t>
+          <t>06:12:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="F29" t="n">
-        <v>9.140000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>327.7</v>
+        <v>326.4</v>
       </c>
       <c r="H29" t="n">
-        <v>26.2</v>
+        <v>17.6</v>
       </c>
       <c r="I29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.47</v>
+        <v>48.47</v>
       </c>
       <c r="K29" t="n">
-        <v>8.58</v>
+        <v>-36.32</v>
       </c>
       <c r="L29" t="n">
-        <v>8.699999999999999</v>
+        <v>60.56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:16:40</t>
+          <t>06:13:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="F30" t="n">
-        <v>8.99</v>
+        <v>9.6</v>
       </c>
       <c r="G30" t="n">
-        <v>343.7</v>
+        <v>317.1</v>
       </c>
       <c r="H30" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-87.73</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>62.49</v>
+        <v>-144.29</v>
       </c>
       <c r="L30" t="n">
-        <v>107.71</v>
+        <v>144.52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:18:18</t>
+          <t>06:15:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.46</v>
+        <v>2.7</v>
       </c>
       <c r="F31" t="n">
-        <v>9.69</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>328.1</v>
+        <v>319.3</v>
       </c>
       <c r="H31" t="n">
-        <v>32.8</v>
+        <v>29.9</v>
       </c>
       <c r="I31" t="n">
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>82.37</v>
+        <v>-83.05</v>
       </c>
       <c r="K31" t="n">
-        <v>11.66</v>
+        <v>-42.99</v>
       </c>
       <c r="L31" t="n">
-        <v>83.19</v>
+        <v>93.52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:23:48</t>
+          <t>06:19:29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.66</v>
+        <v>2.75</v>
       </c>
       <c r="F32" t="n">
-        <v>9.35</v>
+        <v>9.09</v>
       </c>
       <c r="G32" t="n">
-        <v>325.6</v>
+        <v>328.8</v>
       </c>
       <c r="H32" t="n">
-        <v>27.2</v>
+        <v>26</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-42.54</v>
+        <v>-33.1</v>
       </c>
       <c r="K32" t="n">
-        <v>35.4</v>
+        <v>148.81</v>
       </c>
       <c r="L32" t="n">
-        <v>55.34</v>
+        <v>152.44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:26:15</t>
+          <t>06:20:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.14</v>
+        <v>2.96</v>
       </c>
       <c r="F33" t="n">
-        <v>10.02</v>
+        <v>9.44</v>
       </c>
       <c r="G33" t="n">
-        <v>312.7</v>
+        <v>336.7</v>
       </c>
       <c r="H33" t="n">
-        <v>27.1</v>
+        <v>28.4</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-54.46</v>
+        <v>88.67</v>
       </c>
       <c r="K33" t="n">
-        <v>168.35</v>
+        <v>-140.83</v>
       </c>
       <c r="L33" t="n">
-        <v>176.94</v>
+        <v>166.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:28:24</t>
+          <t>06:21:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.55</v>
+        <v>2.83</v>
       </c>
       <c r="F34" t="n">
-        <v>9.33</v>
+        <v>9.42</v>
       </c>
       <c r="G34" t="n">
-        <v>328.6</v>
+        <v>330</v>
       </c>
       <c r="H34" t="n">
-        <v>26</v>
+        <v>21.1</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>32.57</v>
+        <v>-321</v>
       </c>
       <c r="K34" t="n">
-        <v>22.47</v>
+        <v>256.5</v>
       </c>
       <c r="L34" t="n">
-        <v>39.57</v>
+        <v>410.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:33:17</t>
+          <t>06:26:11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.33</v>
+        <v>2.87</v>
       </c>
       <c r="F35" t="n">
-        <v>9.09</v>
+        <v>9.44</v>
       </c>
       <c r="G35" t="n">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="H35" t="n">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-127.43</v>
+        <v>-201.49</v>
       </c>
       <c r="K35" t="n">
-        <v>237</v>
+        <v>-237.3</v>
       </c>
       <c r="L35" t="n">
-        <v>269.09</v>
+        <v>311.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:34:50</t>
+          <t>06:28:31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.99</v>
+        <v>3.37</v>
       </c>
       <c r="F36" t="n">
-        <v>9.640000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>330.3</v>
+        <v>318.1</v>
       </c>
       <c r="H36" t="n">
-        <v>22.4</v>
+        <v>33.6</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-94.68000000000001</v>
+        <v>-91.45999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-153.39</v>
+        <v>-107.07</v>
       </c>
       <c r="L36" t="n">
-        <v>180.26</v>
+        <v>140.81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:35:21</t>
+          <t>06:30:54</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="F37" t="n">
-        <v>8.85</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>321.2</v>
+        <v>331.6</v>
       </c>
       <c r="H37" t="n">
-        <v>26.6</v>
+        <v>23</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-289.2</v>
+        <v>-168.66</v>
       </c>
       <c r="K37" t="n">
-        <v>-309.67</v>
+        <v>-110.34</v>
       </c>
       <c r="L37" t="n">
-        <v>423.71</v>
+        <v>201.55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:39:42</t>
+          <t>06:35:06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.06</v>
+        <v>3.68</v>
       </c>
       <c r="F38" t="n">
-        <v>9.27</v>
+        <v>10.28</v>
       </c>
       <c r="G38" t="n">
-        <v>328.8</v>
+        <v>321.5</v>
       </c>
       <c r="H38" t="n">
-        <v>22.9</v>
+        <v>27.1</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J38" t="n">
-        <v>27.24</v>
+        <v>-228.31</v>
       </c>
       <c r="K38" t="n">
-        <v>-343.01</v>
+        <v>-47.4</v>
       </c>
       <c r="L38" t="n">
-        <v>344.09</v>
+        <v>233.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:40:25</t>
+          <t>06:37:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="F39" t="n">
-        <v>8.85</v>
+        <v>8.77</v>
       </c>
       <c r="G39" t="n">
-        <v>332.1</v>
+        <v>335.2</v>
       </c>
       <c r="H39" t="n">
-        <v>25</v>
+        <v>28.2</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>464.41</v>
+        <v>-151.02</v>
       </c>
       <c r="K39" t="n">
-        <v>28.43</v>
+        <v>-94.64</v>
       </c>
       <c r="L39" t="n">
-        <v>465.28</v>
+        <v>178.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:41:47</t>
+          <t>06:39:20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="F40" t="n">
-        <v>9.470000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="G40" t="n">
-        <v>316.1</v>
+        <v>321.5</v>
       </c>
       <c r="H40" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>-411.92</v>
+        <v>209.29</v>
       </c>
       <c r="K40" t="n">
-        <v>136.08</v>
+        <v>180.66</v>
       </c>
       <c r="L40" t="n">
-        <v>433.81</v>
+        <v>276.48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:44:50</t>
+          <t>06:44:03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.46</v>
+        <v>3.57</v>
       </c>
       <c r="F41" t="n">
-        <v>9.26</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>315.9</v>
+        <v>330.7</v>
       </c>
       <c r="H41" t="n">
-        <v>24.5</v>
+        <v>27.1</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>-275.88</v>
+        <v>-41.69</v>
       </c>
       <c r="K41" t="n">
-        <v>552.99</v>
+        <v>-354.35</v>
       </c>
       <c r="L41" t="n">
-        <v>617.98</v>
+        <v>356.79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:47:04</t>
+          <t>06:46:13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.89</v>
+        <v>2.58</v>
       </c>
       <c r="F42" t="n">
-        <v>9.130000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="G42" t="n">
-        <v>332.7</v>
+        <v>337</v>
       </c>
       <c r="H42" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>197.76</v>
+        <v>-31.7</v>
       </c>
       <c r="K42" t="n">
-        <v>572.39</v>
+        <v>366.47</v>
       </c>
       <c r="L42" t="n">
-        <v>605.59</v>
+        <v>367.83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:49:13</t>
+          <t>06:47:20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.35</v>
+        <v>3.06</v>
       </c>
       <c r="F43" t="n">
-        <v>8.890000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>327.3</v>
+        <v>333.9</v>
       </c>
       <c r="H43" t="n">
-        <v>20.6</v>
+        <v>18.2</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-236.03</v>
+        <v>-413.98</v>
       </c>
       <c r="K43" t="n">
-        <v>425.5</v>
+        <v>-22.95</v>
       </c>
       <c r="L43" t="n">
-        <v>486.58</v>
+        <v>414.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:58:57</t>
+          <t>06:56:28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="F44" t="n">
-        <v>8.68</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>323.9</v>
+        <v>320.8</v>
       </c>
       <c r="H44" t="n">
-        <v>31.4</v>
+        <v>19.8</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-49.55</v>
+        <v>42.77</v>
       </c>
       <c r="K44" t="n">
-        <v>89.26000000000001</v>
+        <v>-97.78</v>
       </c>
       <c r="L44" t="n">
-        <v>102.1</v>
+        <v>106.72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:00:13</t>
+          <t>06:57:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="F45" t="n">
-        <v>9.41</v>
+        <v>8.23</v>
       </c>
       <c r="G45" t="n">
-        <v>316.7</v>
+        <v>329</v>
       </c>
       <c r="H45" t="n">
-        <v>28</v>
+        <v>28.6</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>5.92</v>
+        <v>241.03</v>
       </c>
       <c r="K45" t="n">
-        <v>17.27</v>
+        <v>156.75</v>
       </c>
       <c r="L45" t="n">
-        <v>18.26</v>
+        <v>287.52</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:02:14</t>
+          <t>06:59:56</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="F46" t="n">
-        <v>9.119999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G46" t="n">
-        <v>323.2</v>
+        <v>337.3</v>
       </c>
       <c r="H46" t="n">
-        <v>25.9</v>
+        <v>21.6</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>-33.54</v>
+        <v>34.77</v>
       </c>
       <c r="K46" t="n">
-        <v>-80.34999999999999</v>
+        <v>-78.34</v>
       </c>
       <c r="L46" t="n">
-        <v>87.06999999999999</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:05:56</t>
+          <t>07:04:31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.74</v>
+        <v>3.26</v>
       </c>
       <c r="F47" t="n">
-        <v>8.81</v>
+        <v>8.52</v>
       </c>
       <c r="G47" t="n">
-        <v>323.5</v>
+        <v>330.4</v>
       </c>
       <c r="H47" t="n">
-        <v>24.5</v>
+        <v>26.5</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>-350.65</v>
+        <v>124.81</v>
       </c>
       <c r="K47" t="n">
-        <v>-153.2</v>
+        <v>-178.61</v>
       </c>
       <c r="L47" t="n">
-        <v>382.66</v>
+        <v>217.89</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:07:18</t>
+          <t>07:05:52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="F48" t="n">
-        <v>9.57</v>
+        <v>9.23</v>
       </c>
       <c r="G48" t="n">
-        <v>334.7</v>
+        <v>321.8</v>
       </c>
       <c r="H48" t="n">
-        <v>31.7</v>
+        <v>33.3</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>1.45</v>
+        <v>-177.51</v>
       </c>
       <c r="K48" t="n">
-        <v>323.65</v>
+        <v>-24.79</v>
       </c>
       <c r="L48" t="n">
-        <v>323.66</v>
+        <v>179.23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:08:21</t>
+          <t>07:07:18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="F49" t="n">
-        <v>8.890000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="G49" t="n">
-        <v>337.2</v>
+        <v>317.6</v>
       </c>
       <c r="H49" t="n">
-        <v>31.7</v>
+        <v>28.6</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>68.15000000000001</v>
+        <v>-123.94</v>
       </c>
       <c r="K49" t="n">
-        <v>-28.35</v>
+        <v>25.09</v>
       </c>
       <c r="L49" t="n">
-        <v>73.81</v>
+        <v>126.46</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:14:29</t>
+          <t>07:11:22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="F50" t="n">
-        <v>9.16</v>
+        <v>8.99</v>
       </c>
       <c r="G50" t="n">
-        <v>333.9</v>
+        <v>334.9</v>
       </c>
       <c r="H50" t="n">
-        <v>19</v>
+        <v>19.9</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-16.55</v>
+        <v>-141.44</v>
       </c>
       <c r="K50" t="n">
-        <v>-451.98</v>
+        <v>-119.57</v>
       </c>
       <c r="L50" t="n">
-        <v>452.28</v>
+        <v>185.21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:15:21</t>
+          <t>07:13:37</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="F51" t="n">
-        <v>8.76</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>320.7</v>
+        <v>321.3</v>
       </c>
       <c r="H51" t="n">
-        <v>27</v>
+        <v>29.4</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>-97.15000000000001</v>
+        <v>181.98</v>
       </c>
       <c r="K51" t="n">
-        <v>240.03</v>
+        <v>-133.8</v>
       </c>
       <c r="L51" t="n">
-        <v>258.95</v>
+        <v>225.87</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:17:01</t>
+          <t>07:15:10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.28</v>
+        <v>3.73</v>
       </c>
       <c r="F52" t="n">
-        <v>9.84</v>
+        <v>9.31</v>
       </c>
       <c r="G52" t="n">
-        <v>327.3</v>
+        <v>329.7</v>
       </c>
       <c r="H52" t="n">
-        <v>24.6</v>
+        <v>26.5</v>
       </c>
       <c r="I52" t="n">
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-229.39</v>
+        <v>-18.82</v>
       </c>
       <c r="K52" t="n">
-        <v>-143.38</v>
+        <v>239.88</v>
       </c>
       <c r="L52" t="n">
-        <v>270.52</v>
+        <v>240.61</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:21:54</t>
+          <t>07:19:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="F53" t="n">
-        <v>9.199999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="G53" t="n">
-        <v>312.8</v>
+        <v>322.8</v>
       </c>
       <c r="H53" t="n">
-        <v>18.9</v>
+        <v>29.9</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-149.22</v>
+        <v>-107.42</v>
       </c>
       <c r="K53" t="n">
-        <v>343.95</v>
+        <v>-27.95</v>
       </c>
       <c r="L53" t="n">
-        <v>374.92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:23:34</t>
+          <t>07:20:38</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.26</v>
+        <v>2.91</v>
       </c>
       <c r="F54" t="n">
-        <v>9.26</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>312.4</v>
+        <v>332.7</v>
       </c>
       <c r="H54" t="n">
-        <v>27.2</v>
+        <v>24.3</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>112.38</v>
+        <v>269.06</v>
       </c>
       <c r="K54" t="n">
-        <v>-413.73</v>
+        <v>376.34</v>
       </c>
       <c r="L54" t="n">
-        <v>428.72</v>
+        <v>462.63</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:26:00</t>
+          <t>07:22:04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.32</v>
+        <v>3.68</v>
       </c>
       <c r="F55" t="n">
-        <v>9.369999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="G55" t="n">
-        <v>323.7</v>
+        <v>325.5</v>
       </c>
       <c r="H55" t="n">
-        <v>23.3</v>
+        <v>33.7</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>721.8200000000001</v>
+        <v>282.4</v>
       </c>
       <c r="K55" t="n">
-        <v>-83.51000000000001</v>
+        <v>-139.47</v>
       </c>
       <c r="L55" t="n">
-        <v>726.63</v>
+        <v>314.97</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:30:15</t>
+          <t>07:26:17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.77</v>
+        <v>3.38</v>
       </c>
       <c r="F56" t="n">
-        <v>9.619999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="G56" t="n">
-        <v>325.5</v>
+        <v>323.7</v>
       </c>
       <c r="H56" t="n">
-        <v>15.3</v>
+        <v>21.8</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-575.3200000000001</v>
+        <v>-255.87</v>
       </c>
       <c r="K56" t="n">
-        <v>-412.31</v>
+        <v>236.39</v>
       </c>
       <c r="L56" t="n">
-        <v>707.8099999999999</v>
+        <v>348.35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:32:05</t>
+          <t>07:27:11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="F57" t="n">
-        <v>9.24</v>
+        <v>9.75</v>
       </c>
       <c r="G57" t="n">
-        <v>325.3</v>
+        <v>327</v>
       </c>
       <c r="H57" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-526.3099999999999</v>
+        <v>-111.37</v>
       </c>
       <c r="K57" t="n">
-        <v>185.11</v>
+        <v>195.15</v>
       </c>
       <c r="L57" t="n">
-        <v>557.91</v>
+        <v>224.69</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:33:01</t>
+          <t>07:29:09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.24</v>
+        <v>2.72</v>
       </c>
       <c r="F58" t="n">
-        <v>9.84</v>
+        <v>9.25</v>
       </c>
       <c r="G58" t="n">
-        <v>317.8</v>
+        <v>322.6</v>
       </c>
       <c r="H58" t="n">
-        <v>30.6</v>
+        <v>38.8</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-730.1900000000001</v>
+        <v>542.27</v>
       </c>
       <c r="K58" t="n">
-        <v>350.51</v>
+        <v>374.92</v>
       </c>
       <c r="L58" t="n">
-        <v>809.96</v>
+        <v>659.26</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:40:07</t>
+          <t>07:37:57</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.39</v>
+        <v>2.71</v>
       </c>
       <c r="F59" t="n">
-        <v>9.51</v>
+        <v>9.41</v>
       </c>
       <c r="G59" t="n">
-        <v>320.2</v>
+        <v>314.4</v>
       </c>
       <c r="H59" t="n">
-        <v>23</v>
+        <v>28.9</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J59" t="n">
-        <v>18.67</v>
+        <v>120.8</v>
       </c>
       <c r="K59" t="n">
-        <v>119.17</v>
+        <v>-93.38</v>
       </c>
       <c r="L59" t="n">
-        <v>120.62</v>
+        <v>152.68</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:41:06</t>
+          <t>07:39:17</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.41</v>
+        <v>3.38</v>
       </c>
       <c r="F60" t="n">
-        <v>8.68</v>
+        <v>9.34</v>
       </c>
       <c r="G60" t="n">
-        <v>329.7</v>
+        <v>335.5</v>
       </c>
       <c r="H60" t="n">
-        <v>22</v>
+        <v>24.2</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-66.31999999999999</v>
+        <v>-132.16</v>
       </c>
       <c r="K60" t="n">
-        <v>-67.37</v>
+        <v>-211.46</v>
       </c>
       <c r="L60" t="n">
-        <v>94.54000000000001</v>
+        <v>249.36</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:43:27</t>
+          <t>07:40:44</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="F61" t="n">
-        <v>9.35</v>
+        <v>9.01</v>
       </c>
       <c r="G61" t="n">
-        <v>317.2</v>
+        <v>336.2</v>
       </c>
       <c r="H61" t="n">
-        <v>30.6</v>
+        <v>24.2</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>11.56</v>
+        <v>-132.1</v>
       </c>
       <c r="K61" t="n">
-        <v>75.53</v>
+        <v>122.69</v>
       </c>
       <c r="L61" t="n">
-        <v>76.41</v>
+        <v>180.28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:48:43</t>
+          <t>07:45:19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>9.789999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>318.6</v>
+        <v>333.7</v>
       </c>
       <c r="H62" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-304.09</v>
+        <v>200.88</v>
       </c>
       <c r="K62" t="n">
-        <v>-70.53</v>
+        <v>20.49</v>
       </c>
       <c r="L62" t="n">
-        <v>312.16</v>
+        <v>201.93</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:50:25</t>
+          <t>07:47:26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="F63" t="n">
-        <v>9.44</v>
+        <v>8.93</v>
       </c>
       <c r="G63" t="n">
-        <v>320.5</v>
+        <v>319.3</v>
       </c>
       <c r="H63" t="n">
-        <v>14.3</v>
+        <v>26.2</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-14.33</v>
+        <v>-216.83</v>
       </c>
       <c r="K63" t="n">
-        <v>-160.73</v>
+        <v>-34</v>
       </c>
       <c r="L63" t="n">
-        <v>161.36</v>
+        <v>219.48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:51:54</t>
+          <t>07:48:32</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="F64" t="n">
-        <v>9.9</v>
+        <v>9.25</v>
       </c>
       <c r="G64" t="n">
-        <v>314.9</v>
+        <v>344.1</v>
       </c>
       <c r="H64" t="n">
-        <v>19</v>
+        <v>27.5</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-206.82</v>
+        <v>155.91</v>
       </c>
       <c r="K64" t="n">
-        <v>105.93</v>
+        <v>43.48</v>
       </c>
       <c r="L64" t="n">
-        <v>232.37</v>
+        <v>161.86</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:56:50</t>
+          <t>07:54:43</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.76</v>
+        <v>4.49</v>
       </c>
       <c r="F65" t="n">
-        <v>9.01</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>325.4</v>
+        <v>308.9</v>
       </c>
       <c r="H65" t="n">
-        <v>24</v>
+        <v>19.9</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-152.9</v>
+        <v>327.93</v>
       </c>
       <c r="K65" t="n">
-        <v>175.46</v>
+        <v>27.94</v>
       </c>
       <c r="L65" t="n">
-        <v>232.74</v>
+        <v>329.11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:59:16</t>
+          <t>07:55:48</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.05</v>
+        <v>3.33</v>
       </c>
       <c r="F66" t="n">
-        <v>9.25</v>
+        <v>8.91</v>
       </c>
       <c r="G66" t="n">
-        <v>331.3</v>
+        <v>317.2</v>
       </c>
       <c r="H66" t="n">
-        <v>27</v>
+        <v>28.9</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-305.51</v>
+        <v>84.28</v>
       </c>
       <c r="K66" t="n">
-        <v>-527.8099999999999</v>
+        <v>-49.28</v>
       </c>
       <c r="L66" t="n">
-        <v>609.86</v>
+        <v>97.63</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:02:03</t>
+          <t>07:56:55</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.53</v>
+        <v>3.59</v>
       </c>
       <c r="F67" t="n">
-        <v>9.119999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="G67" t="n">
-        <v>335.5</v>
+        <v>340.2</v>
       </c>
       <c r="H67" t="n">
-        <v>24.3</v>
+        <v>23.1</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-58.19</v>
+        <v>-54.37</v>
       </c>
       <c r="K67" t="n">
-        <v>-113.67</v>
+        <v>221.22</v>
       </c>
       <c r="L67" t="n">
-        <v>127.69</v>
+        <v>227.81</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:07:34</t>
+          <t>08:02:03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.99</v>
+        <v>3.64</v>
       </c>
       <c r="F68" t="n">
-        <v>10.55</v>
+        <v>10.04</v>
       </c>
       <c r="G68" t="n">
-        <v>327.2</v>
+        <v>332.2</v>
       </c>
       <c r="H68" t="n">
-        <v>28.1</v>
+        <v>23</v>
       </c>
       <c r="I68" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-261.62</v>
+        <v>-11.11</v>
       </c>
       <c r="K68" t="n">
-        <v>-101.12</v>
+        <v>-160.65</v>
       </c>
       <c r="L68" t="n">
-        <v>280.49</v>
+        <v>161.03</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:09:44</t>
+          <t>08:04:10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2938,31 +2938,31 @@
         <v>3.32</v>
       </c>
       <c r="F69" t="n">
-        <v>9.210000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>326</v>
+        <v>336.5</v>
       </c>
       <c r="H69" t="n">
-        <v>32.8</v>
+        <v>22.6</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>212.87</v>
+        <v>-165.11</v>
       </c>
       <c r="K69" t="n">
-        <v>45.32</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>217.64</v>
+        <v>183</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:11:34</t>
+          <t>08:06:07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.64</v>
+        <v>3.23</v>
       </c>
       <c r="F70" t="n">
-        <v>9.91</v>
+        <v>9.43</v>
       </c>
       <c r="G70" t="n">
-        <v>321.8</v>
+        <v>329.1</v>
       </c>
       <c r="H70" t="n">
-        <v>27.1</v>
+        <v>19.3</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-177.87</v>
+        <v>-125.41</v>
       </c>
       <c r="K70" t="n">
-        <v>-235.54</v>
+        <v>-220.06</v>
       </c>
       <c r="L70" t="n">
-        <v>295.15</v>
+        <v>253.29</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:15:27</t>
+          <t>08:10:04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="F71" t="n">
-        <v>9.81</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>325.7</v>
+        <v>335.5</v>
       </c>
       <c r="H71" t="n">
-        <v>23.8</v>
+        <v>34.7</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>-244.14</v>
+        <v>168.18</v>
       </c>
       <c r="K71" t="n">
-        <v>172.7</v>
+        <v>45.19</v>
       </c>
       <c r="L71" t="n">
-        <v>299.04</v>
+        <v>174.14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:17:26</t>
+          <t>08:11:18</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.45</v>
+        <v>3.02</v>
       </c>
       <c r="F72" t="n">
-        <v>9.84</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>323.4</v>
+        <v>338.9</v>
       </c>
       <c r="H72" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I72" t="n">
         <v>26</v>
       </c>
-      <c r="I72" t="n">
-        <v>25</v>
-      </c>
       <c r="J72" t="n">
-        <v>250.28</v>
+        <v>-494.18</v>
       </c>
       <c r="K72" t="n">
-        <v>-604.48</v>
+        <v>-332.78</v>
       </c>
       <c r="L72" t="n">
-        <v>654.24</v>
+        <v>595.78</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:19:28</t>
+          <t>08:13:42</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.79</v>
+        <v>3.66</v>
       </c>
       <c r="F73" t="n">
-        <v>10.09</v>
+        <v>9.23</v>
       </c>
       <c r="G73" t="n">
-        <v>314.1</v>
+        <v>312.5</v>
       </c>
       <c r="H73" t="n">
-        <v>22.5</v>
+        <v>26.5</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-138.29</v>
+        <v>-249</v>
       </c>
       <c r="K73" t="n">
-        <v>-13.66</v>
+        <v>-55.83</v>
       </c>
       <c r="L73" t="n">
-        <v>138.96</v>
+        <v>255.18</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:28:22</t>
+          <t>08:24:05</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="F74" t="n">
-        <v>9.67</v>
+        <v>8.9</v>
       </c>
       <c r="G74" t="n">
-        <v>320.4</v>
+        <v>324.2</v>
       </c>
       <c r="H74" t="n">
-        <v>22.1</v>
+        <v>33.4</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.53</v>
+        <v>-174.63</v>
       </c>
       <c r="K74" t="n">
-        <v>-39.31</v>
+        <v>-107.89</v>
       </c>
       <c r="L74" t="n">
-        <v>39.85</v>
+        <v>205.27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:29:16</t>
+          <t>08:26:25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="F75" t="n">
-        <v>9.27</v>
+        <v>9.56</v>
       </c>
       <c r="G75" t="n">
-        <v>323.5</v>
+        <v>323.3</v>
       </c>
       <c r="H75" t="n">
-        <v>33.8</v>
+        <v>26</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-153.73</v>
+        <v>45.26</v>
       </c>
       <c r="K75" t="n">
-        <v>-72.69</v>
+        <v>-6.27</v>
       </c>
       <c r="L75" t="n">
-        <v>170.05</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:30:39</t>
+          <t>08:28:25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.89</v>
+        <v>3.93</v>
       </c>
       <c r="F76" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>334.6</v>
+        <v>333.5</v>
       </c>
       <c r="H76" t="n">
-        <v>25.4</v>
+        <v>21.9</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-72.79000000000001</v>
+        <v>38.34</v>
       </c>
       <c r="K76" t="n">
-        <v>2.03</v>
+        <v>-36.81</v>
       </c>
       <c r="L76" t="n">
-        <v>72.81999999999999</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:33:52</t>
+          <t>08:32:26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.59</v>
+        <v>3.95</v>
       </c>
       <c r="F77" t="n">
-        <v>8.56</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>331.8</v>
+        <v>332.3</v>
       </c>
       <c r="H77" t="n">
-        <v>25.2</v>
+        <v>30</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-9.9</v>
+        <v>111.33</v>
       </c>
       <c r="K77" t="n">
-        <v>265.71</v>
+        <v>40.02</v>
       </c>
       <c r="L77" t="n">
-        <v>265.89</v>
+        <v>118.31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:36:02</t>
+          <t>08:33:33</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="F78" t="n">
-        <v>9.640000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>320.8</v>
+        <v>337.4</v>
       </c>
       <c r="H78" t="n">
-        <v>27.4</v>
+        <v>26.5</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>152.86</v>
+        <v>-78.52</v>
       </c>
       <c r="K78" t="n">
-        <v>-281.34</v>
+        <v>250.8</v>
       </c>
       <c r="L78" t="n">
-        <v>320.19</v>
+        <v>262.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:37:13</t>
+          <t>08:35:39</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="F79" t="n">
-        <v>9.289999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>311.4</v>
+        <v>323.4</v>
       </c>
       <c r="H79" t="n">
-        <v>14.4</v>
+        <v>27.7</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>-159.9</v>
+        <v>56.29</v>
       </c>
       <c r="K79" t="n">
-        <v>-65.06999999999999</v>
+        <v>-80.06</v>
       </c>
       <c r="L79" t="n">
-        <v>172.63</v>
+        <v>97.87</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:43:05</t>
+          <t>08:41:27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.53</v>
+        <v>3.79</v>
       </c>
       <c r="F80" t="n">
-        <v>9.050000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="G80" t="n">
-        <v>330.8</v>
+        <v>321.4</v>
       </c>
       <c r="H80" t="n">
-        <v>23.2</v>
+        <v>30.3</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-28.97</v>
+        <v>-272.76</v>
       </c>
       <c r="K80" t="n">
-        <v>-114.08</v>
+        <v>157.18</v>
       </c>
       <c r="L80" t="n">
-        <v>117.7</v>
+        <v>314.8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:44:52</t>
+          <t>08:43:05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="F81" t="n">
-        <v>9.06</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>331.9</v>
+        <v>325.6</v>
       </c>
       <c r="H81" t="n">
-        <v>31.3</v>
+        <v>29.2</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-127.28</v>
+        <v>-342.16</v>
       </c>
       <c r="K81" t="n">
-        <v>-75.29000000000001</v>
+        <v>-153.1</v>
       </c>
       <c r="L81" t="n">
-        <v>147.88</v>
+        <v>374.85</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:46:58</t>
+          <t>08:45:01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.64</v>
+        <v>3.51</v>
       </c>
       <c r="F82" t="n">
-        <v>9</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>308.7</v>
+        <v>321.6</v>
       </c>
       <c r="H82" t="n">
-        <v>25.9</v>
+        <v>24.2</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>48.07</v>
+        <v>-79.86</v>
       </c>
       <c r="K82" t="n">
-        <v>-137.5</v>
+        <v>362.06</v>
       </c>
       <c r="L82" t="n">
-        <v>145.66</v>
+        <v>370.76</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:51:33</t>
+          <t>08:48:37</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.19</v>
+        <v>3.73</v>
       </c>
       <c r="F83" t="n">
-        <v>9.06</v>
+        <v>8.99</v>
       </c>
       <c r="G83" t="n">
-        <v>331.2</v>
+        <v>317.5</v>
       </c>
       <c r="H83" t="n">
-        <v>29.7</v>
+        <v>26.3</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-155.13</v>
+        <v>-159.61</v>
       </c>
       <c r="K83" t="n">
-        <v>-54.09</v>
+        <v>-309.11</v>
       </c>
       <c r="L83" t="n">
-        <v>164.29</v>
+        <v>347.89</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:52:44</t>
+          <t>08:50:45</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.82</v>
+        <v>3.53</v>
       </c>
       <c r="F84" t="n">
-        <v>10</v>
+        <v>9.65</v>
       </c>
       <c r="G84" t="n">
-        <v>320.3</v>
+        <v>323.3</v>
       </c>
       <c r="H84" t="n">
-        <v>26.8</v>
+        <v>18.5</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-151.51</v>
+        <v>576.74</v>
       </c>
       <c r="K84" t="n">
-        <v>252.15</v>
+        <v>363.32</v>
       </c>
       <c r="L84" t="n">
-        <v>294.17</v>
+        <v>681.64</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:55:35</t>
+          <t>08:53:11</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="F85" t="n">
-        <v>9.75</v>
+        <v>9.08</v>
       </c>
       <c r="G85" t="n">
-        <v>334.1</v>
+        <v>331.4</v>
       </c>
       <c r="H85" t="n">
-        <v>21.8</v>
+        <v>27.1</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>29.94</v>
+        <v>-250.42</v>
       </c>
       <c r="K85" t="n">
-        <v>147.33</v>
+        <v>183.79</v>
       </c>
       <c r="L85" t="n">
-        <v>150.34</v>
+        <v>310.63</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:00:37</t>
+          <t>08:57:58</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.95</v>
+        <v>3.36</v>
       </c>
       <c r="F86" t="n">
-        <v>9.9</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>321.9</v>
+        <v>322.5</v>
       </c>
       <c r="H86" t="n">
-        <v>32.9</v>
+        <v>28.1</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-58.88</v>
+        <v>-476.03</v>
       </c>
       <c r="K86" t="n">
-        <v>-306.58</v>
+        <v>-286.75</v>
       </c>
       <c r="L86" t="n">
-        <v>312.18</v>
+        <v>555.72</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:02:29</t>
+          <t>08:59:55</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="F87" t="n">
-        <v>9.289999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>320.1</v>
+        <v>332.2</v>
       </c>
       <c r="H87" t="n">
-        <v>30.7</v>
+        <v>29.4</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-788.3099999999999</v>
+        <v>407.54</v>
       </c>
       <c r="K87" t="n">
-        <v>178.54</v>
+        <v>433.57</v>
       </c>
       <c r="L87" t="n">
-        <v>808.28</v>
+        <v>595.04</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:03:38</t>
+          <t>09:01:19</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.83</v>
+        <v>3.67</v>
       </c>
       <c r="F88" t="n">
-        <v>8.779999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="G88" t="n">
-        <v>328.6</v>
+        <v>321.3</v>
       </c>
       <c r="H88" t="n">
-        <v>29.8</v>
+        <v>17</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-736.61</v>
+        <v>554.52</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.43</v>
+        <v>-497.77</v>
       </c>
       <c r="L88" t="n">
-        <v>736.61</v>
+        <v>745.17</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>4.94</v>
+        <v>4.78</v>
       </c>
       <c r="K14" t="n">
-        <v>-117.21</v>
+        <v>-113.45</v>
       </c>
       <c r="L14" t="n">
-        <v>117.31</v>
+        <v>113.55</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>45.09</v>
+        <v>60.73</v>
       </c>
       <c r="K15" t="n">
-        <v>11.68</v>
+        <v>15.74</v>
       </c>
       <c r="L15" t="n">
-        <v>46.58</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-137.17</v>
+        <v>-111.22</v>
       </c>
       <c r="K16" t="n">
-        <v>-139.87</v>
+        <v>-113.41</v>
       </c>
       <c r="L16" t="n">
-        <v>195.9</v>
+        <v>158.84</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-46.8</v>
+        <v>-72.31999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="L17" t="n">
-        <v>46.81</v>
+        <v>72.34</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-182.72</v>
+        <v>-109.93</v>
       </c>
       <c r="K18" t="n">
-        <v>-143.49</v>
+        <v>-86.33</v>
       </c>
       <c r="L18" t="n">
-        <v>232.32</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>425.72</v>
+        <v>320.84</v>
       </c>
       <c r="K19" t="n">
-        <v>-298.94</v>
+        <v>-225.29</v>
       </c>
       <c r="L19" t="n">
-        <v>520.1900000000001</v>
+        <v>392.03</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-202.75</v>
+        <v>-209.47</v>
       </c>
       <c r="K20" t="n">
-        <v>179.83</v>
+        <v>185.8</v>
       </c>
       <c r="L20" t="n">
-        <v>271.01</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>191.57</v>
+        <v>150.95</v>
       </c>
       <c r="K21" t="n">
-        <v>-118.53</v>
+        <v>-93.40000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>225.28</v>
+        <v>177.51</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-17.14</v>
+        <v>-15.77</v>
       </c>
       <c r="K22" t="n">
-        <v>258.64</v>
+        <v>237.99</v>
       </c>
       <c r="L22" t="n">
-        <v>259.21</v>
+        <v>238.51</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-76.95999999999999</v>
+        <v>-90.12</v>
       </c>
       <c r="K23" t="n">
-        <v>207.52</v>
+        <v>243.01</v>
       </c>
       <c r="L23" t="n">
-        <v>221.33</v>
+        <v>259.19</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-432.53</v>
+        <v>-337.93</v>
       </c>
       <c r="K24" t="n">
-        <v>195.91</v>
+        <v>153.06</v>
       </c>
       <c r="L24" t="n">
-        <v>474.83</v>
+        <v>370.98</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-383.84</v>
+        <v>-401.12</v>
       </c>
       <c r="K25" t="n">
-        <v>84.73</v>
+        <v>88.55</v>
       </c>
       <c r="L25" t="n">
-        <v>393.09</v>
+        <v>410.77</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-533.6</v>
+        <v>-540.4400000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-39.31</v>
+        <v>-39.82</v>
       </c>
       <c r="L26" t="n">
-        <v>535.05</v>
+        <v>541.9</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>327.99</v>
+        <v>330.46</v>
       </c>
       <c r="K27" t="n">
-        <v>-486.26</v>
+        <v>-489.93</v>
       </c>
       <c r="L27" t="n">
-        <v>586.54</v>
+        <v>590.96</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-535.64</v>
+        <v>-557.02</v>
       </c>
       <c r="K28" t="n">
-        <v>221.48</v>
+        <v>230.32</v>
       </c>
       <c r="L28" t="n">
-        <v>579.62</v>
+        <v>602.76</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>48.47</v>
+        <v>54.77</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.32</v>
+        <v>-41.04</v>
       </c>
       <c r="L29" t="n">
-        <v>60.56</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.300000000000001</v>
+        <v>-6.91</v>
       </c>
       <c r="K30" t="n">
-        <v>-144.29</v>
+        <v>-120.11</v>
       </c>
       <c r="L30" t="n">
-        <v>144.52</v>
+        <v>120.31</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-83.05</v>
+        <v>-79.41</v>
       </c>
       <c r="K31" t="n">
-        <v>-42.99</v>
+        <v>-41.1</v>
       </c>
       <c r="L31" t="n">
-        <v>93.52</v>
+        <v>89.41</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-33.1</v>
+        <v>-31.18</v>
       </c>
       <c r="K32" t="n">
-        <v>148.81</v>
+        <v>140.17</v>
       </c>
       <c r="L32" t="n">
-        <v>152.44</v>
+        <v>143.6</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>88.67</v>
+        <v>75.48</v>
       </c>
       <c r="K33" t="n">
-        <v>-140.83</v>
+        <v>-119.89</v>
       </c>
       <c r="L33" t="n">
-        <v>166.42</v>
+        <v>141.67</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-321</v>
+        <v>-236.14</v>
       </c>
       <c r="K34" t="n">
-        <v>256.5</v>
+        <v>188.69</v>
       </c>
       <c r="L34" t="n">
-        <v>410.89</v>
+        <v>302.26</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-201.49</v>
+        <v>-170.18</v>
       </c>
       <c r="K35" t="n">
-        <v>-237.3</v>
+        <v>-200.42</v>
       </c>
       <c r="L35" t="n">
-        <v>311.3</v>
+        <v>262.92</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-91.45999999999999</v>
+        <v>-117.9</v>
       </c>
       <c r="K36" t="n">
-        <v>-107.07</v>
+        <v>-138.03</v>
       </c>
       <c r="L36" t="n">
-        <v>140.81</v>
+        <v>181.53</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-168.66</v>
+        <v>-198.25</v>
       </c>
       <c r="K37" t="n">
-        <v>-110.34</v>
+        <v>-129.69</v>
       </c>
       <c r="L37" t="n">
-        <v>201.55</v>
+        <v>236.9</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>31</v>
       </c>
       <c r="J38" t="n">
-        <v>-228.31</v>
+        <v>-256.57</v>
       </c>
       <c r="K38" t="n">
-        <v>-47.4</v>
+        <v>-53.27</v>
       </c>
       <c r="L38" t="n">
-        <v>233.18</v>
+        <v>262.04</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-151.02</v>
+        <v>-198.69</v>
       </c>
       <c r="K39" t="n">
-        <v>-94.64</v>
+        <v>-124.52</v>
       </c>
       <c r="L39" t="n">
-        <v>178.22</v>
+        <v>234.49</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>209.29</v>
+        <v>248.16</v>
       </c>
       <c r="K40" t="n">
-        <v>180.66</v>
+        <v>214.21</v>
       </c>
       <c r="L40" t="n">
-        <v>276.48</v>
+        <v>327.83</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>-41.69</v>
+        <v>-50.53</v>
       </c>
       <c r="K41" t="n">
-        <v>-354.35</v>
+        <v>-429.54</v>
       </c>
       <c r="L41" t="n">
-        <v>356.79</v>
+        <v>432.5</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-31.7</v>
+        <v>-36.34</v>
       </c>
       <c r="K42" t="n">
-        <v>366.47</v>
+        <v>420.18</v>
       </c>
       <c r="L42" t="n">
-        <v>367.83</v>
+        <v>421.74</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-413.98</v>
+        <v>-415.83</v>
       </c>
       <c r="K43" t="n">
-        <v>-22.95</v>
+        <v>-23.05</v>
       </c>
       <c r="L43" t="n">
-        <v>414.61</v>
+        <v>416.47</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>42.77</v>
+        <v>52.55</v>
       </c>
       <c r="K44" t="n">
-        <v>-97.78</v>
+        <v>-120.11</v>
       </c>
       <c r="L44" t="n">
-        <v>106.72</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>241.03</v>
+        <v>181.73</v>
       </c>
       <c r="K45" t="n">
-        <v>156.75</v>
+        <v>118.18</v>
       </c>
       <c r="L45" t="n">
-        <v>287.52</v>
+        <v>216.78</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>34.77</v>
+        <v>30.16</v>
       </c>
       <c r="K46" t="n">
-        <v>-78.34</v>
+        <v>-67.95</v>
       </c>
       <c r="L46" t="n">
-        <v>85.70999999999999</v>
+        <v>74.34</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>124.81</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-178.61</v>
+        <v>-135.45</v>
       </c>
       <c r="L47" t="n">
-        <v>217.89</v>
+        <v>165.24</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-177.51</v>
+        <v>-145.17</v>
       </c>
       <c r="K48" t="n">
-        <v>-24.79</v>
+        <v>-20.27</v>
       </c>
       <c r="L48" t="n">
-        <v>179.23</v>
+        <v>146.58</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-123.94</v>
+        <v>-127.38</v>
       </c>
       <c r="K49" t="n">
-        <v>25.09</v>
+        <v>25.78</v>
       </c>
       <c r="L49" t="n">
-        <v>126.46</v>
+        <v>129.97</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-141.44</v>
+        <v>-156.41</v>
       </c>
       <c r="K50" t="n">
-        <v>-119.57</v>
+        <v>-132.22</v>
       </c>
       <c r="L50" t="n">
-        <v>185.21</v>
+        <v>204.81</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>181.98</v>
+        <v>181.3</v>
       </c>
       <c r="K51" t="n">
-        <v>-133.8</v>
+        <v>-133.29</v>
       </c>
       <c r="L51" t="n">
-        <v>225.87</v>
+        <v>225.02</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-18.82</v>
+        <v>-22.3</v>
       </c>
       <c r="K52" t="n">
-        <v>239.88</v>
+        <v>284.29</v>
       </c>
       <c r="L52" t="n">
-        <v>240.61</v>
+        <v>285.16</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-107.42</v>
+        <v>-184.91</v>
       </c>
       <c r="K53" t="n">
-        <v>-27.95</v>
+        <v>-48.12</v>
       </c>
       <c r="L53" t="n">
-        <v>111</v>
+        <v>191.07</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>269.06</v>
+        <v>227.47</v>
       </c>
       <c r="K54" t="n">
-        <v>376.34</v>
+        <v>318.17</v>
       </c>
       <c r="L54" t="n">
-        <v>462.63</v>
+        <v>391.12</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>282.4</v>
+        <v>329.09</v>
       </c>
       <c r="K55" t="n">
-        <v>-139.47</v>
+        <v>-162.53</v>
       </c>
       <c r="L55" t="n">
-        <v>314.97</v>
+        <v>367.03</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-255.87</v>
+        <v>-306</v>
       </c>
       <c r="K56" t="n">
-        <v>236.39</v>
+        <v>282.69</v>
       </c>
       <c r="L56" t="n">
-        <v>348.35</v>
+        <v>416.59</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-111.37</v>
+        <v>-142.15</v>
       </c>
       <c r="K57" t="n">
-        <v>195.15</v>
+        <v>249.09</v>
       </c>
       <c r="L57" t="n">
-        <v>224.69</v>
+        <v>286.79</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>542.27</v>
+        <v>549.42</v>
       </c>
       <c r="K58" t="n">
-        <v>374.92</v>
+        <v>379.87</v>
       </c>
       <c r="L58" t="n">
-        <v>659.26</v>
+        <v>667.95</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>29</v>
       </c>
       <c r="J59" t="n">
-        <v>120.8</v>
+        <v>85.48</v>
       </c>
       <c r="K59" t="n">
-        <v>-93.38</v>
+        <v>-66.06999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>152.68</v>
+        <v>108.04</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-132.16</v>
+        <v>-93.06999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-211.46</v>
+        <v>-148.92</v>
       </c>
       <c r="L60" t="n">
-        <v>249.36</v>
+        <v>175.62</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-132.1</v>
+        <v>-114.05</v>
       </c>
       <c r="K61" t="n">
-        <v>122.69</v>
+        <v>105.93</v>
       </c>
       <c r="L61" t="n">
-        <v>180.28</v>
+        <v>155.65</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>200.88</v>
+        <v>191.98</v>
       </c>
       <c r="K62" t="n">
-        <v>20.49</v>
+        <v>19.58</v>
       </c>
       <c r="L62" t="n">
-        <v>201.93</v>
+        <v>192.98</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-216.83</v>
+        <v>-200.87</v>
       </c>
       <c r="K63" t="n">
-        <v>-34</v>
+        <v>-31.5</v>
       </c>
       <c r="L63" t="n">
-        <v>219.48</v>
+        <v>203.33</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>155.91</v>
+        <v>156.31</v>
       </c>
       <c r="K64" t="n">
-        <v>43.48</v>
+        <v>43.59</v>
       </c>
       <c r="L64" t="n">
-        <v>161.86</v>
+        <v>162.28</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>327.93</v>
+        <v>385.25</v>
       </c>
       <c r="K65" t="n">
-        <v>27.94</v>
+        <v>32.82</v>
       </c>
       <c r="L65" t="n">
-        <v>329.11</v>
+        <v>386.64</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>84.28</v>
+        <v>133.86</v>
       </c>
       <c r="K66" t="n">
-        <v>-49.28</v>
+        <v>-78.27</v>
       </c>
       <c r="L66" t="n">
-        <v>97.63</v>
+        <v>155.06</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-54.37</v>
+        <v>-64.73999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>221.22</v>
+        <v>263.42</v>
       </c>
       <c r="L67" t="n">
-        <v>227.81</v>
+        <v>271.26</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-11.11</v>
+        <v>-19.54</v>
       </c>
       <c r="K68" t="n">
-        <v>-160.65</v>
+        <v>-282.62</v>
       </c>
       <c r="L68" t="n">
-        <v>161.03</v>
+        <v>283.29</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-165.11</v>
+        <v>-240.39</v>
       </c>
       <c r="K69" t="n">
-        <v>78.93000000000001</v>
+        <v>114.92</v>
       </c>
       <c r="L69" t="n">
-        <v>183</v>
+        <v>266.45</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-125.41</v>
+        <v>-139.68</v>
       </c>
       <c r="K70" t="n">
-        <v>-220.06</v>
+        <v>-245.08</v>
       </c>
       <c r="L70" t="n">
-        <v>253.29</v>
+        <v>282.09</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>168.18</v>
+        <v>268.3</v>
       </c>
       <c r="K71" t="n">
-        <v>45.19</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>174.14</v>
+        <v>277.82</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-494.18</v>
+        <v>-525.4</v>
       </c>
       <c r="K72" t="n">
-        <v>-332.78</v>
+        <v>-353.81</v>
       </c>
       <c r="L72" t="n">
-        <v>595.78</v>
+        <v>633.42</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-249</v>
+        <v>-342.56</v>
       </c>
       <c r="K73" t="n">
-        <v>-55.83</v>
+        <v>-76.8</v>
       </c>
       <c r="L73" t="n">
-        <v>255.18</v>
+        <v>351.06</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>-174.63</v>
+        <v>-128.34</v>
       </c>
       <c r="K74" t="n">
-        <v>-107.89</v>
+        <v>-79.29000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>205.27</v>
+        <v>150.86</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>45.26</v>
+        <v>89.7</v>
       </c>
       <c r="K75" t="n">
-        <v>-6.27</v>
+        <v>-12.42</v>
       </c>
       <c r="L75" t="n">
-        <v>45.69</v>
+        <v>90.56</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>38.34</v>
+        <v>66.11</v>
       </c>
       <c r="K76" t="n">
-        <v>-36.81</v>
+        <v>-63.47</v>
       </c>
       <c r="L76" t="n">
-        <v>53.16</v>
+        <v>91.64</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>111.33</v>
+        <v>144.25</v>
       </c>
       <c r="K77" t="n">
-        <v>40.02</v>
+        <v>51.86</v>
       </c>
       <c r="L77" t="n">
-        <v>118.31</v>
+        <v>153.28</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-78.52</v>
+        <v>-75.95</v>
       </c>
       <c r="K78" t="n">
-        <v>250.8</v>
+        <v>242.58</v>
       </c>
       <c r="L78" t="n">
-        <v>262.8</v>
+        <v>254.19</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>56.29</v>
+        <v>62.62</v>
       </c>
       <c r="K79" t="n">
-        <v>-80.06</v>
+        <v>-89.05</v>
       </c>
       <c r="L79" t="n">
-        <v>97.87</v>
+        <v>108.86</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-272.76</v>
+        <v>-247.21</v>
       </c>
       <c r="K80" t="n">
-        <v>157.18</v>
+        <v>142.46</v>
       </c>
       <c r="L80" t="n">
-        <v>314.8</v>
+        <v>285.32</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-342.16</v>
+        <v>-270.44</v>
       </c>
       <c r="K81" t="n">
-        <v>-153.1</v>
+        <v>-121.01</v>
       </c>
       <c r="L81" t="n">
-        <v>374.85</v>
+        <v>296.28</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>-79.86</v>
+        <v>-69.48</v>
       </c>
       <c r="K82" t="n">
-        <v>362.06</v>
+        <v>314.98</v>
       </c>
       <c r="L82" t="n">
-        <v>370.76</v>
+        <v>322.55</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-159.61</v>
+        <v>-188.62</v>
       </c>
       <c r="K83" t="n">
-        <v>-309.11</v>
+        <v>-365.28</v>
       </c>
       <c r="L83" t="n">
-        <v>347.89</v>
+        <v>411.11</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>576.74</v>
+        <v>518.92</v>
       </c>
       <c r="K84" t="n">
-        <v>363.32</v>
+        <v>326.9</v>
       </c>
       <c r="L84" t="n">
-        <v>681.64</v>
+        <v>613.3</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-250.42</v>
+        <v>-336.96</v>
       </c>
       <c r="K85" t="n">
-        <v>183.79</v>
+        <v>247.3</v>
       </c>
       <c r="L85" t="n">
-        <v>310.63</v>
+        <v>417.97</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-476.03</v>
+        <v>-522.3</v>
       </c>
       <c r="K86" t="n">
-        <v>-286.75</v>
+        <v>-314.62</v>
       </c>
       <c r="L86" t="n">
-        <v>555.72</v>
+        <v>609.74</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>407.54</v>
+        <v>455.77</v>
       </c>
       <c r="K87" t="n">
-        <v>433.57</v>
+        <v>484.88</v>
       </c>
       <c r="L87" t="n">
-        <v>595.04</v>
+        <v>665.46</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>554.52</v>
+        <v>556.54</v>
       </c>
       <c r="K88" t="n">
-        <v>-497.77</v>
+        <v>-499.59</v>
       </c>
       <c r="L88" t="n">
-        <v>745.17</v>
+        <v>747.88</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>4.78</v>
+        <v>5.01</v>
       </c>
       <c r="K14" t="n">
-        <v>-113.45</v>
+        <v>-119.07</v>
       </c>
       <c r="L14" t="n">
-        <v>113.55</v>
+        <v>119.18</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>60.73</v>
+        <v>63.61</v>
       </c>
       <c r="K15" t="n">
-        <v>15.74</v>
+        <v>16.48</v>
       </c>
       <c r="L15" t="n">
-        <v>62.74</v>
+        <v>65.70999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-111.22</v>
+        <v>-98.20999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-113.41</v>
+        <v>-100.14</v>
       </c>
       <c r="L16" t="n">
-        <v>158.84</v>
+        <v>140.26</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-72.31999999999999</v>
+        <v>-64.87</v>
       </c>
       <c r="K17" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="L17" t="n">
-        <v>72.34</v>
+        <v>64.89</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-109.93</v>
+        <v>-123.11</v>
       </c>
       <c r="K18" t="n">
-        <v>-86.33</v>
+        <v>-96.68000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>139.77</v>
+        <v>156.53</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>320.84</v>
+        <v>255.02</v>
       </c>
       <c r="K19" t="n">
-        <v>-225.29</v>
+        <v>-179.07</v>
       </c>
       <c r="L19" t="n">
-        <v>392.03</v>
+        <v>311.61</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-209.47</v>
+        <v>-149.41</v>
       </c>
       <c r="K20" t="n">
-        <v>185.8</v>
+        <v>132.52</v>
       </c>
       <c r="L20" t="n">
-        <v>280</v>
+        <v>199.72</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>150.95</v>
+        <v>137.47</v>
       </c>
       <c r="K21" t="n">
-        <v>-93.40000000000001</v>
+        <v>-85.05</v>
       </c>
       <c r="L21" t="n">
-        <v>177.51</v>
+        <v>161.65</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-15.77</v>
+        <v>-12.47</v>
       </c>
       <c r="K22" t="n">
-        <v>237.99</v>
+        <v>188.23</v>
       </c>
       <c r="L22" t="n">
-        <v>238.51</v>
+        <v>188.64</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-90.12</v>
+        <v>-62.88</v>
       </c>
       <c r="K23" t="n">
-        <v>243.01</v>
+        <v>169.56</v>
       </c>
       <c r="L23" t="n">
-        <v>259.19</v>
+        <v>180.84</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-337.93</v>
+        <v>-242.7</v>
       </c>
       <c r="K24" t="n">
-        <v>153.06</v>
+        <v>109.92</v>
       </c>
       <c r="L24" t="n">
-        <v>370.98</v>
+        <v>266.43</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-401.12</v>
+        <v>-255.21</v>
       </c>
       <c r="K25" t="n">
-        <v>88.55</v>
+        <v>56.34</v>
       </c>
       <c r="L25" t="n">
-        <v>410.77</v>
+        <v>261.36</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-540.4400000000001</v>
+        <v>-342.58</v>
       </c>
       <c r="K26" t="n">
-        <v>-39.82</v>
+        <v>-25.24</v>
       </c>
       <c r="L26" t="n">
-        <v>541.9</v>
+        <v>343.51</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>330.46</v>
+        <v>207.86</v>
       </c>
       <c r="K27" t="n">
-        <v>-489.93</v>
+        <v>-308.16</v>
       </c>
       <c r="L27" t="n">
-        <v>590.96</v>
+        <v>371.71</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-557.02</v>
+        <v>-347.08</v>
       </c>
       <c r="K28" t="n">
-        <v>230.32</v>
+        <v>143.51</v>
       </c>
       <c r="L28" t="n">
-        <v>602.76</v>
+        <v>375.58</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>54.77</v>
+        <v>57.69</v>
       </c>
       <c r="K29" t="n">
-        <v>-41.04</v>
+        <v>-43.23</v>
       </c>
       <c r="L29" t="n">
-        <v>68.44</v>
+        <v>72.09</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.91</v>
+        <v>-6.43</v>
       </c>
       <c r="K30" t="n">
-        <v>-120.11</v>
+        <v>-111.79</v>
       </c>
       <c r="L30" t="n">
-        <v>120.31</v>
+        <v>111.97</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-79.41</v>
+        <v>-72.73</v>
       </c>
       <c r="K31" t="n">
-        <v>-41.1</v>
+        <v>-37.65</v>
       </c>
       <c r="L31" t="n">
-        <v>89.41</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-31.18</v>
+        <v>-25.67</v>
       </c>
       <c r="K32" t="n">
-        <v>140.17</v>
+        <v>115.38</v>
       </c>
       <c r="L32" t="n">
-        <v>143.6</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>75.48</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-119.89</v>
+        <v>-109.84</v>
       </c>
       <c r="L33" t="n">
-        <v>141.67</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-236.14</v>
+        <v>-192.98</v>
       </c>
       <c r="K34" t="n">
-        <v>188.69</v>
+        <v>154.2</v>
       </c>
       <c r="L34" t="n">
-        <v>302.26</v>
+        <v>247.03</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-170.18</v>
+        <v>-136</v>
       </c>
       <c r="K35" t="n">
-        <v>-200.42</v>
+        <v>-160.17</v>
       </c>
       <c r="L35" t="n">
-        <v>262.92</v>
+        <v>210.12</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-117.9</v>
+        <v>-90.79000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-138.03</v>
+        <v>-106.29</v>
       </c>
       <c r="L36" t="n">
-        <v>181.53</v>
+        <v>139.78</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-198.25</v>
+        <v>-140.67</v>
       </c>
       <c r="K37" t="n">
-        <v>-129.69</v>
+        <v>-92.02</v>
       </c>
       <c r="L37" t="n">
-        <v>236.9</v>
+        <v>168.1</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>31</v>
       </c>
       <c r="J38" t="n">
-        <v>-256.57</v>
+        <v>-201.46</v>
       </c>
       <c r="K38" t="n">
-        <v>-53.27</v>
+        <v>-41.83</v>
       </c>
       <c r="L38" t="n">
-        <v>262.04</v>
+        <v>205.76</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-198.69</v>
+        <v>-137.92</v>
       </c>
       <c r="K39" t="n">
-        <v>-124.52</v>
+        <v>-86.44</v>
       </c>
       <c r="L39" t="n">
-        <v>234.49</v>
+        <v>162.77</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>248.16</v>
+        <v>173.75</v>
       </c>
       <c r="K40" t="n">
-        <v>214.21</v>
+        <v>149.98</v>
       </c>
       <c r="L40" t="n">
-        <v>327.83</v>
+        <v>229.53</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>-50.53</v>
+        <v>-32.79</v>
       </c>
       <c r="K41" t="n">
-        <v>-429.54</v>
+        <v>-278.74</v>
       </c>
       <c r="L41" t="n">
-        <v>432.5</v>
+        <v>280.67</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-36.34</v>
+        <v>-21.78</v>
       </c>
       <c r="K42" t="n">
-        <v>420.18</v>
+        <v>251.75</v>
       </c>
       <c r="L42" t="n">
-        <v>421.74</v>
+        <v>252.69</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-415.83</v>
+        <v>-291.3</v>
       </c>
       <c r="K43" t="n">
-        <v>-23.05</v>
+        <v>-16.15</v>
       </c>
       <c r="L43" t="n">
-        <v>416.47</v>
+        <v>291.75</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>52.55</v>
+        <v>43.8</v>
       </c>
       <c r="K44" t="n">
-        <v>-120.11</v>
+        <v>-100.13</v>
       </c>
       <c r="L44" t="n">
-        <v>131.1</v>
+        <v>109.29</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>181.73</v>
+        <v>163.35</v>
       </c>
       <c r="K45" t="n">
-        <v>118.18</v>
+        <v>106.23</v>
       </c>
       <c r="L45" t="n">
-        <v>216.78</v>
+        <v>194.85</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>30.16</v>
+        <v>31.65</v>
       </c>
       <c r="K46" t="n">
-        <v>-67.95</v>
+        <v>-71.33</v>
       </c>
       <c r="L46" t="n">
-        <v>74.34</v>
+        <v>78.03</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>94.65000000000001</v>
+        <v>93.87</v>
       </c>
       <c r="K47" t="n">
-        <v>-135.45</v>
+        <v>-134.33</v>
       </c>
       <c r="L47" t="n">
-        <v>165.24</v>
+        <v>163.87</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-145.17</v>
+        <v>-143.25</v>
       </c>
       <c r="K48" t="n">
-        <v>-20.27</v>
+        <v>-20.01</v>
       </c>
       <c r="L48" t="n">
-        <v>146.58</v>
+        <v>144.64</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-127.38</v>
+        <v>-110.26</v>
       </c>
       <c r="K49" t="n">
-        <v>25.78</v>
+        <v>22.32</v>
       </c>
       <c r="L49" t="n">
-        <v>129.97</v>
+        <v>112.49</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-156.41</v>
+        <v>-121.54</v>
       </c>
       <c r="K50" t="n">
-        <v>-132.22</v>
+        <v>-102.75</v>
       </c>
       <c r="L50" t="n">
-        <v>204.81</v>
+        <v>159.15</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>181.3</v>
+        <v>152.29</v>
       </c>
       <c r="K51" t="n">
-        <v>-133.29</v>
+        <v>-111.96</v>
       </c>
       <c r="L51" t="n">
-        <v>225.02</v>
+        <v>189.02</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-22.3</v>
+        <v>-15.47</v>
       </c>
       <c r="K52" t="n">
-        <v>284.29</v>
+        <v>197.13</v>
       </c>
       <c r="L52" t="n">
-        <v>285.16</v>
+        <v>197.74</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-184.91</v>
+        <v>-128.36</v>
       </c>
       <c r="K53" t="n">
-        <v>-48.12</v>
+        <v>-33.4</v>
       </c>
       <c r="L53" t="n">
-        <v>191.07</v>
+        <v>132.63</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>227.47</v>
+        <v>168.17</v>
       </c>
       <c r="K54" t="n">
-        <v>318.17</v>
+        <v>235.22</v>
       </c>
       <c r="L54" t="n">
-        <v>391.12</v>
+        <v>289.16</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>329.09</v>
+        <v>220.51</v>
       </c>
       <c r="K55" t="n">
-        <v>-162.53</v>
+        <v>-108.9</v>
       </c>
       <c r="L55" t="n">
-        <v>367.03</v>
+        <v>245.93</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-306</v>
+        <v>-200.13</v>
       </c>
       <c r="K56" t="n">
-        <v>282.69</v>
+        <v>184.89</v>
       </c>
       <c r="L56" t="n">
-        <v>416.59</v>
+        <v>272.47</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-142.15</v>
+        <v>-104.55</v>
       </c>
       <c r="K57" t="n">
-        <v>249.09</v>
+        <v>183.21</v>
       </c>
       <c r="L57" t="n">
-        <v>286.79</v>
+        <v>210.94</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>549.42</v>
+        <v>313.55</v>
       </c>
       <c r="K58" t="n">
-        <v>379.87</v>
+        <v>216.79</v>
       </c>
       <c r="L58" t="n">
-        <v>667.95</v>
+        <v>381.2</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>29</v>
       </c>
       <c r="J59" t="n">
-        <v>85.48</v>
+        <v>89.47</v>
       </c>
       <c r="K59" t="n">
-        <v>-66.06999999999999</v>
+        <v>-69.16</v>
       </c>
       <c r="L59" t="n">
-        <v>108.04</v>
+        <v>113.08</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-93.06999999999999</v>
+        <v>-95.84</v>
       </c>
       <c r="K60" t="n">
-        <v>-148.92</v>
+        <v>-153.35</v>
       </c>
       <c r="L60" t="n">
-        <v>175.62</v>
+        <v>180.84</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-114.05</v>
+        <v>-96.98</v>
       </c>
       <c r="K61" t="n">
-        <v>105.93</v>
+        <v>90.08</v>
       </c>
       <c r="L61" t="n">
-        <v>155.65</v>
+        <v>132.36</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>191.98</v>
+        <v>172.03</v>
       </c>
       <c r="K62" t="n">
-        <v>19.58</v>
+        <v>17.55</v>
       </c>
       <c r="L62" t="n">
-        <v>192.98</v>
+        <v>172.92</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-200.87</v>
+        <v>-168.51</v>
       </c>
       <c r="K63" t="n">
-        <v>-31.5</v>
+        <v>-26.42</v>
       </c>
       <c r="L63" t="n">
-        <v>203.33</v>
+        <v>170.57</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>156.31</v>
+        <v>132.37</v>
       </c>
       <c r="K64" t="n">
-        <v>43.59</v>
+        <v>36.92</v>
       </c>
       <c r="L64" t="n">
-        <v>162.28</v>
+        <v>137.42</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>385.25</v>
+        <v>259.26</v>
       </c>
       <c r="K65" t="n">
-        <v>32.82</v>
+        <v>22.09</v>
       </c>
       <c r="L65" t="n">
-        <v>386.64</v>
+        <v>260.2</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>133.86</v>
+        <v>103.31</v>
       </c>
       <c r="K66" t="n">
-        <v>-78.27</v>
+        <v>-60.41</v>
       </c>
       <c r="L66" t="n">
-        <v>155.06</v>
+        <v>119.68</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-64.73999999999999</v>
+        <v>-45.2</v>
       </c>
       <c r="K67" t="n">
-        <v>263.42</v>
+        <v>183.9</v>
       </c>
       <c r="L67" t="n">
-        <v>271.26</v>
+        <v>189.37</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-19.54</v>
+        <v>-12.04</v>
       </c>
       <c r="K68" t="n">
-        <v>-282.62</v>
+        <v>-174.06</v>
       </c>
       <c r="L68" t="n">
-        <v>283.29</v>
+        <v>174.48</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-240.39</v>
+        <v>-157.21</v>
       </c>
       <c r="K69" t="n">
-        <v>114.92</v>
+        <v>75.16</v>
       </c>
       <c r="L69" t="n">
-        <v>266.45</v>
+        <v>174.25</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-139.68</v>
+        <v>-100.86</v>
       </c>
       <c r="K70" t="n">
-        <v>-245.08</v>
+        <v>-176.97</v>
       </c>
       <c r="L70" t="n">
-        <v>282.09</v>
+        <v>203.7</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>268.3</v>
+        <v>193.78</v>
       </c>
       <c r="K71" t="n">
-        <v>72.09999999999999</v>
+        <v>52.07</v>
       </c>
       <c r="L71" t="n">
-        <v>277.82</v>
+        <v>200.65</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-525.4</v>
+        <v>-305.85</v>
       </c>
       <c r="K72" t="n">
-        <v>-353.81</v>
+        <v>-205.96</v>
       </c>
       <c r="L72" t="n">
-        <v>633.42</v>
+        <v>368.73</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-342.56</v>
+        <v>-233.5</v>
       </c>
       <c r="K73" t="n">
-        <v>-76.8</v>
+        <v>-52.35</v>
       </c>
       <c r="L73" t="n">
-        <v>351.06</v>
+        <v>239.29</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>-128.34</v>
+        <v>-127.88</v>
       </c>
       <c r="K74" t="n">
-        <v>-79.29000000000001</v>
+        <v>-79.01000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>150.86</v>
+        <v>150.32</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>89.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-12.42</v>
+        <v>-10.72</v>
       </c>
       <c r="L75" t="n">
-        <v>90.56</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>66.11</v>
+        <v>59.5</v>
       </c>
       <c r="K76" t="n">
-        <v>-63.47</v>
+        <v>-57.13</v>
       </c>
       <c r="L76" t="n">
-        <v>91.64</v>
+        <v>82.48999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>144.25</v>
+        <v>118.05</v>
       </c>
       <c r="K77" t="n">
-        <v>51.86</v>
+        <v>42.44</v>
       </c>
       <c r="L77" t="n">
-        <v>153.28</v>
+        <v>125.45</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-75.95</v>
+        <v>-59.88</v>
       </c>
       <c r="K78" t="n">
-        <v>242.58</v>
+        <v>191.27</v>
       </c>
       <c r="L78" t="n">
-        <v>254.19</v>
+        <v>200.42</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>62.62</v>
+        <v>56.92</v>
       </c>
       <c r="K79" t="n">
-        <v>-89.05</v>
+        <v>-80.95</v>
       </c>
       <c r="L79" t="n">
-        <v>108.86</v>
+        <v>98.95999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-247.21</v>
+        <v>-206.2</v>
       </c>
       <c r="K80" t="n">
-        <v>142.46</v>
+        <v>118.82</v>
       </c>
       <c r="L80" t="n">
-        <v>285.32</v>
+        <v>237.99</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-270.44</v>
+        <v>-241.58</v>
       </c>
       <c r="K81" t="n">
-        <v>-121.01</v>
+        <v>-108.09</v>
       </c>
       <c r="L81" t="n">
-        <v>296.28</v>
+        <v>264.66</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>-69.48</v>
+        <v>-55.73</v>
       </c>
       <c r="K82" t="n">
-        <v>314.98</v>
+        <v>252.67</v>
       </c>
       <c r="L82" t="n">
-        <v>322.55</v>
+        <v>258.74</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-188.62</v>
+        <v>-120.54</v>
       </c>
       <c r="K83" t="n">
-        <v>-365.28</v>
+        <v>-233.45</v>
       </c>
       <c r="L83" t="n">
-        <v>411.11</v>
+        <v>262.73</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>518.92</v>
+        <v>350.51</v>
       </c>
       <c r="K84" t="n">
-        <v>326.9</v>
+        <v>220.81</v>
       </c>
       <c r="L84" t="n">
-        <v>613.3</v>
+        <v>414.26</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-336.96</v>
+        <v>-204.16</v>
       </c>
       <c r="K85" t="n">
-        <v>247.3</v>
+        <v>149.84</v>
       </c>
       <c r="L85" t="n">
-        <v>417.97</v>
+        <v>253.25</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-522.3</v>
+        <v>-311.46</v>
       </c>
       <c r="K86" t="n">
-        <v>-314.62</v>
+        <v>-187.61</v>
       </c>
       <c r="L86" t="n">
-        <v>609.74</v>
+        <v>363.6</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>455.77</v>
+        <v>268.29</v>
       </c>
       <c r="K87" t="n">
-        <v>484.88</v>
+        <v>285.43</v>
       </c>
       <c r="L87" t="n">
-        <v>665.46</v>
+        <v>391.72</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>556.54</v>
+        <v>342.75</v>
       </c>
       <c r="K88" t="n">
-        <v>-499.59</v>
+        <v>-307.67</v>
       </c>
       <c r="L88" t="n">
-        <v>747.88</v>
+        <v>460.58</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>5.01</v>
+        <v>4.67</v>
       </c>
       <c r="K14" t="n">
-        <v>-119.07</v>
+        <v>-110.97</v>
       </c>
       <c r="L14" t="n">
-        <v>119.18</v>
+        <v>111.07</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>63.61</v>
+        <v>58.68</v>
       </c>
       <c r="K15" t="n">
-        <v>16.48</v>
+        <v>15.2</v>
       </c>
       <c r="L15" t="n">
-        <v>65.70999999999999</v>
+        <v>60.62</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-98.20999999999999</v>
+        <v>-92.45</v>
       </c>
       <c r="K16" t="n">
-        <v>-100.14</v>
+        <v>-94.27</v>
       </c>
       <c r="L16" t="n">
-        <v>140.26</v>
+        <v>132.04</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-64.87</v>
+        <v>-63.38</v>
       </c>
       <c r="K17" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="L17" t="n">
-        <v>64.89</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-123.11</v>
+        <v>-115.92</v>
       </c>
       <c r="K18" t="n">
-        <v>-96.68000000000001</v>
+        <v>-91.03</v>
       </c>
       <c r="L18" t="n">
-        <v>156.53</v>
+        <v>147.4</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>255.02</v>
+        <v>250.02</v>
       </c>
       <c r="K19" t="n">
-        <v>-179.07</v>
+        <v>-175.56</v>
       </c>
       <c r="L19" t="n">
-        <v>311.61</v>
+        <v>305.5</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-149.41</v>
+        <v>-151.12</v>
       </c>
       <c r="K20" t="n">
-        <v>132.52</v>
+        <v>134.04</v>
       </c>
       <c r="L20" t="n">
-        <v>199.72</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>137.47</v>
+        <v>135.25</v>
       </c>
       <c r="K21" t="n">
-        <v>-85.05</v>
+        <v>-83.68000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>161.65</v>
+        <v>159.05</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-12.47</v>
+        <v>-12.63</v>
       </c>
       <c r="K22" t="n">
-        <v>188.23</v>
+        <v>190.61</v>
       </c>
       <c r="L22" t="n">
-        <v>188.64</v>
+        <v>191.03</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-62.88</v>
+        <v>-64.25</v>
       </c>
       <c r="K23" t="n">
-        <v>169.56</v>
+        <v>173.25</v>
       </c>
       <c r="L23" t="n">
-        <v>180.84</v>
+        <v>184.78</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-242.7</v>
+        <v>-252.05</v>
       </c>
       <c r="K24" t="n">
-        <v>109.92</v>
+        <v>114.16</v>
       </c>
       <c r="L24" t="n">
-        <v>266.43</v>
+        <v>276.7</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-255.21</v>
+        <v>-262.11</v>
       </c>
       <c r="K25" t="n">
-        <v>56.34</v>
+        <v>57.86</v>
       </c>
       <c r="L25" t="n">
-        <v>261.36</v>
+        <v>268.42</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-342.58</v>
+        <v>-356.73</v>
       </c>
       <c r="K26" t="n">
-        <v>-25.24</v>
+        <v>-26.28</v>
       </c>
       <c r="L26" t="n">
-        <v>343.51</v>
+        <v>357.69</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>207.86</v>
+        <v>216.43</v>
       </c>
       <c r="K27" t="n">
-        <v>-308.16</v>
+        <v>-320.86</v>
       </c>
       <c r="L27" t="n">
-        <v>371.71</v>
+        <v>387.03</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-347.08</v>
+        <v>-360.47</v>
       </c>
       <c r="K28" t="n">
-        <v>143.51</v>
+        <v>149.05</v>
       </c>
       <c r="L28" t="n">
-        <v>375.58</v>
+        <v>390.06</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>57.69</v>
+        <v>52.49</v>
       </c>
       <c r="K29" t="n">
-        <v>-43.23</v>
+        <v>-39.33</v>
       </c>
       <c r="L29" t="n">
-        <v>72.09</v>
+        <v>65.59</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.43</v>
+        <v>-6.05</v>
       </c>
       <c r="K30" t="n">
-        <v>-111.79</v>
+        <v>-105.18</v>
       </c>
       <c r="L30" t="n">
-        <v>111.97</v>
+        <v>105.35</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-72.73</v>
+        <v>-68.93000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-37.65</v>
+        <v>-35.68</v>
       </c>
       <c r="L31" t="n">
-        <v>81.90000000000001</v>
+        <v>77.62</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-25.67</v>
+        <v>-25.27</v>
       </c>
       <c r="K32" t="n">
-        <v>115.38</v>
+        <v>113.6</v>
       </c>
       <c r="L32" t="n">
-        <v>118.2</v>
+        <v>116.37</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>69.15000000000001</v>
+        <v>67.41</v>
       </c>
       <c r="K33" t="n">
-        <v>-109.84</v>
+        <v>-107.06</v>
       </c>
       <c r="L33" t="n">
-        <v>129.8</v>
+        <v>126.51</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-192.98</v>
+        <v>-188.88</v>
       </c>
       <c r="K34" t="n">
-        <v>154.2</v>
+        <v>150.93</v>
       </c>
       <c r="L34" t="n">
-        <v>247.03</v>
+        <v>241.78</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-136</v>
+        <v>-135.9</v>
       </c>
       <c r="K35" t="n">
-        <v>-160.17</v>
+        <v>-160.05</v>
       </c>
       <c r="L35" t="n">
-        <v>210.12</v>
+        <v>209.96</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-90.79000000000001</v>
+        <v>-92.08</v>
       </c>
       <c r="K36" t="n">
-        <v>-106.29</v>
+        <v>-107.8</v>
       </c>
       <c r="L36" t="n">
-        <v>139.78</v>
+        <v>141.78</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-140.67</v>
+        <v>-142.1</v>
       </c>
       <c r="K37" t="n">
-        <v>-92.02</v>
+        <v>-92.95999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>168.1</v>
+        <v>169.8</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>31</v>
       </c>
       <c r="J38" t="n">
-        <v>-201.46</v>
+        <v>-203.45</v>
       </c>
       <c r="K38" t="n">
-        <v>-41.83</v>
+        <v>-42.24</v>
       </c>
       <c r="L38" t="n">
-        <v>205.76</v>
+        <v>207.79</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-137.92</v>
+        <v>-141.65</v>
       </c>
       <c r="K39" t="n">
-        <v>-86.44</v>
+        <v>-88.78</v>
       </c>
       <c r="L39" t="n">
-        <v>162.77</v>
+        <v>167.17</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>173.75</v>
+        <v>178.6</v>
       </c>
       <c r="K40" t="n">
-        <v>149.98</v>
+        <v>154.17</v>
       </c>
       <c r="L40" t="n">
-        <v>229.53</v>
+        <v>235.94</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>-32.79</v>
+        <v>-34.05</v>
       </c>
       <c r="K41" t="n">
-        <v>-278.74</v>
+        <v>-289.42</v>
       </c>
       <c r="L41" t="n">
-        <v>280.67</v>
+        <v>291.42</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-21.78</v>
+        <v>-23.13</v>
       </c>
       <c r="K42" t="n">
-        <v>251.75</v>
+        <v>267.43</v>
       </c>
       <c r="L42" t="n">
-        <v>252.69</v>
+        <v>268.43</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-291.3</v>
+        <v>-295.11</v>
       </c>
       <c r="K43" t="n">
-        <v>-16.15</v>
+        <v>-16.36</v>
       </c>
       <c r="L43" t="n">
-        <v>291.75</v>
+        <v>295.56</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>43.8</v>
+        <v>41.45</v>
       </c>
       <c r="K44" t="n">
-        <v>-100.13</v>
+        <v>-94.73999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>109.29</v>
+        <v>103.41</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>163.35</v>
+        <v>153.68</v>
       </c>
       <c r="K45" t="n">
-        <v>106.23</v>
+        <v>99.94</v>
       </c>
       <c r="L45" t="n">
-        <v>194.85</v>
+        <v>183.32</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>31.65</v>
+        <v>29.14</v>
       </c>
       <c r="K46" t="n">
-        <v>-71.33</v>
+        <v>-65.67</v>
       </c>
       <c r="L46" t="n">
-        <v>78.03</v>
+        <v>71.84999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>93.87</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-134.33</v>
+        <v>-129.45</v>
       </c>
       <c r="L47" t="n">
-        <v>163.87</v>
+        <v>157.92</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-143.25</v>
+        <v>-139.3</v>
       </c>
       <c r="K48" t="n">
-        <v>-20.01</v>
+        <v>-19.45</v>
       </c>
       <c r="L48" t="n">
-        <v>144.64</v>
+        <v>140.65</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-110.26</v>
+        <v>-108.33</v>
       </c>
       <c r="K49" t="n">
-        <v>22.32</v>
+        <v>21.93</v>
       </c>
       <c r="L49" t="n">
-        <v>112.49</v>
+        <v>110.52</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-121.54</v>
+        <v>-120.86</v>
       </c>
       <c r="K50" t="n">
-        <v>-102.75</v>
+        <v>-102.18</v>
       </c>
       <c r="L50" t="n">
-        <v>159.15</v>
+        <v>158.27</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>152.29</v>
+        <v>151.7</v>
       </c>
       <c r="K51" t="n">
-        <v>-111.96</v>
+        <v>-111.53</v>
       </c>
       <c r="L51" t="n">
-        <v>189.02</v>
+        <v>188.29</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-15.47</v>
+        <v>-15.7</v>
       </c>
       <c r="K52" t="n">
-        <v>197.13</v>
+        <v>200.14</v>
       </c>
       <c r="L52" t="n">
-        <v>197.74</v>
+        <v>200.75</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-128.36</v>
+        <v>-132.15</v>
       </c>
       <c r="K53" t="n">
-        <v>-33.4</v>
+        <v>-34.39</v>
       </c>
       <c r="L53" t="n">
-        <v>132.63</v>
+        <v>136.55</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>168.17</v>
+        <v>171.04</v>
       </c>
       <c r="K54" t="n">
-        <v>235.22</v>
+        <v>239.23</v>
       </c>
       <c r="L54" t="n">
-        <v>289.16</v>
+        <v>294.09</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>220.51</v>
+        <v>228.96</v>
       </c>
       <c r="K55" t="n">
-        <v>-108.9</v>
+        <v>-113.08</v>
       </c>
       <c r="L55" t="n">
-        <v>245.93</v>
+        <v>255.37</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-200.13</v>
+        <v>-205.38</v>
       </c>
       <c r="K56" t="n">
-        <v>184.89</v>
+        <v>189.74</v>
       </c>
       <c r="L56" t="n">
-        <v>272.47</v>
+        <v>279.61</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-104.55</v>
+        <v>-105.67</v>
       </c>
       <c r="K57" t="n">
-        <v>183.21</v>
+        <v>185.17</v>
       </c>
       <c r="L57" t="n">
-        <v>210.94</v>
+        <v>213.2</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>313.55</v>
+        <v>337.56</v>
       </c>
       <c r="K58" t="n">
-        <v>216.79</v>
+        <v>233.39</v>
       </c>
       <c r="L58" t="n">
-        <v>381.2</v>
+        <v>410.38</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>29</v>
       </c>
       <c r="J59" t="n">
-        <v>89.47</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-69.16</v>
+        <v>-64.34</v>
       </c>
       <c r="L59" t="n">
-        <v>113.08</v>
+        <v>105.21</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-95.84</v>
+        <v>-88.36</v>
       </c>
       <c r="K60" t="n">
-        <v>-153.35</v>
+        <v>-141.39</v>
       </c>
       <c r="L60" t="n">
-        <v>180.84</v>
+        <v>166.73</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-96.98</v>
+        <v>-91.65000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>90.08</v>
+        <v>85.12</v>
       </c>
       <c r="L61" t="n">
-        <v>132.36</v>
+        <v>125.08</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>172.03</v>
+        <v>165.25</v>
       </c>
       <c r="K62" t="n">
-        <v>17.55</v>
+        <v>16.86</v>
       </c>
       <c r="L62" t="n">
-        <v>172.92</v>
+        <v>166.11</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-168.51</v>
+        <v>-164.7</v>
       </c>
       <c r="K63" t="n">
-        <v>-26.42</v>
+        <v>-25.82</v>
       </c>
       <c r="L63" t="n">
-        <v>170.57</v>
+        <v>166.71</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>132.37</v>
+        <v>129.8</v>
       </c>
       <c r="K64" t="n">
-        <v>36.92</v>
+        <v>36.2</v>
       </c>
       <c r="L64" t="n">
-        <v>137.42</v>
+        <v>134.75</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>259.26</v>
+        <v>260.72</v>
       </c>
       <c r="K65" t="n">
-        <v>22.09</v>
+        <v>22.21</v>
       </c>
       <c r="L65" t="n">
-        <v>260.2</v>
+        <v>261.66</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>103.31</v>
+        <v>104.08</v>
       </c>
       <c r="K66" t="n">
-        <v>-60.41</v>
+        <v>-60.86</v>
       </c>
       <c r="L66" t="n">
-        <v>119.68</v>
+        <v>120.57</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-45.2</v>
+        <v>-45.66</v>
       </c>
       <c r="K67" t="n">
-        <v>183.9</v>
+        <v>185.79</v>
       </c>
       <c r="L67" t="n">
-        <v>189.37</v>
+        <v>191.32</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-12.04</v>
+        <v>-12.44</v>
       </c>
       <c r="K68" t="n">
-        <v>-174.06</v>
+        <v>-179.92</v>
       </c>
       <c r="L68" t="n">
-        <v>174.48</v>
+        <v>180.35</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-157.21</v>
+        <v>-161.01</v>
       </c>
       <c r="K69" t="n">
-        <v>75.16</v>
+        <v>76.97</v>
       </c>
       <c r="L69" t="n">
-        <v>174.25</v>
+        <v>178.46</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-100.86</v>
+        <v>-101.56</v>
       </c>
       <c r="K70" t="n">
-        <v>-176.97</v>
+        <v>-178.2</v>
       </c>
       <c r="L70" t="n">
-        <v>203.7</v>
+        <v>205.11</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>193.78</v>
+        <v>201.2</v>
       </c>
       <c r="K71" t="n">
-        <v>52.07</v>
+        <v>54.07</v>
       </c>
       <c r="L71" t="n">
-        <v>200.65</v>
+        <v>208.34</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-305.85</v>
+        <v>-320.99</v>
       </c>
       <c r="K72" t="n">
-        <v>-205.96</v>
+        <v>-216.15</v>
       </c>
       <c r="L72" t="n">
-        <v>368.73</v>
+        <v>386.98</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-233.5</v>
+        <v>-241.19</v>
       </c>
       <c r="K73" t="n">
-        <v>-52.35</v>
+        <v>-54.08</v>
       </c>
       <c r="L73" t="n">
-        <v>239.29</v>
+        <v>247.18</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>-127.88</v>
+        <v>-119.75</v>
       </c>
       <c r="K74" t="n">
-        <v>-79.01000000000001</v>
+        <v>-73.98999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>150.32</v>
+        <v>140.76</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>77.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="K75" t="n">
-        <v>-10.72</v>
+        <v>-10.21</v>
       </c>
       <c r="L75" t="n">
-        <v>78.14</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>59.5</v>
+        <v>56.06</v>
       </c>
       <c r="K76" t="n">
-        <v>-57.13</v>
+        <v>-53.82</v>
       </c>
       <c r="L76" t="n">
-        <v>82.48999999999999</v>
+        <v>77.70999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>118.05</v>
+        <v>115.59</v>
       </c>
       <c r="K77" t="n">
-        <v>42.44</v>
+        <v>41.55</v>
       </c>
       <c r="L77" t="n">
-        <v>125.45</v>
+        <v>122.83</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-59.88</v>
+        <v>-58.7</v>
       </c>
       <c r="K78" t="n">
-        <v>191.27</v>
+        <v>187.48</v>
       </c>
       <c r="L78" t="n">
-        <v>200.42</v>
+        <v>196.45</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>56.92</v>
+        <v>55.01</v>
       </c>
       <c r="K79" t="n">
-        <v>-80.95</v>
+        <v>-78.23</v>
       </c>
       <c r="L79" t="n">
-        <v>98.95999999999999</v>
+        <v>95.64</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-206.2</v>
+        <v>-205.67</v>
       </c>
       <c r="K80" t="n">
-        <v>118.82</v>
+        <v>118.52</v>
       </c>
       <c r="L80" t="n">
-        <v>237.99</v>
+        <v>237.37</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-241.58</v>
+        <v>-239.05</v>
       </c>
       <c r="K81" t="n">
-        <v>-108.09</v>
+        <v>-106.96</v>
       </c>
       <c r="L81" t="n">
-        <v>264.66</v>
+        <v>261.89</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>-55.73</v>
+        <v>-55.44</v>
       </c>
       <c r="K82" t="n">
-        <v>252.67</v>
+        <v>251.35</v>
       </c>
       <c r="L82" t="n">
-        <v>258.74</v>
+        <v>257.4</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-120.54</v>
+        <v>-124.61</v>
       </c>
       <c r="K83" t="n">
-        <v>-233.45</v>
+        <v>-241.32</v>
       </c>
       <c r="L83" t="n">
-        <v>262.73</v>
+        <v>271.59</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>350.51</v>
+        <v>355.59</v>
       </c>
       <c r="K84" t="n">
-        <v>220.81</v>
+        <v>224.01</v>
       </c>
       <c r="L84" t="n">
-        <v>414.26</v>
+        <v>420.27</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-204.16</v>
+        <v>-212.89</v>
       </c>
       <c r="K85" t="n">
-        <v>149.84</v>
+        <v>156.24</v>
       </c>
       <c r="L85" t="n">
-        <v>253.25</v>
+        <v>264.07</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-311.46</v>
+        <v>-326.15</v>
       </c>
       <c r="K86" t="n">
-        <v>-187.61</v>
+        <v>-196.46</v>
       </c>
       <c r="L86" t="n">
-        <v>363.6</v>
+        <v>380.75</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>268.29</v>
+        <v>283.37</v>
       </c>
       <c r="K87" t="n">
-        <v>285.43</v>
+        <v>301.47</v>
       </c>
       <c r="L87" t="n">
-        <v>391.72</v>
+        <v>413.74</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>342.75</v>
+        <v>353.5</v>
       </c>
       <c r="K88" t="n">
-        <v>-307.67</v>
+        <v>-317.32</v>
       </c>
       <c r="L88" t="n">
-        <v>460.58</v>
+        <v>475.04</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>4.67</v>
+        <v>2.11</v>
       </c>
       <c r="K14" t="n">
-        <v>-110.97</v>
+        <v>-50.22</v>
       </c>
       <c r="L14" t="n">
-        <v>111.07</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>58.68</v>
+        <v>32.36</v>
       </c>
       <c r="K15" t="n">
-        <v>15.2</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>60.62</v>
+        <v>33.43</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-92.45</v>
+        <v>-52.28</v>
       </c>
       <c r="K16" t="n">
-        <v>-94.27</v>
+        <v>-53.31</v>
       </c>
       <c r="L16" t="n">
-        <v>132.04</v>
+        <v>74.67</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-63.38</v>
+        <v>-38.03</v>
       </c>
       <c r="K17" t="n">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="L17" t="n">
-        <v>63.4</v>
+        <v>38.04</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-115.92</v>
+        <v>-72.39</v>
       </c>
       <c r="K18" t="n">
-        <v>-91.03</v>
+        <v>-56.85</v>
       </c>
       <c r="L18" t="n">
-        <v>147.4</v>
+        <v>92.04000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>250.02</v>
+        <v>136.38</v>
       </c>
       <c r="K19" t="n">
-        <v>-175.56</v>
+        <v>-95.77</v>
       </c>
       <c r="L19" t="n">
-        <v>305.5</v>
+        <v>166.65</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-151.12</v>
+        <v>-78.53</v>
       </c>
       <c r="K20" t="n">
-        <v>134.04</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>202</v>
+        <v>104.97</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>135.25</v>
+        <v>80.92</v>
       </c>
       <c r="K21" t="n">
-        <v>-83.68000000000001</v>
+        <v>-50.07</v>
       </c>
       <c r="L21" t="n">
-        <v>159.05</v>
+        <v>95.16</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-12.63</v>
+        <v>-6.87</v>
       </c>
       <c r="K22" t="n">
-        <v>190.61</v>
+        <v>103.61</v>
       </c>
       <c r="L22" t="n">
-        <v>191.03</v>
+        <v>103.84</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-64.25</v>
+        <v>-38.33</v>
       </c>
       <c r="K23" t="n">
-        <v>173.25</v>
+        <v>103.36</v>
       </c>
       <c r="L23" t="n">
-        <v>184.78</v>
+        <v>110.23</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-252.05</v>
+        <v>-170.82</v>
       </c>
       <c r="K24" t="n">
-        <v>114.16</v>
+        <v>77.37</v>
       </c>
       <c r="L24" t="n">
-        <v>276.7</v>
+        <v>187.52</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-262.11</v>
+        <v>-154.58</v>
       </c>
       <c r="K25" t="n">
-        <v>57.86</v>
+        <v>34.12</v>
       </c>
       <c r="L25" t="n">
-        <v>268.42</v>
+        <v>158.3</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-356.73</v>
+        <v>-209.53</v>
       </c>
       <c r="K26" t="n">
-        <v>-26.28</v>
+        <v>-15.44</v>
       </c>
       <c r="L26" t="n">
-        <v>357.69</v>
+        <v>210.1</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>216.43</v>
+        <v>124.15</v>
       </c>
       <c r="K27" t="n">
-        <v>-320.86</v>
+        <v>-184.06</v>
       </c>
       <c r="L27" t="n">
-        <v>387.03</v>
+        <v>222.02</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-360.47</v>
+        <v>-202.84</v>
       </c>
       <c r="K28" t="n">
-        <v>149.05</v>
+        <v>83.87</v>
       </c>
       <c r="L28" t="n">
-        <v>390.06</v>
+        <v>219.49</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>52.49</v>
+        <v>29.19</v>
       </c>
       <c r="K29" t="n">
-        <v>-39.33</v>
+        <v>-21.87</v>
       </c>
       <c r="L29" t="n">
-        <v>65.59</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.05</v>
+        <v>-3.48</v>
       </c>
       <c r="K30" t="n">
-        <v>-105.18</v>
+        <v>-60.44</v>
       </c>
       <c r="L30" t="n">
-        <v>105.35</v>
+        <v>60.54</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-68.93000000000001</v>
+        <v>-41.05</v>
       </c>
       <c r="K31" t="n">
-        <v>-35.68</v>
+        <v>-21.25</v>
       </c>
       <c r="L31" t="n">
-        <v>77.62</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-25.27</v>
+        <v>-14.97</v>
       </c>
       <c r="K32" t="n">
-        <v>113.6</v>
+        <v>67.31</v>
       </c>
       <c r="L32" t="n">
-        <v>116.37</v>
+        <v>68.95</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>67.41</v>
+        <v>38.32</v>
       </c>
       <c r="K33" t="n">
-        <v>-107.06</v>
+        <v>-60.86</v>
       </c>
       <c r="L33" t="n">
-        <v>126.51</v>
+        <v>71.92</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-188.88</v>
+        <v>-110.11</v>
       </c>
       <c r="K34" t="n">
-        <v>150.93</v>
+        <v>87.98</v>
       </c>
       <c r="L34" t="n">
-        <v>241.78</v>
+        <v>140.94</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-135.9</v>
+        <v>-75.84</v>
       </c>
       <c r="K35" t="n">
-        <v>-160.05</v>
+        <v>-89.31999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>209.96</v>
+        <v>117.18</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-92.08</v>
+        <v>-47.1</v>
       </c>
       <c r="K36" t="n">
-        <v>-107.8</v>
+        <v>-55.14</v>
       </c>
       <c r="L36" t="n">
-        <v>141.78</v>
+        <v>72.52</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-142.1</v>
+        <v>-73.06999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-92.95999999999999</v>
+        <v>-47.8</v>
       </c>
       <c r="L37" t="n">
-        <v>169.8</v>
+        <v>87.31999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>31</v>
       </c>
       <c r="J38" t="n">
-        <v>-203.45</v>
+        <v>-107.06</v>
       </c>
       <c r="K38" t="n">
-        <v>-42.24</v>
+        <v>-22.23</v>
       </c>
       <c r="L38" t="n">
-        <v>207.79</v>
+        <v>109.34</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-141.65</v>
+        <v>-83.66</v>
       </c>
       <c r="K39" t="n">
-        <v>-88.78</v>
+        <v>-52.43</v>
       </c>
       <c r="L39" t="n">
-        <v>167.17</v>
+        <v>98.73</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>178.6</v>
+        <v>92.28</v>
       </c>
       <c r="K40" t="n">
-        <v>154.17</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>235.94</v>
+        <v>121.9</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>-34.05</v>
+        <v>-18.96</v>
       </c>
       <c r="K41" t="n">
-        <v>-289.42</v>
+        <v>-161.13</v>
       </c>
       <c r="L41" t="n">
-        <v>291.42</v>
+        <v>162.24</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-23.13</v>
+        <v>-14.78</v>
       </c>
       <c r="K42" t="n">
-        <v>267.43</v>
+        <v>170.91</v>
       </c>
       <c r="L42" t="n">
-        <v>268.43</v>
+        <v>171.55</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-295.11</v>
+        <v>-172.74</v>
       </c>
       <c r="K43" t="n">
-        <v>-16.36</v>
+        <v>-9.57</v>
       </c>
       <c r="L43" t="n">
-        <v>295.56</v>
+        <v>173.01</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>41.45</v>
+        <v>19.93</v>
       </c>
       <c r="K44" t="n">
-        <v>-94.73999999999999</v>
+        <v>-45.55</v>
       </c>
       <c r="L44" t="n">
-        <v>103.41</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>153.68</v>
+        <v>83.83</v>
       </c>
       <c r="K45" t="n">
-        <v>99.94</v>
+        <v>54.51</v>
       </c>
       <c r="L45" t="n">
-        <v>183.32</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>29.14</v>
+        <v>17.39</v>
       </c>
       <c r="K46" t="n">
-        <v>-65.67</v>
+        <v>-39.18</v>
       </c>
       <c r="L46" t="n">
-        <v>71.84999999999999</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>90.45999999999999</v>
+        <v>48.73</v>
       </c>
       <c r="K47" t="n">
-        <v>-129.45</v>
+        <v>-69.73999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>157.92</v>
+        <v>85.08</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-139.3</v>
+        <v>-74.01000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-19.45</v>
+        <v>-10.34</v>
       </c>
       <c r="L48" t="n">
-        <v>140.65</v>
+        <v>74.73</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-108.33</v>
+        <v>-59.81</v>
       </c>
       <c r="K49" t="n">
-        <v>21.93</v>
+        <v>12.11</v>
       </c>
       <c r="L49" t="n">
-        <v>110.52</v>
+        <v>61.03</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-120.86</v>
+        <v>-62.68</v>
       </c>
       <c r="K50" t="n">
-        <v>-102.18</v>
+        <v>-52.99</v>
       </c>
       <c r="L50" t="n">
-        <v>158.27</v>
+        <v>82.08</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>151.7</v>
+        <v>76.33</v>
       </c>
       <c r="K51" t="n">
-        <v>-111.53</v>
+        <v>-56.12</v>
       </c>
       <c r="L51" t="n">
-        <v>188.29</v>
+        <v>94.73</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-15.7</v>
+        <v>-7.86</v>
       </c>
       <c r="K52" t="n">
-        <v>200.14</v>
+        <v>100.18</v>
       </c>
       <c r="L52" t="n">
-        <v>200.75</v>
+        <v>100.49</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-132.15</v>
+        <v>-78.05</v>
       </c>
       <c r="K53" t="n">
-        <v>-34.39</v>
+        <v>-20.31</v>
       </c>
       <c r="L53" t="n">
-        <v>136.55</v>
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>171.04</v>
+        <v>103.88</v>
       </c>
       <c r="K54" t="n">
-        <v>239.23</v>
+        <v>145.29</v>
       </c>
       <c r="L54" t="n">
-        <v>294.09</v>
+        <v>178.61</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>228.96</v>
+        <v>120.48</v>
       </c>
       <c r="K55" t="n">
-        <v>-113.08</v>
+        <v>-59.5</v>
       </c>
       <c r="L55" t="n">
-        <v>255.37</v>
+        <v>134.38</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-205.38</v>
+        <v>-115.57</v>
       </c>
       <c r="K56" t="n">
-        <v>189.74</v>
+        <v>106.77</v>
       </c>
       <c r="L56" t="n">
-        <v>279.61</v>
+        <v>157.34</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-105.67</v>
+        <v>-60.22</v>
       </c>
       <c r="K57" t="n">
-        <v>185.17</v>
+        <v>105.52</v>
       </c>
       <c r="L57" t="n">
-        <v>213.2</v>
+        <v>121.49</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>337.56</v>
+        <v>210.01</v>
       </c>
       <c r="K58" t="n">
-        <v>233.39</v>
+        <v>145.2</v>
       </c>
       <c r="L58" t="n">
-        <v>410.38</v>
+        <v>255.32</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>29</v>
       </c>
       <c r="J59" t="n">
-        <v>83.23999999999999</v>
+        <v>49.47</v>
       </c>
       <c r="K59" t="n">
-        <v>-64.34</v>
+        <v>-38.24</v>
       </c>
       <c r="L59" t="n">
-        <v>105.21</v>
+        <v>62.53</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-88.36</v>
+        <v>-46.52</v>
       </c>
       <c r="K60" t="n">
-        <v>-141.39</v>
+        <v>-74.44</v>
       </c>
       <c r="L60" t="n">
-        <v>166.73</v>
+        <v>87.78</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-91.65000000000001</v>
+        <v>-51.91</v>
       </c>
       <c r="K61" t="n">
-        <v>85.12</v>
+        <v>48.21</v>
       </c>
       <c r="L61" t="n">
-        <v>125.08</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>165.25</v>
+        <v>76.72</v>
       </c>
       <c r="K62" t="n">
-        <v>16.86</v>
+        <v>7.83</v>
       </c>
       <c r="L62" t="n">
-        <v>166.11</v>
+        <v>77.12</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-164.7</v>
+        <v>-83.42</v>
       </c>
       <c r="K63" t="n">
-        <v>-25.82</v>
+        <v>-13.08</v>
       </c>
       <c r="L63" t="n">
-        <v>166.71</v>
+        <v>84.44</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>129.8</v>
+        <v>67.59</v>
       </c>
       <c r="K64" t="n">
-        <v>36.2</v>
+        <v>18.85</v>
       </c>
       <c r="L64" t="n">
-        <v>134.75</v>
+        <v>70.17</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>260.72</v>
+        <v>125.76</v>
       </c>
       <c r="K65" t="n">
-        <v>22.21</v>
+        <v>10.71</v>
       </c>
       <c r="L65" t="n">
-        <v>261.66</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>104.08</v>
+        <v>53.38</v>
       </c>
       <c r="K66" t="n">
-        <v>-60.86</v>
+        <v>-31.21</v>
       </c>
       <c r="L66" t="n">
-        <v>120.57</v>
+        <v>61.84</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-45.66</v>
+        <v>-23.04</v>
       </c>
       <c r="K67" t="n">
-        <v>185.79</v>
+        <v>93.75</v>
       </c>
       <c r="L67" t="n">
-        <v>191.32</v>
+        <v>96.54000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-12.44</v>
+        <v>-6.6</v>
       </c>
       <c r="K68" t="n">
-        <v>-179.92</v>
+        <v>-95.45999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>180.35</v>
+        <v>95.69</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-161.01</v>
+        <v>-91.65000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>76.97</v>
+        <v>43.81</v>
       </c>
       <c r="L69" t="n">
-        <v>178.46</v>
+        <v>101.58</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-101.56</v>
+        <v>-58.92</v>
       </c>
       <c r="K70" t="n">
-        <v>-178.2</v>
+        <v>-103.38</v>
       </c>
       <c r="L70" t="n">
-        <v>205.11</v>
+        <v>118.99</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>201.2</v>
+        <v>111.54</v>
       </c>
       <c r="K71" t="n">
-        <v>54.07</v>
+        <v>29.97</v>
       </c>
       <c r="L71" t="n">
-        <v>208.34</v>
+        <v>115.49</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-320.99</v>
+        <v>-189.19</v>
       </c>
       <c r="K72" t="n">
-        <v>-216.15</v>
+        <v>-127.4</v>
       </c>
       <c r="L72" t="n">
-        <v>386.98</v>
+        <v>228.09</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-241.19</v>
+        <v>-133.63</v>
       </c>
       <c r="K73" t="n">
-        <v>-54.08</v>
+        <v>-29.96</v>
       </c>
       <c r="L73" t="n">
-        <v>247.18</v>
+        <v>136.95</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>-119.75</v>
+        <v>-66.31999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>-73.98999999999999</v>
+        <v>-40.98</v>
       </c>
       <c r="L74" t="n">
-        <v>140.76</v>
+        <v>77.95999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>73.7</v>
+        <v>24.01</v>
       </c>
       <c r="K75" t="n">
-        <v>-10.21</v>
+        <v>-3.33</v>
       </c>
       <c r="L75" t="n">
-        <v>74.40000000000001</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>56.06</v>
+        <v>25.9</v>
       </c>
       <c r="K76" t="n">
-        <v>-53.82</v>
+        <v>-24.87</v>
       </c>
       <c r="L76" t="n">
-        <v>77.70999999999999</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>115.59</v>
+        <v>54.14</v>
       </c>
       <c r="K77" t="n">
-        <v>41.55</v>
+        <v>19.46</v>
       </c>
       <c r="L77" t="n">
-        <v>122.83</v>
+        <v>57.53</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-58.7</v>
+        <v>-27.89</v>
       </c>
       <c r="K78" t="n">
-        <v>187.48</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>196.45</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>55.01</v>
+        <v>26.78</v>
       </c>
       <c r="K79" t="n">
-        <v>-78.23</v>
+        <v>-38.08</v>
       </c>
       <c r="L79" t="n">
-        <v>95.64</v>
+        <v>46.55</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-205.67</v>
+        <v>-102.61</v>
       </c>
       <c r="K80" t="n">
-        <v>118.52</v>
+        <v>59.13</v>
       </c>
       <c r="L80" t="n">
-        <v>237.37</v>
+        <v>118.42</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-239.05</v>
+        <v>-120.84</v>
       </c>
       <c r="K81" t="n">
-        <v>-106.96</v>
+        <v>-54.07</v>
       </c>
       <c r="L81" t="n">
-        <v>261.89</v>
+        <v>132.39</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>-55.44</v>
+        <v>-28.11</v>
       </c>
       <c r="K82" t="n">
-        <v>251.35</v>
+        <v>127.45</v>
       </c>
       <c r="L82" t="n">
-        <v>257.4</v>
+        <v>130.51</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-124.61</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-241.32</v>
+        <v>-125.69</v>
       </c>
       <c r="L83" t="n">
-        <v>271.59</v>
+        <v>141.46</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>355.59</v>
+        <v>193.13</v>
       </c>
       <c r="K84" t="n">
-        <v>224.01</v>
+        <v>121.66</v>
       </c>
       <c r="L84" t="n">
-        <v>420.27</v>
+        <v>228.26</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-212.89</v>
+        <v>-105.59</v>
       </c>
       <c r="K85" t="n">
-        <v>156.24</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>264.07</v>
+        <v>130.97</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-326.15</v>
+        <v>-183.74</v>
       </c>
       <c r="K86" t="n">
-        <v>-196.46</v>
+        <v>-110.68</v>
       </c>
       <c r="L86" t="n">
-        <v>380.75</v>
+        <v>214.5</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>283.37</v>
+        <v>156.84</v>
       </c>
       <c r="K87" t="n">
-        <v>301.47</v>
+        <v>166.85</v>
       </c>
       <c r="L87" t="n">
-        <v>413.74</v>
+        <v>228.99</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>353.5</v>
+        <v>195.76</v>
       </c>
       <c r="K88" t="n">
-        <v>-317.32</v>
+        <v>-175.72</v>
       </c>
       <c r="L88" t="n">
-        <v>475.04</v>
+        <v>263.06</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="K14" t="n">
-        <v>-50.22</v>
+        <v>-50.38</v>
       </c>
       <c r="L14" t="n">
-        <v>50.26</v>
+        <v>50.42</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>32.36</v>
+        <v>35.34</v>
       </c>
       <c r="K15" t="n">
-        <v>8.380000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="L15" t="n">
-        <v>33.43</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-52.28</v>
+        <v>-51.12</v>
       </c>
       <c r="K16" t="n">
-        <v>-53.31</v>
+        <v>-52.13</v>
       </c>
       <c r="L16" t="n">
-        <v>74.67</v>
+        <v>73.01000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-38.03</v>
+        <v>-39.43</v>
       </c>
       <c r="K17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="L17" t="n">
-        <v>38.04</v>
+        <v>39.44</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-72.39</v>
+        <v>-69.42</v>
       </c>
       <c r="K18" t="n">
-        <v>-56.85</v>
+        <v>-54.51</v>
       </c>
       <c r="L18" t="n">
-        <v>92.04000000000001</v>
+        <v>88.26000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>136.38</v>
+        <v>127.24</v>
       </c>
       <c r="K19" t="n">
-        <v>-95.77</v>
+        <v>-89.34999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>166.65</v>
+        <v>155.48</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-78.53</v>
+        <v>-78.43000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>69.65000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>104.97</v>
+        <v>104.84</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>80.92</v>
+        <v>80.27</v>
       </c>
       <c r="K21" t="n">
-        <v>-50.07</v>
+        <v>-49.67</v>
       </c>
       <c r="L21" t="n">
-        <v>95.16</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-6.87</v>
+        <v>-6.82</v>
       </c>
       <c r="K22" t="n">
-        <v>103.61</v>
+        <v>102.98</v>
       </c>
       <c r="L22" t="n">
-        <v>103.84</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-38.33</v>
+        <v>-39.45</v>
       </c>
       <c r="K23" t="n">
-        <v>103.36</v>
+        <v>106.37</v>
       </c>
       <c r="L23" t="n">
-        <v>110.23</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-170.82</v>
+        <v>-163.66</v>
       </c>
       <c r="K24" t="n">
-        <v>77.37</v>
+        <v>74.13</v>
       </c>
       <c r="L24" t="n">
-        <v>187.52</v>
+        <v>179.67</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-154.58</v>
+        <v>-152.79</v>
       </c>
       <c r="K25" t="n">
-        <v>34.12</v>
+        <v>33.73</v>
       </c>
       <c r="L25" t="n">
-        <v>158.3</v>
+        <v>156.47</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-209.53</v>
+        <v>-206.42</v>
       </c>
       <c r="K26" t="n">
-        <v>-15.44</v>
+        <v>-15.21</v>
       </c>
       <c r="L26" t="n">
-        <v>210.1</v>
+        <v>206.98</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>124.15</v>
+        <v>121.72</v>
       </c>
       <c r="K27" t="n">
-        <v>-184.06</v>
+        <v>-180.46</v>
       </c>
       <c r="L27" t="n">
-        <v>222.02</v>
+        <v>217.67</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-202.84</v>
+        <v>-201.11</v>
       </c>
       <c r="K28" t="n">
-        <v>83.87</v>
+        <v>83.16</v>
       </c>
       <c r="L28" t="n">
-        <v>219.49</v>
+        <v>217.62</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>29.19</v>
+        <v>31.17</v>
       </c>
       <c r="K29" t="n">
-        <v>-21.87</v>
+        <v>-23.36</v>
       </c>
       <c r="L29" t="n">
-        <v>36.48</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.48</v>
+        <v>-3.46</v>
       </c>
       <c r="K30" t="n">
-        <v>-60.44</v>
+        <v>-60.19</v>
       </c>
       <c r="L30" t="n">
-        <v>60.54</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-41.05</v>
+        <v>-42.22</v>
       </c>
       <c r="K31" t="n">
-        <v>-21.25</v>
+        <v>-21.85</v>
       </c>
       <c r="L31" t="n">
-        <v>46.22</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-14.97</v>
+        <v>-15.06</v>
       </c>
       <c r="K32" t="n">
-        <v>67.31</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>68.95</v>
+        <v>69.34</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>38.32</v>
+        <v>38.17</v>
       </c>
       <c r="K33" t="n">
-        <v>-60.86</v>
+        <v>-60.63</v>
       </c>
       <c r="L33" t="n">
-        <v>71.92</v>
+        <v>71.65000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-110.11</v>
+        <v>-103.52</v>
       </c>
       <c r="K34" t="n">
-        <v>87.98</v>
+        <v>82.72</v>
       </c>
       <c r="L34" t="n">
-        <v>140.94</v>
+        <v>132.51</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-75.84</v>
+        <v>-74.14</v>
       </c>
       <c r="K35" t="n">
-        <v>-89.31999999999999</v>
+        <v>-87.31</v>
       </c>
       <c r="L35" t="n">
-        <v>117.18</v>
+        <v>114.54</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-47.1</v>
+        <v>-49.47</v>
       </c>
       <c r="K36" t="n">
-        <v>-55.14</v>
+        <v>-57.91</v>
       </c>
       <c r="L36" t="n">
-        <v>72.52</v>
+        <v>76.16</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-73.06999999999999</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-47.8</v>
+        <v>-48.93</v>
       </c>
       <c r="L37" t="n">
-        <v>87.31999999999999</v>
+        <v>89.38</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>31</v>
       </c>
       <c r="J38" t="n">
-        <v>-107.06</v>
+        <v>-110.64</v>
       </c>
       <c r="K38" t="n">
-        <v>-22.23</v>
+        <v>-22.97</v>
       </c>
       <c r="L38" t="n">
-        <v>109.34</v>
+        <v>112.99</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-83.66</v>
+        <v>-87.75</v>
       </c>
       <c r="K39" t="n">
-        <v>-52.43</v>
+        <v>-55</v>
       </c>
       <c r="L39" t="n">
-        <v>98.73</v>
+        <v>103.56</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>92.28</v>
+        <v>94.7</v>
       </c>
       <c r="K40" t="n">
-        <v>79.65000000000001</v>
+        <v>81.75</v>
       </c>
       <c r="L40" t="n">
-        <v>121.9</v>
+        <v>125.11</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.96</v>
+        <v>-19.74</v>
       </c>
       <c r="K41" t="n">
-        <v>-161.13</v>
+        <v>-167.8</v>
       </c>
       <c r="L41" t="n">
-        <v>162.24</v>
+        <v>168.96</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-14.78</v>
+        <v>-14.94</v>
       </c>
       <c r="K42" t="n">
-        <v>170.91</v>
+        <v>172.77</v>
       </c>
       <c r="L42" t="n">
-        <v>171.55</v>
+        <v>173.42</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-172.74</v>
+        <v>-172.79</v>
       </c>
       <c r="K43" t="n">
-        <v>-9.57</v>
+        <v>-9.58</v>
       </c>
       <c r="L43" t="n">
-        <v>173.01</v>
+        <v>173.06</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>19.93</v>
+        <v>20.47</v>
       </c>
       <c r="K44" t="n">
-        <v>-45.55</v>
+        <v>-46.8</v>
       </c>
       <c r="L44" t="n">
-        <v>49.72</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>83.83</v>
+        <v>80.16</v>
       </c>
       <c r="K45" t="n">
-        <v>54.51</v>
+        <v>52.13</v>
       </c>
       <c r="L45" t="n">
-        <v>99.98999999999999</v>
+        <v>95.62</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>17.39</v>
+        <v>17.91</v>
       </c>
       <c r="K46" t="n">
-        <v>-39.18</v>
+        <v>-40.36</v>
       </c>
       <c r="L46" t="n">
-        <v>42.86</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>48.73</v>
+        <v>47.65</v>
       </c>
       <c r="K47" t="n">
-        <v>-69.73999999999999</v>
+        <v>-68.19</v>
       </c>
       <c r="L47" t="n">
-        <v>85.08</v>
+        <v>83.19</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-74.01000000000001</v>
+        <v>-73.40000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-10.34</v>
+        <v>-10.25</v>
       </c>
       <c r="L48" t="n">
-        <v>74.73</v>
+        <v>74.11</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-59.81</v>
+        <v>-61.34</v>
       </c>
       <c r="K49" t="n">
-        <v>12.11</v>
+        <v>12.42</v>
       </c>
       <c r="L49" t="n">
-        <v>61.03</v>
+        <v>62.59</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-62.68</v>
+        <v>-64.37</v>
       </c>
       <c r="K50" t="n">
-        <v>-52.99</v>
+        <v>-54.42</v>
       </c>
       <c r="L50" t="n">
-        <v>82.08</v>
+        <v>84.29000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>76.33</v>
+        <v>76.91</v>
       </c>
       <c r="K51" t="n">
-        <v>-56.12</v>
+        <v>-56.54</v>
       </c>
       <c r="L51" t="n">
-        <v>94.73</v>
+        <v>95.45999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-7.86</v>
+        <v>-7.95</v>
       </c>
       <c r="K52" t="n">
-        <v>100.18</v>
+        <v>101.38</v>
       </c>
       <c r="L52" t="n">
-        <v>100.49</v>
+        <v>101.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-78.05</v>
+        <v>-85.15000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-20.31</v>
+        <v>-22.16</v>
       </c>
       <c r="L53" t="n">
-        <v>80.65000000000001</v>
+        <v>87.98999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>103.88</v>
+        <v>100.57</v>
       </c>
       <c r="K54" t="n">
-        <v>145.29</v>
+        <v>140.66</v>
       </c>
       <c r="L54" t="n">
-        <v>178.61</v>
+        <v>172.91</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>120.48</v>
+        <v>122.51</v>
       </c>
       <c r="K55" t="n">
-        <v>-59.5</v>
+        <v>-60.5</v>
       </c>
       <c r="L55" t="n">
-        <v>134.38</v>
+        <v>136.64</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-115.57</v>
+        <v>-119.19</v>
       </c>
       <c r="K56" t="n">
-        <v>106.77</v>
+        <v>110.11</v>
       </c>
       <c r="L56" t="n">
-        <v>157.34</v>
+        <v>162.27</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-60.22</v>
+        <v>-63.46</v>
       </c>
       <c r="K57" t="n">
-        <v>105.52</v>
+        <v>111.2</v>
       </c>
       <c r="L57" t="n">
-        <v>121.49</v>
+        <v>128.04</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>210.01</v>
+        <v>204.14</v>
       </c>
       <c r="K58" t="n">
-        <v>145.2</v>
+        <v>141.14</v>
       </c>
       <c r="L58" t="n">
-        <v>255.32</v>
+        <v>248.18</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>29</v>
       </c>
       <c r="J59" t="n">
-        <v>49.47</v>
+        <v>48.77</v>
       </c>
       <c r="K59" t="n">
-        <v>-38.24</v>
+        <v>-37.7</v>
       </c>
       <c r="L59" t="n">
-        <v>62.53</v>
+        <v>61.64</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-46.52</v>
+        <v>-44.64</v>
       </c>
       <c r="K60" t="n">
-        <v>-74.44</v>
+        <v>-71.42</v>
       </c>
       <c r="L60" t="n">
-        <v>87.78</v>
+        <v>84.22</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-51.91</v>
+        <v>-51.3</v>
       </c>
       <c r="K61" t="n">
-        <v>48.21</v>
+        <v>47.65</v>
       </c>
       <c r="L61" t="n">
-        <v>70.84</v>
+        <v>70.01000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>76.72</v>
+        <v>75.12</v>
       </c>
       <c r="K62" t="n">
-        <v>7.83</v>
+        <v>7.66</v>
       </c>
       <c r="L62" t="n">
-        <v>77.12</v>
+        <v>75.51000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-83.42</v>
+        <v>-81.92</v>
       </c>
       <c r="K63" t="n">
-        <v>-13.08</v>
+        <v>-12.84</v>
       </c>
       <c r="L63" t="n">
-        <v>84.44</v>
+        <v>82.92</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>67.59</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>18.85</v>
+        <v>18.99</v>
       </c>
       <c r="L64" t="n">
-        <v>70.17</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>125.76</v>
+        <v>124.7</v>
       </c>
       <c r="K65" t="n">
-        <v>10.71</v>
+        <v>10.62</v>
       </c>
       <c r="L65" t="n">
-        <v>126.21</v>
+        <v>125.15</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>53.38</v>
+        <v>57.93</v>
       </c>
       <c r="K66" t="n">
-        <v>-31.21</v>
+        <v>-33.87</v>
       </c>
       <c r="L66" t="n">
-        <v>61.84</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-23.04</v>
+        <v>-23.46</v>
       </c>
       <c r="K67" t="n">
-        <v>93.75</v>
+        <v>95.44</v>
       </c>
       <c r="L67" t="n">
-        <v>96.54000000000001</v>
+        <v>98.28</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-6.6</v>
+        <v>-7.13</v>
       </c>
       <c r="K68" t="n">
-        <v>-95.45999999999999</v>
+        <v>-103.14</v>
       </c>
       <c r="L68" t="n">
-        <v>95.69</v>
+        <v>103.39</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-91.65000000000001</v>
+        <v>-96.95999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>43.81</v>
+        <v>46.35</v>
       </c>
       <c r="L69" t="n">
-        <v>101.58</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-58.92</v>
+        <v>-60.24</v>
       </c>
       <c r="K70" t="n">
-        <v>-103.38</v>
+        <v>-105.71</v>
       </c>
       <c r="L70" t="n">
-        <v>118.99</v>
+        <v>121.67</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>111.54</v>
+        <v>123.67</v>
       </c>
       <c r="K71" t="n">
-        <v>29.97</v>
+        <v>33.23</v>
       </c>
       <c r="L71" t="n">
-        <v>115.49</v>
+        <v>128.06</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-189.19</v>
+        <v>-186.09</v>
       </c>
       <c r="K72" t="n">
-        <v>-127.4</v>
+        <v>-125.31</v>
       </c>
       <c r="L72" t="n">
-        <v>228.09</v>
+        <v>224.35</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-133.63</v>
+        <v>-144.12</v>
       </c>
       <c r="K73" t="n">
-        <v>-29.96</v>
+        <v>-32.31</v>
       </c>
       <c r="L73" t="n">
-        <v>136.95</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>-66.31999999999999</v>
+        <v>-64.48</v>
       </c>
       <c r="K74" t="n">
-        <v>-40.98</v>
+        <v>-39.84</v>
       </c>
       <c r="L74" t="n">
-        <v>77.95999999999999</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>24.01</v>
+        <v>23</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.33</v>
+        <v>-3.19</v>
       </c>
       <c r="L75" t="n">
-        <v>24.24</v>
+        <v>23.22</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>25.9</v>
+        <v>25.3</v>
       </c>
       <c r="K76" t="n">
-        <v>-24.87</v>
+        <v>-24.29</v>
       </c>
       <c r="L76" t="n">
-        <v>35.91</v>
+        <v>35.07</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>54.14</v>
+        <v>55.56</v>
       </c>
       <c r="K77" t="n">
-        <v>19.46</v>
+        <v>19.97</v>
       </c>
       <c r="L77" t="n">
-        <v>57.53</v>
+        <v>59.04</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-27.89</v>
+        <v>-26.9</v>
       </c>
       <c r="K78" t="n">
-        <v>89.06999999999999</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>93.33</v>
+        <v>90.04000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>26.78</v>
+        <v>28.35</v>
       </c>
       <c r="K79" t="n">
-        <v>-38.08</v>
+        <v>-40.32</v>
       </c>
       <c r="L79" t="n">
-        <v>46.55</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-102.61</v>
+        <v>-100.73</v>
       </c>
       <c r="K80" t="n">
-        <v>59.13</v>
+        <v>58.04</v>
       </c>
       <c r="L80" t="n">
-        <v>118.42</v>
+        <v>116.25</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-120.84</v>
+        <v>-116.79</v>
       </c>
       <c r="K81" t="n">
-        <v>-54.07</v>
+        <v>-52.26</v>
       </c>
       <c r="L81" t="n">
-        <v>132.39</v>
+        <v>127.95</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>-28.11</v>
+        <v>-27.3</v>
       </c>
       <c r="K82" t="n">
-        <v>127.45</v>
+        <v>123.78</v>
       </c>
       <c r="L82" t="n">
-        <v>130.51</v>
+        <v>126.75</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-64.90000000000001</v>
+        <v>-65.68000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-125.69</v>
+        <v>-127.19</v>
       </c>
       <c r="L83" t="n">
-        <v>141.46</v>
+        <v>143.15</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>193.13</v>
+        <v>184.77</v>
       </c>
       <c r="K84" t="n">
-        <v>121.66</v>
+        <v>116.4</v>
       </c>
       <c r="L84" t="n">
-        <v>228.26</v>
+        <v>218.38</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-105.59</v>
+        <v>-108.77</v>
       </c>
       <c r="K85" t="n">
-        <v>77.48999999999999</v>
+        <v>79.83</v>
       </c>
       <c r="L85" t="n">
-        <v>130.97</v>
+        <v>134.92</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-183.74</v>
+        <v>-183.01</v>
       </c>
       <c r="K86" t="n">
-        <v>-110.68</v>
+        <v>-110.24</v>
       </c>
       <c r="L86" t="n">
-        <v>214.5</v>
+        <v>213.65</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>156.84</v>
+        <v>158.8</v>
       </c>
       <c r="K87" t="n">
-        <v>166.85</v>
+        <v>168.94</v>
       </c>
       <c r="L87" t="n">
-        <v>228.99</v>
+        <v>231.85</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>195.76</v>
+        <v>194.43</v>
       </c>
       <c r="K88" t="n">
-        <v>-175.72</v>
+        <v>-174.53</v>
       </c>
       <c r="L88" t="n">
-        <v>263.06</v>
+        <v>261.27</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="K14" t="n">
-        <v>-50.38</v>
+        <v>-51.83</v>
       </c>
       <c r="L14" t="n">
-        <v>50.42</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>35.34</v>
+        <v>38.74</v>
       </c>
       <c r="K15" t="n">
-        <v>9.16</v>
+        <v>10.04</v>
       </c>
       <c r="L15" t="n">
-        <v>36.5</v>
+        <v>40.02</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-51.12</v>
+        <v>-49.79</v>
       </c>
       <c r="K16" t="n">
-        <v>-52.13</v>
+        <v>-50.77</v>
       </c>
       <c r="L16" t="n">
-        <v>73.01000000000001</v>
+        <v>71.11</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-39.43</v>
+        <v>-43.41</v>
       </c>
       <c r="K17" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="L17" t="n">
-        <v>39.44</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-69.42</v>
+        <v>-66.02</v>
       </c>
       <c r="K18" t="n">
-        <v>-54.51</v>
+        <v>-51.84</v>
       </c>
       <c r="L18" t="n">
-        <v>88.26000000000001</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>127.24</v>
+        <v>116.79</v>
       </c>
       <c r="K19" t="n">
-        <v>-89.34999999999999</v>
+        <v>-82.01000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>155.48</v>
+        <v>142.71</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-78.43000000000001</v>
+        <v>-78.31999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>69.56999999999999</v>
+        <v>69.47</v>
       </c>
       <c r="L20" t="n">
-        <v>104.84</v>
+        <v>104.69</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>80.27</v>
+        <v>79.53</v>
       </c>
       <c r="K21" t="n">
-        <v>-49.67</v>
+        <v>-49.21</v>
       </c>
       <c r="L21" t="n">
-        <v>94.40000000000001</v>
+        <v>93.53</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-6.82</v>
+        <v>-6.77</v>
       </c>
       <c r="K22" t="n">
-        <v>102.98</v>
+        <v>102.25</v>
       </c>
       <c r="L22" t="n">
-        <v>103.2</v>
+        <v>102.47</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-39.45</v>
+        <v>-40.72</v>
       </c>
       <c r="K23" t="n">
-        <v>106.37</v>
+        <v>109.81</v>
       </c>
       <c r="L23" t="n">
-        <v>113.45</v>
+        <v>117.11</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-163.66</v>
+        <v>-155.48</v>
       </c>
       <c r="K24" t="n">
-        <v>74.13</v>
+        <v>70.42</v>
       </c>
       <c r="L24" t="n">
-        <v>179.67</v>
+        <v>170.69</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-152.79</v>
+        <v>-150.74</v>
       </c>
       <c r="K25" t="n">
-        <v>33.73</v>
+        <v>33.28</v>
       </c>
       <c r="L25" t="n">
-        <v>156.47</v>
+        <v>154.37</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-206.42</v>
+        <v>-202.86</v>
       </c>
       <c r="K26" t="n">
-        <v>-15.21</v>
+        <v>-14.95</v>
       </c>
       <c r="L26" t="n">
-        <v>206.98</v>
+        <v>203.41</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>121.72</v>
+        <v>118.95</v>
       </c>
       <c r="K27" t="n">
-        <v>-180.46</v>
+        <v>-176.34</v>
       </c>
       <c r="L27" t="n">
-        <v>217.67</v>
+        <v>212.71</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-201.11</v>
+        <v>-197.51</v>
       </c>
       <c r="K28" t="n">
-        <v>83.16</v>
+        <v>81.67</v>
       </c>
       <c r="L28" t="n">
-        <v>217.62</v>
+        <v>213.73</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>31.17</v>
+        <v>33.44</v>
       </c>
       <c r="K29" t="n">
-        <v>-23.36</v>
+        <v>-25.05</v>
       </c>
       <c r="L29" t="n">
-        <v>38.95</v>
+        <v>41.78</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.46</v>
+        <v>-3.45</v>
       </c>
       <c r="K30" t="n">
-        <v>-60.19</v>
+        <v>-59.9</v>
       </c>
       <c r="L30" t="n">
-        <v>60.29</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-42.22</v>
+        <v>-43.55</v>
       </c>
       <c r="K31" t="n">
-        <v>-21.85</v>
+        <v>-22.54</v>
       </c>
       <c r="L31" t="n">
-        <v>47.54</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-15.06</v>
+        <v>-15.15</v>
       </c>
       <c r="K32" t="n">
-        <v>67.68000000000001</v>
+        <v>68.11</v>
       </c>
       <c r="L32" t="n">
-        <v>69.34</v>
+        <v>69.78</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>38.17</v>
+        <v>38.01</v>
       </c>
       <c r="K33" t="n">
-        <v>-60.63</v>
+        <v>-60.37</v>
       </c>
       <c r="L33" t="n">
-        <v>71.65000000000001</v>
+        <v>71.34</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-103.52</v>
+        <v>-96</v>
       </c>
       <c r="K34" t="n">
-        <v>82.72</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>132.51</v>
+        <v>122.88</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-74.14</v>
+        <v>-72.19</v>
       </c>
       <c r="K35" t="n">
-        <v>-87.31</v>
+        <v>-85.02</v>
       </c>
       <c r="L35" t="n">
-        <v>114.54</v>
+        <v>111.53</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-49.47</v>
+        <v>-52.24</v>
       </c>
       <c r="K36" t="n">
-        <v>-57.91</v>
+        <v>-61.16</v>
       </c>
       <c r="L36" t="n">
-        <v>76.16</v>
+        <v>80.44</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-74.79000000000001</v>
+        <v>-76.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-48.93</v>
+        <v>-50.24</v>
       </c>
       <c r="L37" t="n">
-        <v>89.38</v>
+        <v>91.77</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>31</v>
       </c>
       <c r="J38" t="n">
-        <v>-110.64</v>
+        <v>-114.34</v>
       </c>
       <c r="K38" t="n">
-        <v>-22.97</v>
+        <v>-23.74</v>
       </c>
       <c r="L38" t="n">
-        <v>112.99</v>
+        <v>116.78</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-87.75</v>
+        <v>-92.43000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>-55</v>
+        <v>-57.93</v>
       </c>
       <c r="L39" t="n">
-        <v>103.56</v>
+        <v>109.08</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>94.7</v>
+        <v>97.08</v>
       </c>
       <c r="K40" t="n">
-        <v>81.75</v>
+        <v>83.8</v>
       </c>
       <c r="L40" t="n">
-        <v>125.11</v>
+        <v>128.25</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.74</v>
+        <v>-20.27</v>
       </c>
       <c r="K41" t="n">
-        <v>-167.8</v>
+        <v>-172.35</v>
       </c>
       <c r="L41" t="n">
-        <v>168.96</v>
+        <v>173.54</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-14.94</v>
+        <v>-15.13</v>
       </c>
       <c r="K42" t="n">
-        <v>172.77</v>
+        <v>174.9</v>
       </c>
       <c r="L42" t="n">
-        <v>173.42</v>
+        <v>175.55</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-172.79</v>
+        <v>-172.85</v>
       </c>
       <c r="K43" t="n">
         <v>-9.58</v>
       </c>
       <c r="L43" t="n">
-        <v>173.06</v>
+        <v>173.12</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>20.47</v>
+        <v>21.43</v>
       </c>
       <c r="K44" t="n">
-        <v>-46.8</v>
+        <v>-48.99</v>
       </c>
       <c r="L44" t="n">
-        <v>51.08</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>80.16</v>
+        <v>75.97</v>
       </c>
       <c r="K45" t="n">
-        <v>52.13</v>
+        <v>49.4</v>
       </c>
       <c r="L45" t="n">
-        <v>95.62</v>
+        <v>90.62</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>17.91</v>
+        <v>18.51</v>
       </c>
       <c r="K46" t="n">
-        <v>-40.36</v>
+        <v>-41.71</v>
       </c>
       <c r="L46" t="n">
-        <v>44.15</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>47.65</v>
+        <v>46.44</v>
       </c>
       <c r="K47" t="n">
-        <v>-68.19</v>
+        <v>-66.45</v>
       </c>
       <c r="L47" t="n">
-        <v>83.19</v>
+        <v>81.06999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-73.40000000000001</v>
+        <v>-72.88</v>
       </c>
       <c r="K48" t="n">
-        <v>-10.25</v>
+        <v>-10.18</v>
       </c>
       <c r="L48" t="n">
-        <v>74.11</v>
+        <v>73.59</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-61.34</v>
+        <v>-63.09</v>
       </c>
       <c r="K49" t="n">
-        <v>12.42</v>
+        <v>12.77</v>
       </c>
       <c r="L49" t="n">
-        <v>62.59</v>
+        <v>64.37</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-64.37</v>
+        <v>-66.3</v>
       </c>
       <c r="K50" t="n">
-        <v>-54.42</v>
+        <v>-56.05</v>
       </c>
       <c r="L50" t="n">
-        <v>84.29000000000001</v>
+        <v>86.81999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>76.91</v>
+        <v>77.94</v>
       </c>
       <c r="K51" t="n">
-        <v>-56.54</v>
+        <v>-57.3</v>
       </c>
       <c r="L51" t="n">
-        <v>95.45999999999999</v>
+        <v>96.73999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-7.95</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>101.38</v>
+        <v>103.34</v>
       </c>
       <c r="L52" t="n">
-        <v>101.69</v>
+        <v>103.65</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-85.15000000000001</v>
+        <v>-93.28</v>
       </c>
       <c r="K53" t="n">
-        <v>-22.16</v>
+        <v>-24.27</v>
       </c>
       <c r="L53" t="n">
-        <v>87.98999999999999</v>
+        <v>96.38</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>100.57</v>
+        <v>96.78</v>
       </c>
       <c r="K54" t="n">
-        <v>140.66</v>
+        <v>135.37</v>
       </c>
       <c r="L54" t="n">
-        <v>172.91</v>
+        <v>166.41</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>122.51</v>
+        <v>124.4</v>
       </c>
       <c r="K55" t="n">
-        <v>-60.5</v>
+        <v>-61.44</v>
       </c>
       <c r="L55" t="n">
-        <v>136.64</v>
+        <v>138.74</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-119.19</v>
+        <v>-122.4</v>
       </c>
       <c r="K56" t="n">
-        <v>110.11</v>
+        <v>113.08</v>
       </c>
       <c r="L56" t="n">
-        <v>162.27</v>
+        <v>166.64</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-63.46</v>
+        <v>-67.17</v>
       </c>
       <c r="K57" t="n">
-        <v>111.2</v>
+        <v>117.7</v>
       </c>
       <c r="L57" t="n">
-        <v>128.04</v>
+        <v>135.51</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>204.14</v>
+        <v>197.43</v>
       </c>
       <c r="K58" t="n">
-        <v>141.14</v>
+        <v>136.5</v>
       </c>
       <c r="L58" t="n">
-        <v>248.18</v>
+        <v>240.03</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>29</v>
       </c>
       <c r="J59" t="n">
-        <v>48.77</v>
+        <v>47.97</v>
       </c>
       <c r="K59" t="n">
-        <v>-37.7</v>
+        <v>-37.08</v>
       </c>
       <c r="L59" t="n">
-        <v>61.64</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-44.64</v>
+        <v>-42.69</v>
       </c>
       <c r="K60" t="n">
-        <v>-71.42</v>
+        <v>-68.3</v>
       </c>
       <c r="L60" t="n">
-        <v>84.22</v>
+        <v>80.55</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-51.3</v>
+        <v>-50.6</v>
       </c>
       <c r="K61" t="n">
-        <v>47.65</v>
+        <v>47</v>
       </c>
       <c r="L61" t="n">
-        <v>70.01000000000001</v>
+        <v>69.06</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>75.12</v>
+        <v>75.17</v>
       </c>
       <c r="K62" t="n">
-        <v>7.66</v>
+        <v>7.67</v>
       </c>
       <c r="L62" t="n">
-        <v>75.51000000000001</v>
+        <v>75.56</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-81.92</v>
+        <v>-81.03</v>
       </c>
       <c r="K63" t="n">
-        <v>-12.84</v>
+        <v>-12.71</v>
       </c>
       <c r="L63" t="n">
-        <v>82.92</v>
+        <v>82.02</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>68.09999999999999</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>18.99</v>
+        <v>19.26</v>
       </c>
       <c r="L64" t="n">
-        <v>70.7</v>
+        <v>71.70999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>124.7</v>
+        <v>125.18</v>
       </c>
       <c r="K65" t="n">
-        <v>10.62</v>
+        <v>10.67</v>
       </c>
       <c r="L65" t="n">
-        <v>125.15</v>
+        <v>125.64</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>57.93</v>
+        <v>63.17</v>
       </c>
       <c r="K66" t="n">
-        <v>-33.87</v>
+        <v>-36.94</v>
       </c>
       <c r="L66" t="n">
-        <v>67.09999999999999</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-23.46</v>
+        <v>-24.03</v>
       </c>
       <c r="K67" t="n">
-        <v>95.44</v>
+        <v>97.77</v>
       </c>
       <c r="L67" t="n">
-        <v>98.28</v>
+        <v>100.68</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-7.13</v>
+        <v>-7.72</v>
       </c>
       <c r="K68" t="n">
-        <v>-103.14</v>
+        <v>-111.61</v>
       </c>
       <c r="L68" t="n">
-        <v>103.39</v>
+        <v>111.87</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-96.95999999999999</v>
+        <v>-102.97</v>
       </c>
       <c r="K69" t="n">
-        <v>46.35</v>
+        <v>49.22</v>
       </c>
       <c r="L69" t="n">
-        <v>107.46</v>
+        <v>114.13</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-60.24</v>
+        <v>-61.76</v>
       </c>
       <c r="K70" t="n">
-        <v>-105.71</v>
+        <v>-108.37</v>
       </c>
       <c r="L70" t="n">
-        <v>121.67</v>
+        <v>124.74</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>123.67</v>
+        <v>134.94</v>
       </c>
       <c r="K71" t="n">
-        <v>33.23</v>
+        <v>36.26</v>
       </c>
       <c r="L71" t="n">
-        <v>128.06</v>
+        <v>139.73</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-186.09</v>
+        <v>-182.54</v>
       </c>
       <c r="K72" t="n">
-        <v>-125.31</v>
+        <v>-122.92</v>
       </c>
       <c r="L72" t="n">
-        <v>224.35</v>
+        <v>220.07</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-144.12</v>
+        <v>-152.91</v>
       </c>
       <c r="K73" t="n">
-        <v>-32.31</v>
+        <v>-34.28</v>
       </c>
       <c r="L73" t="n">
-        <v>147.7</v>
+        <v>156.7</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>-64.48</v>
+        <v>-62.38</v>
       </c>
       <c r="K74" t="n">
-        <v>-39.84</v>
+        <v>-38.54</v>
       </c>
       <c r="L74" t="n">
-        <v>75.8</v>
+        <v>73.33</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>23</v>
+        <v>25.05</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.19</v>
+        <v>-3.47</v>
       </c>
       <c r="L75" t="n">
-        <v>23.22</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>25.3</v>
+        <v>27.77</v>
       </c>
       <c r="K76" t="n">
-        <v>-24.29</v>
+        <v>-26.66</v>
       </c>
       <c r="L76" t="n">
-        <v>35.07</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>55.56</v>
+        <v>58.41</v>
       </c>
       <c r="K77" t="n">
-        <v>19.97</v>
+        <v>21</v>
       </c>
       <c r="L77" t="n">
-        <v>59.04</v>
+        <v>62.07</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-26.9</v>
+        <v>-26.35</v>
       </c>
       <c r="K78" t="n">
-        <v>85.93000000000001</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>90.04000000000001</v>
+        <v>88.20999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>28.35</v>
+        <v>30.59</v>
       </c>
       <c r="K79" t="n">
-        <v>-40.32</v>
+        <v>-43.5</v>
       </c>
       <c r="L79" t="n">
-        <v>49.29</v>
+        <v>53.18</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-100.73</v>
+        <v>-99.26000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>58.04</v>
+        <v>57.2</v>
       </c>
       <c r="L80" t="n">
-        <v>116.25</v>
+        <v>114.56</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-116.79</v>
+        <v>-112.64</v>
       </c>
       <c r="K81" t="n">
-        <v>-52.26</v>
+        <v>-50.4</v>
       </c>
       <c r="L81" t="n">
-        <v>127.95</v>
+        <v>123.4</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>-27.3</v>
+        <v>-26.47</v>
       </c>
       <c r="K82" t="n">
-        <v>123.78</v>
+        <v>120.01</v>
       </c>
       <c r="L82" t="n">
-        <v>126.75</v>
+        <v>122.9</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-65.68000000000001</v>
+        <v>-66.3</v>
       </c>
       <c r="K83" t="n">
-        <v>-127.19</v>
+        <v>-128.4</v>
       </c>
       <c r="L83" t="n">
-        <v>143.15</v>
+        <v>144.51</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>184.77</v>
+        <v>174.77</v>
       </c>
       <c r="K84" t="n">
-        <v>116.4</v>
+        <v>110.1</v>
       </c>
       <c r="L84" t="n">
-        <v>218.38</v>
+        <v>206.55</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-108.77</v>
+        <v>-111.78</v>
       </c>
       <c r="K85" t="n">
-        <v>79.83</v>
+        <v>82.03</v>
       </c>
       <c r="L85" t="n">
-        <v>134.92</v>
+        <v>138.65</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-183.01</v>
+        <v>-180.93</v>
       </c>
       <c r="K86" t="n">
-        <v>-110.24</v>
+        <v>-108.99</v>
       </c>
       <c r="L86" t="n">
-        <v>213.65</v>
+        <v>211.22</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>158.8</v>
+        <v>157.04</v>
       </c>
       <c r="K87" t="n">
-        <v>168.94</v>
+        <v>167.07</v>
       </c>
       <c r="L87" t="n">
-        <v>231.85</v>
+        <v>229.3</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>194.43</v>
+        <v>188.02</v>
       </c>
       <c r="K88" t="n">
-        <v>-174.53</v>
+        <v>-168.78</v>
       </c>
       <c r="L88" t="n">
-        <v>261.27</v>
+        <v>252.67</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -625,10 +625,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.03</v>
+        <v>2.85</v>
       </c>
       <c r="F14" t="n">
-        <v>9.99</v>
+        <v>6.49</v>
       </c>
       <c r="G14" t="n">
         <v>324.7</v>
@@ -637,22 +637,22 @@
         <v>25.8</v>
       </c>
       <c r="I14" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>2.18</v>
+        <v>-39.98</v>
       </c>
       <c r="K14" t="n">
-        <v>-51.83</v>
+        <v>12.65</v>
       </c>
       <c r="L14" t="n">
-        <v>51.88</v>
+        <v>41.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:31:15</t>
+          <t>05:31:38</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,10 +667,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.17</v>
+        <v>2.7</v>
       </c>
       <c r="F15" t="n">
-        <v>9.24</v>
+        <v>9.35</v>
       </c>
       <c r="G15" t="n">
         <v>328.2</v>
@@ -679,22 +679,22 @@
         <v>27.2</v>
       </c>
       <c r="I15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>38.74</v>
+        <v>43.88</v>
       </c>
       <c r="K15" t="n">
-        <v>10.04</v>
+        <v>29.57</v>
       </c>
       <c r="L15" t="n">
-        <v>40.02</v>
+        <v>52.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:33:43</t>
+          <t>05:33:16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,10 +709,10 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="F16" t="n">
-        <v>9.98</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>321.7</v>
@@ -721,22 +721,22 @@
         <v>25.2</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-49.79</v>
+        <v>98.09</v>
       </c>
       <c r="K16" t="n">
-        <v>-50.77</v>
+        <v>-42.87</v>
       </c>
       <c r="L16" t="n">
-        <v>71.11</v>
+        <v>107.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:38:21</t>
+          <t>05:37:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,10 +751,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="F17" t="n">
-        <v>9.51</v>
+        <v>6.63</v>
       </c>
       <c r="G17" t="n">
         <v>325</v>
@@ -763,22 +763,22 @@
         <v>28.8</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-43.41</v>
+        <v>-64.65000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>1.16</v>
+        <v>-16.92</v>
       </c>
       <c r="L17" t="n">
-        <v>43.43</v>
+        <v>66.81999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:40:05</t>
+          <t>05:39:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,10 +793,10 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.51</v>
+        <v>2.97</v>
       </c>
       <c r="F18" t="n">
-        <v>9.4</v>
+        <v>5.83</v>
       </c>
       <c r="G18" t="n">
         <v>329.7</v>
@@ -805,22 +805,22 @@
         <v>21.9</v>
       </c>
       <c r="I18" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-66.02</v>
+        <v>25.8</v>
       </c>
       <c r="K18" t="n">
-        <v>-51.84</v>
+        <v>-79.84999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>83.94</v>
+        <v>83.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:42:21</t>
+          <t>05:40:54</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,10 +835,10 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.19</v>
+        <v>2.54</v>
       </c>
       <c r="F19" t="n">
-        <v>8.94</v>
+        <v>2.84</v>
       </c>
       <c r="G19" t="n">
         <v>330.3</v>
@@ -847,22 +847,22 @@
         <v>19.1</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>116.79</v>
+        <v>35.16</v>
       </c>
       <c r="K19" t="n">
-        <v>-82.01000000000001</v>
+        <v>112.78</v>
       </c>
       <c r="L19" t="n">
-        <v>142.71</v>
+        <v>118.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:47:01</t>
+          <t>05:44:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.21</v>
+        <v>2.32</v>
       </c>
       <c r="F20" t="n">
-        <v>9.220000000000001</v>
+        <v>3.06</v>
       </c>
       <c r="G20" t="n">
-        <v>327</v>
+        <v>321.9</v>
       </c>
       <c r="H20" t="n">
-        <v>23.9</v>
+        <v>28.1</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-78.31999999999999</v>
+        <v>-75.54000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>69.47</v>
+        <v>67.47</v>
       </c>
       <c r="L20" t="n">
-        <v>104.69</v>
+        <v>101.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:48:41</t>
+          <t>05:46:48</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="F21" t="n">
-        <v>9.27</v>
+        <v>6.09</v>
       </c>
       <c r="G21" t="n">
-        <v>336.4</v>
+        <v>323.1</v>
       </c>
       <c r="H21" t="n">
-        <v>20.8</v>
+        <v>32.8</v>
       </c>
       <c r="I21" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>79.53</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-49.21</v>
+        <v>-52.35</v>
       </c>
       <c r="L21" t="n">
-        <v>93.53</v>
+        <v>102.21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:50:06</t>
+          <t>05:47:46</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="F22" t="n">
-        <v>9.369999999999999</v>
+        <v>10.44</v>
       </c>
       <c r="G22" t="n">
-        <v>327.1</v>
+        <v>325</v>
       </c>
       <c r="H22" t="n">
-        <v>32.5</v>
+        <v>28.2</v>
       </c>
       <c r="I22" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-6.77</v>
+        <v>-12.99</v>
       </c>
       <c r="K22" t="n">
-        <v>102.25</v>
+        <v>121.38</v>
       </c>
       <c r="L22" t="n">
-        <v>102.47</v>
+        <v>122.07</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:53:25</t>
+          <t>05:52:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>7.04</v>
       </c>
       <c r="G23" t="n">
-        <v>312.4</v>
+        <v>317.6</v>
       </c>
       <c r="H23" t="n">
-        <v>24.2</v>
+        <v>20.8</v>
       </c>
       <c r="I23" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-40.72</v>
+        <v>-61.48</v>
       </c>
       <c r="K23" t="n">
-        <v>109.81</v>
+        <v>137.51</v>
       </c>
       <c r="L23" t="n">
-        <v>117.11</v>
+        <v>150.63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:54:41</t>
+          <t>05:53:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1048,31 +1048,31 @@
         <v>2.29</v>
       </c>
       <c r="F24" t="n">
-        <v>9.369999999999999</v>
+        <v>5.79</v>
       </c>
       <c r="G24" t="n">
-        <v>319.7</v>
+        <v>325</v>
       </c>
       <c r="H24" t="n">
-        <v>25.8</v>
+        <v>24.5</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-155.48</v>
+        <v>-167.08</v>
       </c>
       <c r="K24" t="n">
-        <v>70.42</v>
+        <v>82.61</v>
       </c>
       <c r="L24" t="n">
-        <v>170.69</v>
+        <v>186.39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:56:23</t>
+          <t>05:54:21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="F25" t="n">
-        <v>9.949999999999999</v>
+        <v>6.59</v>
       </c>
       <c r="G25" t="n">
-        <v>325.4</v>
+        <v>336.5</v>
       </c>
       <c r="H25" t="n">
-        <v>20.5</v>
+        <v>27.3</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-150.74</v>
+        <v>-156.19</v>
       </c>
       <c r="K25" t="n">
-        <v>33.28</v>
+        <v>53.88</v>
       </c>
       <c r="L25" t="n">
-        <v>154.37</v>
+        <v>165.23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:01:02</t>
+          <t>05:59:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="F26" t="n">
-        <v>9.52</v>
+        <v>9.08</v>
       </c>
       <c r="G26" t="n">
-        <v>299.7</v>
+        <v>328</v>
       </c>
       <c r="H26" t="n">
-        <v>28.8</v>
+        <v>14.5</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-202.86</v>
+        <v>-248.99</v>
       </c>
       <c r="K26" t="n">
-        <v>-14.95</v>
+        <v>22.98</v>
       </c>
       <c r="L26" t="n">
-        <v>203.41</v>
+        <v>250.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:02:28</t>
+          <t>06:00:38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="F27" t="n">
-        <v>8.949999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>324</v>
+        <v>316.7</v>
       </c>
       <c r="H27" t="n">
-        <v>29.5</v>
+        <v>26.6</v>
       </c>
       <c r="I27" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>118.95</v>
+        <v>122.98</v>
       </c>
       <c r="K27" t="n">
-        <v>-176.34</v>
+        <v>-199.64</v>
       </c>
       <c r="L27" t="n">
-        <v>212.71</v>
+        <v>234.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:04:46</t>
+          <t>06:01:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="F28" t="n">
-        <v>9.24</v>
+        <v>8.82</v>
       </c>
       <c r="G28" t="n">
-        <v>309.9</v>
+        <v>322.4</v>
       </c>
       <c r="H28" t="n">
-        <v>26</v>
+        <v>19.6</v>
       </c>
       <c r="I28" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-197.51</v>
+        <v>-238.73</v>
       </c>
       <c r="K28" t="n">
-        <v>81.67</v>
+        <v>123.19</v>
       </c>
       <c r="L28" t="n">
-        <v>213.73</v>
+        <v>268.64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:12:26</t>
+          <t>06:14:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="F29" t="n">
-        <v>9.949999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="G29" t="n">
-        <v>326.4</v>
+        <v>336.6</v>
       </c>
       <c r="H29" t="n">
-        <v>17.6</v>
+        <v>27.8</v>
       </c>
       <c r="I29" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>33.44</v>
+        <v>48.54</v>
       </c>
       <c r="K29" t="n">
-        <v>-25.05</v>
+        <v>-34.39</v>
       </c>
       <c r="L29" t="n">
-        <v>41.78</v>
+        <v>59.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:13:28</t>
+          <t>06:16:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F30" t="n">
-        <v>9.6</v>
+        <v>8.75</v>
       </c>
       <c r="G30" t="n">
-        <v>317.1</v>
+        <v>329.7</v>
       </c>
       <c r="H30" t="n">
-        <v>28.6</v>
+        <v>23.2</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.45</v>
+        <v>-4.11</v>
       </c>
       <c r="K30" t="n">
-        <v>-59.9</v>
+        <v>-66.8</v>
       </c>
       <c r="L30" t="n">
-        <v>60</v>
+        <v>66.93000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:15:03</t>
+          <t>06:17:06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1342,31 +1342,31 @@
         <v>2.7</v>
       </c>
       <c r="F31" t="n">
-        <v>9.630000000000001</v>
+        <v>7.17</v>
       </c>
       <c r="G31" t="n">
-        <v>319.3</v>
+        <v>330.2</v>
       </c>
       <c r="H31" t="n">
-        <v>29.9</v>
+        <v>24.3</v>
       </c>
       <c r="I31" t="n">
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-43.55</v>
+        <v>-47.63</v>
       </c>
       <c r="K31" t="n">
-        <v>-22.54</v>
+        <v>-23.56</v>
       </c>
       <c r="L31" t="n">
-        <v>49.04</v>
+        <v>53.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:19:29</t>
+          <t>06:21:41</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="F32" t="n">
-        <v>9.09</v>
+        <v>7.29</v>
       </c>
       <c r="G32" t="n">
-        <v>328.8</v>
+        <v>319.3</v>
       </c>
       <c r="H32" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-15.15</v>
+        <v>-19.35</v>
       </c>
       <c r="K32" t="n">
-        <v>68.11</v>
+        <v>80.06</v>
       </c>
       <c r="L32" t="n">
-        <v>69.78</v>
+        <v>82.36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:20:33</t>
+          <t>06:22:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="F33" t="n">
-        <v>9.44</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>336.7</v>
+        <v>327.6</v>
       </c>
       <c r="H33" t="n">
-        <v>28.4</v>
+        <v>26.8</v>
       </c>
       <c r="I33" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>38.01</v>
+        <v>29.22</v>
       </c>
       <c r="K33" t="n">
-        <v>-60.37</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>71.34</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:21:52</t>
+          <t>06:23:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.83</v>
+        <v>3.34</v>
       </c>
       <c r="F34" t="n">
-        <v>9.42</v>
+        <v>7.41</v>
       </c>
       <c r="G34" t="n">
-        <v>330</v>
+        <v>312.9</v>
       </c>
       <c r="H34" t="n">
-        <v>21.1</v>
+        <v>22.1</v>
       </c>
       <c r="I34" t="n">
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-96</v>
+        <v>45.92</v>
       </c>
       <c r="K34" t="n">
-        <v>76.70999999999999</v>
+        <v>27.35</v>
       </c>
       <c r="L34" t="n">
-        <v>122.88</v>
+        <v>53.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:26:11</t>
+          <t>06:28:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.87</v>
+        <v>2.37</v>
       </c>
       <c r="F35" t="n">
-        <v>9.44</v>
+        <v>4.92</v>
       </c>
       <c r="G35" t="n">
-        <v>306</v>
+        <v>317.1</v>
       </c>
       <c r="H35" t="n">
-        <v>23.2</v>
+        <v>20.6</v>
       </c>
       <c r="I35" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-72.19</v>
+        <v>25.32</v>
       </c>
       <c r="K35" t="n">
-        <v>-85.02</v>
+        <v>-95.78</v>
       </c>
       <c r="L35" t="n">
-        <v>111.53</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:28:31</t>
+          <t>06:30:32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.37</v>
+        <v>2.83</v>
       </c>
       <c r="F36" t="n">
-        <v>9.390000000000001</v>
+        <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>318.1</v>
+        <v>338.1</v>
       </c>
       <c r="H36" t="n">
-        <v>33.6</v>
+        <v>29.2</v>
       </c>
       <c r="I36" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-52.24</v>
+        <v>15.64</v>
       </c>
       <c r="K36" t="n">
-        <v>-61.16</v>
+        <v>-114.64</v>
       </c>
       <c r="L36" t="n">
-        <v>80.44</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:30:54</t>
+          <t>06:31:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.29</v>
+        <v>3.05</v>
       </c>
       <c r="F37" t="n">
-        <v>9.279999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="G37" t="n">
-        <v>331.6</v>
+        <v>316.9</v>
       </c>
       <c r="H37" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="I37" t="n">
         <v>23</v>
       </c>
-      <c r="I37" t="n">
-        <v>26</v>
-      </c>
       <c r="J37" t="n">
-        <v>-76.8</v>
+        <v>-51.5</v>
       </c>
       <c r="K37" t="n">
-        <v>-50.24</v>
+        <v>-56.05</v>
       </c>
       <c r="L37" t="n">
-        <v>91.77</v>
+        <v>76.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:35:06</t>
+          <t>06:36:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.68</v>
+        <v>2.95</v>
       </c>
       <c r="F38" t="n">
-        <v>10.28</v>
+        <v>10.7</v>
       </c>
       <c r="G38" t="n">
-        <v>321.5</v>
+        <v>325</v>
       </c>
       <c r="H38" t="n">
-        <v>27.1</v>
+        <v>27.6</v>
       </c>
       <c r="I38" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-114.34</v>
+        <v>219.42</v>
       </c>
       <c r="K38" t="n">
-        <v>-23.74</v>
+        <v>150.52</v>
       </c>
       <c r="L38" t="n">
-        <v>116.78</v>
+        <v>266.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:37:32</t>
+          <t>06:37:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="F39" t="n">
-        <v>8.77</v>
+        <v>7.69</v>
       </c>
       <c r="G39" t="n">
-        <v>335.2</v>
+        <v>327.1</v>
       </c>
       <c r="H39" t="n">
-        <v>28.2</v>
+        <v>23.6</v>
       </c>
       <c r="I39" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-92.43000000000001</v>
+        <v>-152.46</v>
       </c>
       <c r="K39" t="n">
-        <v>-57.93</v>
+        <v>-89.56999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>109.08</v>
+        <v>176.82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:39:20</t>
+          <t>06:39:42</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,10 +1717,10 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.77</v>
+        <v>3.71</v>
       </c>
       <c r="F40" t="n">
-        <v>9.19</v>
+        <v>10.7</v>
       </c>
       <c r="G40" t="n">
         <v>321.5</v>
@@ -1729,22 +1729,22 @@
         <v>30.2</v>
       </c>
       <c r="I40" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>97.08</v>
+        <v>-194.62</v>
       </c>
       <c r="K40" t="n">
-        <v>83.8</v>
+        <v>124.7</v>
       </c>
       <c r="L40" t="n">
-        <v>128.25</v>
+        <v>231.14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:44:03</t>
+          <t>06:45:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.57</v>
+        <v>3.34</v>
       </c>
       <c r="F41" t="n">
-        <v>8.710000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="G41" t="n">
-        <v>330.7</v>
+        <v>325</v>
       </c>
       <c r="H41" t="n">
-        <v>27.1</v>
+        <v>25.8</v>
       </c>
       <c r="I41" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-20.27</v>
+        <v>-244.58</v>
       </c>
       <c r="K41" t="n">
-        <v>-172.35</v>
+        <v>153.07</v>
       </c>
       <c r="L41" t="n">
-        <v>173.54</v>
+        <v>288.53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:46:13</t>
+          <t>06:46:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.58</v>
+        <v>3.19</v>
       </c>
       <c r="F42" t="n">
-        <v>9.44</v>
+        <v>5.25</v>
       </c>
       <c r="G42" t="n">
-        <v>337</v>
+        <v>335.2</v>
       </c>
       <c r="H42" t="n">
-        <v>32.2</v>
+        <v>25.9</v>
       </c>
       <c r="I42" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-15.13</v>
+        <v>20.39</v>
       </c>
       <c r="K42" t="n">
-        <v>174.9</v>
+        <v>252.71</v>
       </c>
       <c r="L42" t="n">
-        <v>175.55</v>
+        <v>253.53</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:47:20</t>
+          <t>06:49:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.06</v>
+        <v>3.19</v>
       </c>
       <c r="F43" t="n">
-        <v>9.039999999999999</v>
+        <v>8.01</v>
       </c>
       <c r="G43" t="n">
-        <v>333.9</v>
+        <v>307.1</v>
       </c>
       <c r="H43" t="n">
-        <v>18.2</v>
+        <v>23.7</v>
       </c>
       <c r="I43" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-172.85</v>
+        <v>-168.68</v>
       </c>
       <c r="K43" t="n">
-        <v>-9.58</v>
+        <v>-98.34999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>173.12</v>
+        <v>195.26</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:56:28</t>
+          <t>07:00:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.75</v>
+        <v>2.89</v>
       </c>
       <c r="F44" t="n">
-        <v>8.890000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G44" t="n">
-        <v>320.8</v>
+        <v>310.3</v>
       </c>
       <c r="H44" t="n">
-        <v>19.8</v>
+        <v>34.8</v>
       </c>
       <c r="I44" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>21.43</v>
+        <v>-55.22</v>
       </c>
       <c r="K44" t="n">
-        <v>-48.99</v>
+        <v>52.6</v>
       </c>
       <c r="L44" t="n">
-        <v>53.47</v>
+        <v>76.26000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:57:43</t>
+          <t>07:02:26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="F45" t="n">
-        <v>8.23</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H45" t="n">
-        <v>28.6</v>
+        <v>32.9</v>
       </c>
       <c r="I45" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>75.97</v>
+        <v>-111.29</v>
       </c>
       <c r="K45" t="n">
-        <v>49.4</v>
+        <v>-1.26</v>
       </c>
       <c r="L45" t="n">
-        <v>90.62</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:59:56</t>
+          <t>07:05:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.69</v>
+        <v>3.87</v>
       </c>
       <c r="F46" t="n">
-        <v>9.4</v>
+        <v>7.64</v>
       </c>
       <c r="G46" t="n">
-        <v>337.3</v>
+        <v>314</v>
       </c>
       <c r="H46" t="n">
-        <v>21.6</v>
+        <v>25.1</v>
       </c>
       <c r="I46" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>18.51</v>
+        <v>16.2</v>
       </c>
       <c r="K46" t="n">
-        <v>-41.71</v>
+        <v>-56.98</v>
       </c>
       <c r="L46" t="n">
-        <v>45.63</v>
+        <v>59.24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:04:31</t>
+          <t>07:08:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="F47" t="n">
-        <v>8.52</v>
+        <v>7.3</v>
       </c>
       <c r="G47" t="n">
-        <v>330.4</v>
+        <v>308.1</v>
       </c>
       <c r="H47" t="n">
-        <v>26.5</v>
+        <v>29.8</v>
       </c>
       <c r="I47" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>46.44</v>
+        <v>48.1</v>
       </c>
       <c r="K47" t="n">
-        <v>-66.45</v>
+        <v>-71.29000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>81.06999999999999</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:05:52</t>
+          <t>07:10:37</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="F48" t="n">
-        <v>9.23</v>
+        <v>10.7</v>
       </c>
       <c r="G48" t="n">
-        <v>321.8</v>
+        <v>322.2</v>
       </c>
       <c r="H48" t="n">
-        <v>33.3</v>
+        <v>25.5</v>
       </c>
       <c r="I48" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-72.88</v>
+        <v>-92.83</v>
       </c>
       <c r="K48" t="n">
-        <v>-10.18</v>
+        <v>-10.44</v>
       </c>
       <c r="L48" t="n">
-        <v>73.59</v>
+        <v>93.42</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:07:18</t>
+          <t>07:12:19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="F49" t="n">
-        <v>9.35</v>
+        <v>10.19</v>
       </c>
       <c r="G49" t="n">
-        <v>317.6</v>
+        <v>324.7</v>
       </c>
       <c r="H49" t="n">
-        <v>28.6</v>
+        <v>23.4</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-63.09</v>
+        <v>-72.42</v>
       </c>
       <c r="K49" t="n">
-        <v>12.77</v>
+        <v>17.28</v>
       </c>
       <c r="L49" t="n">
-        <v>64.37</v>
+        <v>74.45</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:11:22</t>
+          <t>07:17:54</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="F50" t="n">
-        <v>8.99</v>
+        <v>6.29</v>
       </c>
       <c r="G50" t="n">
-        <v>334.9</v>
+        <v>317.4</v>
       </c>
       <c r="H50" t="n">
-        <v>19.9</v>
+        <v>32</v>
       </c>
       <c r="I50" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-66.3</v>
+        <v>-85.75</v>
       </c>
       <c r="K50" t="n">
-        <v>-56.05</v>
+        <v>-54.36</v>
       </c>
       <c r="L50" t="n">
-        <v>86.81999999999999</v>
+        <v>101.52</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:13:37</t>
+          <t>07:19:05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="F51" t="n">
-        <v>9.300000000000001</v>
+        <v>10.61</v>
       </c>
       <c r="G51" t="n">
-        <v>321.3</v>
+        <v>323.5</v>
       </c>
       <c r="H51" t="n">
-        <v>29.4</v>
+        <v>25.2</v>
       </c>
       <c r="I51" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>77.94</v>
+        <v>93.17</v>
       </c>
       <c r="K51" t="n">
-        <v>-57.3</v>
+        <v>-61.99</v>
       </c>
       <c r="L51" t="n">
-        <v>96.73999999999999</v>
+        <v>111.91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:15:10</t>
+          <t>07:19:43</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="F52" t="n">
-        <v>9.31</v>
+        <v>10.52</v>
       </c>
       <c r="G52" t="n">
-        <v>329.7</v>
+        <v>323.8</v>
       </c>
       <c r="H52" t="n">
-        <v>26.5</v>
+        <v>29.4</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-8.109999999999999</v>
+        <v>-19.22</v>
       </c>
       <c r="K52" t="n">
-        <v>103.34</v>
+        <v>125.02</v>
       </c>
       <c r="L52" t="n">
-        <v>103.65</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:19:30</t>
+          <t>07:24:02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="F53" t="n">
-        <v>10.02</v>
+        <v>8.76</v>
       </c>
       <c r="G53" t="n">
-        <v>322.8</v>
+        <v>338.1</v>
       </c>
       <c r="H53" t="n">
-        <v>29.9</v>
+        <v>26</v>
       </c>
       <c r="I53" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-93.28</v>
+        <v>-106.7</v>
       </c>
       <c r="K53" t="n">
-        <v>-24.27</v>
+        <v>38.62</v>
       </c>
       <c r="L53" t="n">
-        <v>96.38</v>
+        <v>113.47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:20:38</t>
+          <t>07:25:56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="F54" t="n">
-        <v>9.289999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="G54" t="n">
-        <v>332.7</v>
+        <v>323.3</v>
       </c>
       <c r="H54" t="n">
-        <v>24.3</v>
+        <v>30.9</v>
       </c>
       <c r="I54" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>96.78</v>
+        <v>98.38</v>
       </c>
       <c r="K54" t="n">
-        <v>135.37</v>
+        <v>169.07</v>
       </c>
       <c r="L54" t="n">
-        <v>166.41</v>
+        <v>195.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:22:04</t>
+          <t>07:27:35</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="F55" t="n">
-        <v>9.19</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>325.5</v>
+        <v>321.5</v>
       </c>
       <c r="H55" t="n">
-        <v>33.7</v>
+        <v>27.4</v>
       </c>
       <c r="I55" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>124.4</v>
+        <v>146.62</v>
       </c>
       <c r="K55" t="n">
-        <v>-61.44</v>
+        <v>-51.63</v>
       </c>
       <c r="L55" t="n">
-        <v>138.74</v>
+        <v>155.44</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:26:17</t>
+          <t>07:31:27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="F56" t="n">
-        <v>8.85</v>
+        <v>7.64</v>
       </c>
       <c r="G56" t="n">
-        <v>323.7</v>
+        <v>314.7</v>
       </c>
       <c r="H56" t="n">
-        <v>21.8</v>
+        <v>26.4</v>
       </c>
       <c r="I56" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-122.4</v>
+        <v>-161.04</v>
       </c>
       <c r="K56" t="n">
-        <v>113.08</v>
+        <v>144.14</v>
       </c>
       <c r="L56" t="n">
-        <v>166.64</v>
+        <v>216.12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:27:11</t>
+          <t>07:32:54</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="F57" t="n">
-        <v>9.75</v>
+        <v>9.24</v>
       </c>
       <c r="G57" t="n">
-        <v>327</v>
+        <v>332.7</v>
       </c>
       <c r="H57" t="n">
-        <v>21.8</v>
+        <v>28.1</v>
       </c>
       <c r="I57" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-67.17</v>
+        <v>-93.47</v>
       </c>
       <c r="K57" t="n">
-        <v>117.7</v>
+        <v>176.46</v>
       </c>
       <c r="L57" t="n">
-        <v>135.51</v>
+        <v>199.68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:29:09</t>
+          <t>07:34:58</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="F58" t="n">
-        <v>9.25</v>
+        <v>10.7</v>
       </c>
       <c r="G58" t="n">
         <v>322.6</v>
       </c>
       <c r="H58" t="n">
-        <v>38.8</v>
+        <v>25.9</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>197.43</v>
+        <v>215.07</v>
       </c>
       <c r="K58" t="n">
-        <v>136.5</v>
+        <v>198.26</v>
       </c>
       <c r="L58" t="n">
-        <v>240.03</v>
+        <v>292.51</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:37:57</t>
+          <t>07:43:48</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="F59" t="n">
-        <v>9.41</v>
+        <v>10.7</v>
       </c>
       <c r="G59" t="n">
-        <v>314.4</v>
+        <v>325.9</v>
       </c>
       <c r="H59" t="n">
-        <v>28.9</v>
+        <v>21.8</v>
       </c>
       <c r="I59" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>47.97</v>
+        <v>57.98</v>
       </c>
       <c r="K59" t="n">
-        <v>-37.08</v>
+        <v>-44.29</v>
       </c>
       <c r="L59" t="n">
-        <v>60.63</v>
+        <v>72.95999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:39:17</t>
+          <t>07:45:45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="F60" t="n">
-        <v>9.34</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>335.5</v>
+        <v>324.4</v>
       </c>
       <c r="H60" t="n">
-        <v>24.2</v>
+        <v>32.3</v>
       </c>
       <c r="I60" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-42.69</v>
+        <v>-47.61</v>
       </c>
       <c r="K60" t="n">
-        <v>-68.3</v>
+        <v>-74.69</v>
       </c>
       <c r="L60" t="n">
-        <v>80.55</v>
+        <v>88.56999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:40:44</t>
+          <t>07:47:54</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="F61" t="n">
-        <v>9.01</v>
+        <v>10.23</v>
       </c>
       <c r="G61" t="n">
-        <v>336.2</v>
+        <v>317.9</v>
       </c>
       <c r="H61" t="n">
-        <v>24.2</v>
+        <v>32.7</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-50.6</v>
+        <v>-54.41</v>
       </c>
       <c r="K61" t="n">
-        <v>47</v>
+        <v>50.18</v>
       </c>
       <c r="L61" t="n">
-        <v>69.06</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:45:19</t>
+          <t>07:53:25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="F62" t="n">
-        <v>8.720000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G62" t="n">
-        <v>333.7</v>
+        <v>312</v>
       </c>
       <c r="H62" t="n">
-        <v>25</v>
+        <v>31.5</v>
       </c>
       <c r="I62" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>75.17</v>
+        <v>89.19</v>
       </c>
       <c r="K62" t="n">
-        <v>7.67</v>
+        <v>11.31</v>
       </c>
       <c r="L62" t="n">
-        <v>75.56</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:47:26</t>
+          <t>07:54:24</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="F63" t="n">
-        <v>8.93</v>
+        <v>10.7</v>
       </c>
       <c r="G63" t="n">
-        <v>319.3</v>
+        <v>316.2</v>
       </c>
       <c r="H63" t="n">
-        <v>26.2</v>
+        <v>24.3</v>
       </c>
       <c r="I63" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-81.03</v>
+        <v>-90.34999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-12.71</v>
+        <v>-11.87</v>
       </c>
       <c r="L63" t="n">
-        <v>82.02</v>
+        <v>91.12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:48:32</t>
+          <t>07:57:06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="F64" t="n">
-        <v>9.25</v>
+        <v>10.29</v>
       </c>
       <c r="G64" t="n">
-        <v>344.1</v>
+        <v>322.6</v>
       </c>
       <c r="H64" t="n">
-        <v>27.5</v>
+        <v>36.7</v>
       </c>
       <c r="I64" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>69.06999999999999</v>
+        <v>75.33</v>
       </c>
       <c r="K64" t="n">
-        <v>19.26</v>
+        <v>24.06</v>
       </c>
       <c r="L64" t="n">
-        <v>71.70999999999999</v>
+        <v>79.08</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:54:43</t>
+          <t>08:01:30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.49</v>
+        <v>4.51</v>
       </c>
       <c r="F65" t="n">
-        <v>9.449999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="G65" t="n">
-        <v>308.9</v>
+        <v>326.6</v>
       </c>
       <c r="H65" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="I65" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>125.18</v>
+        <v>130.08</v>
       </c>
       <c r="K65" t="n">
-        <v>10.67</v>
+        <v>30.9</v>
       </c>
       <c r="L65" t="n">
-        <v>125.64</v>
+        <v>133.69</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:55:48</t>
+          <t>08:02:46</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="F66" t="n">
-        <v>8.91</v>
+        <v>10.67</v>
       </c>
       <c r="G66" t="n">
-        <v>317.2</v>
+        <v>315.7</v>
       </c>
       <c r="H66" t="n">
-        <v>28.9</v>
+        <v>23.2</v>
       </c>
       <c r="I66" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>63.17</v>
+        <v>61.9</v>
       </c>
       <c r="K66" t="n">
-        <v>-36.94</v>
+        <v>-25.68</v>
       </c>
       <c r="L66" t="n">
-        <v>73.18000000000001</v>
+        <v>67.01000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:56:55</t>
+          <t>08:04:22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="F67" t="n">
-        <v>9.07</v>
+        <v>10.7</v>
       </c>
       <c r="G67" t="n">
-        <v>340.2</v>
+        <v>319</v>
       </c>
       <c r="H67" t="n">
-        <v>23.1</v>
+        <v>34.7</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-24.03</v>
+        <v>-41.08</v>
       </c>
       <c r="K67" t="n">
-        <v>97.77</v>
+        <v>119.67</v>
       </c>
       <c r="L67" t="n">
-        <v>100.68</v>
+        <v>126.53</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:02:03</t>
+          <t>08:09:19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="F68" t="n">
-        <v>10.04</v>
+        <v>9.1</v>
       </c>
       <c r="G68" t="n">
-        <v>332.2</v>
+        <v>338.4</v>
       </c>
       <c r="H68" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="I68" t="n">
         <v>23</v>
       </c>
-      <c r="I68" t="n">
-        <v>26</v>
-      </c>
       <c r="J68" t="n">
-        <v>-7.72</v>
+        <v>-38.65</v>
       </c>
       <c r="K68" t="n">
-        <v>-111.61</v>
+        <v>-62.24</v>
       </c>
       <c r="L68" t="n">
-        <v>111.87</v>
+        <v>73.27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:04:10</t>
+          <t>08:10:27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="F69" t="n">
-        <v>9.550000000000001</v>
+        <v>7.94</v>
       </c>
       <c r="G69" t="n">
-        <v>336.5</v>
+        <v>328.6</v>
       </c>
       <c r="H69" t="n">
-        <v>22.6</v>
+        <v>32.8</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-102.97</v>
+        <v>-110.68</v>
       </c>
       <c r="K69" t="n">
-        <v>49.22</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>114.13</v>
+        <v>133.24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:06:07</t>
+          <t>08:12:22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="F70" t="n">
-        <v>9.43</v>
+        <v>6.39</v>
       </c>
       <c r="G70" t="n">
-        <v>329.1</v>
+        <v>326.2</v>
       </c>
       <c r="H70" t="n">
-        <v>19.3</v>
+        <v>29.1</v>
       </c>
       <c r="I70" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-61.76</v>
+        <v>-98.51000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>-108.37</v>
+        <v>-104.36</v>
       </c>
       <c r="L70" t="n">
-        <v>124.74</v>
+        <v>143.51</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:10:04</t>
+          <t>08:16:06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="F71" t="n">
-        <v>8.699999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G71" t="n">
-        <v>335.5</v>
+        <v>311.6</v>
       </c>
       <c r="H71" t="n">
-        <v>34.7</v>
+        <v>32.3</v>
       </c>
       <c r="I71" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>134.94</v>
+        <v>72.09</v>
       </c>
       <c r="K71" t="n">
-        <v>36.26</v>
+        <v>115.09</v>
       </c>
       <c r="L71" t="n">
-        <v>139.73</v>
+        <v>135.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:11:18</t>
+          <t>08:18:39</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="F72" t="n">
-        <v>9.199999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>338.9</v>
+        <v>321.6</v>
       </c>
       <c r="H72" t="n">
-        <v>26.4</v>
+        <v>34.1</v>
       </c>
       <c r="I72" t="n">
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-182.54</v>
+        <v>-210.31</v>
       </c>
       <c r="K72" t="n">
-        <v>-122.92</v>
+        <v>-99.15000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>220.07</v>
+        <v>232.51</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:13:42</t>
+          <t>08:20:10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="F73" t="n">
-        <v>9.23</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>312.5</v>
+        <v>322.2</v>
       </c>
       <c r="H73" t="n">
-        <v>26.5</v>
+        <v>20.9</v>
       </c>
       <c r="I73" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-152.91</v>
+        <v>-184.63</v>
       </c>
       <c r="K73" t="n">
-        <v>-34.28</v>
+        <v>18.2</v>
       </c>
       <c r="L73" t="n">
-        <v>156.7</v>
+        <v>185.52</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:24:05</t>
+          <t>08:33:10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="F74" t="n">
-        <v>8.9</v>
+        <v>10.7</v>
       </c>
       <c r="G74" t="n">
-        <v>324.2</v>
+        <v>315.6</v>
       </c>
       <c r="H74" t="n">
-        <v>33.4</v>
+        <v>26.7</v>
       </c>
       <c r="I74" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-62.38</v>
+        <v>-75.89</v>
       </c>
       <c r="K74" t="n">
-        <v>-38.54</v>
+        <v>-45.98</v>
       </c>
       <c r="L74" t="n">
-        <v>73.33</v>
+        <v>88.73</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:26:25</t>
+          <t>08:34:25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="F75" t="n">
-        <v>9.56</v>
+        <v>10.7</v>
       </c>
       <c r="G75" t="n">
-        <v>323.3</v>
+        <v>328.7</v>
       </c>
       <c r="H75" t="n">
-        <v>26</v>
+        <v>26.3</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>25.05</v>
+        <v>26.33</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.47</v>
+        <v>-0.9</v>
       </c>
       <c r="L75" t="n">
-        <v>25.29</v>
+        <v>26.35</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:28:25</t>
+          <t>08:36:13</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="F76" t="n">
-        <v>9.199999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>333.5</v>
+        <v>321.5</v>
       </c>
       <c r="H76" t="n">
-        <v>21.9</v>
+        <v>31.4</v>
       </c>
       <c r="I76" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>27.77</v>
+        <v>29.58</v>
       </c>
       <c r="K76" t="n">
-        <v>-26.66</v>
+        <v>-29.14</v>
       </c>
       <c r="L76" t="n">
-        <v>38.5</v>
+        <v>41.52</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:32:26</t>
+          <t>08:40:24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="F77" t="n">
-        <v>9.609999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G77" t="n">
-        <v>332.3</v>
+        <v>329.9</v>
       </c>
       <c r="H77" t="n">
-        <v>30</v>
+        <v>30.8</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>58.41</v>
+        <v>62.62</v>
       </c>
       <c r="K77" t="n">
-        <v>21</v>
+        <v>28.4</v>
       </c>
       <c r="L77" t="n">
-        <v>62.07</v>
+        <v>68.76000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:33:33</t>
+          <t>08:42:43</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="F78" t="n">
-        <v>9.949999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G78" t="n">
-        <v>337.4</v>
+        <v>336.6</v>
       </c>
       <c r="H78" t="n">
-        <v>26.5</v>
+        <v>33.3</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-26.35</v>
+        <v>-28.54</v>
       </c>
       <c r="K78" t="n">
-        <v>84.18000000000001</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>88.20999999999999</v>
+        <v>94.43000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:35:39</t>
+          <t>08:44:58</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="F79" t="n">
-        <v>9.029999999999999</v>
+        <v>10.48</v>
       </c>
       <c r="G79" t="n">
-        <v>323.4</v>
+        <v>318.3</v>
       </c>
       <c r="H79" t="n">
-        <v>27.7</v>
+        <v>26.3</v>
       </c>
       <c r="I79" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>30.59</v>
+        <v>36.28</v>
       </c>
       <c r="K79" t="n">
-        <v>-43.5</v>
+        <v>-54.58</v>
       </c>
       <c r="L79" t="n">
-        <v>53.18</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:41:27</t>
+          <t>08:48:56</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="F80" t="n">
-        <v>9.6</v>
+        <v>10.7</v>
       </c>
       <c r="G80" t="n">
-        <v>321.4</v>
+        <v>329.6</v>
       </c>
       <c r="H80" t="n">
-        <v>30.3</v>
+        <v>25.3</v>
       </c>
       <c r="I80" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>-99.26000000000001</v>
+        <v>-122.88</v>
       </c>
       <c r="K80" t="n">
-        <v>57.2</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>114.56</v>
+        <v>146.28</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:43:05</t>
+          <t>08:49:41</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="F81" t="n">
-        <v>9.369999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G81" t="n">
-        <v>325.6</v>
+        <v>324.9</v>
       </c>
       <c r="H81" t="n">
-        <v>29.2</v>
+        <v>27.4</v>
       </c>
       <c r="I81" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-112.64</v>
+        <v>-145.76</v>
       </c>
       <c r="K81" t="n">
-        <v>-50.4</v>
+        <v>-54.09</v>
       </c>
       <c r="L81" t="n">
-        <v>123.4</v>
+        <v>155.47</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:45:01</t>
+          <t>08:51:09</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="F82" t="n">
-        <v>9.210000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>321.6</v>
+        <v>321.9</v>
       </c>
       <c r="H82" t="n">
-        <v>24.2</v>
+        <v>25.4</v>
       </c>
       <c r="I82" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-26.47</v>
+        <v>-34.03</v>
       </c>
       <c r="K82" t="n">
-        <v>120.01</v>
+        <v>135.57</v>
       </c>
       <c r="L82" t="n">
-        <v>122.9</v>
+        <v>139.78</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:48:37</t>
+          <t>08:57:12</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="F83" t="n">
-        <v>8.99</v>
+        <v>10.7</v>
       </c>
       <c r="G83" t="n">
-        <v>317.5</v>
+        <v>317.4</v>
       </c>
       <c r="H83" t="n">
-        <v>26.3</v>
+        <v>23.3</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-66.3</v>
+        <v>-98.22</v>
       </c>
       <c r="K83" t="n">
-        <v>-128.4</v>
+        <v>-115.8</v>
       </c>
       <c r="L83" t="n">
-        <v>144.51</v>
+        <v>151.84</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:50:45</t>
+          <t>08:59:06</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="F84" t="n">
-        <v>9.65</v>
+        <v>7.12</v>
       </c>
       <c r="G84" t="n">
-        <v>323.3</v>
+        <v>330.5</v>
       </c>
       <c r="H84" t="n">
-        <v>18.5</v>
+        <v>26.2</v>
       </c>
       <c r="I84" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>174.77</v>
+        <v>176.29</v>
       </c>
       <c r="K84" t="n">
-        <v>110.1</v>
+        <v>135.34</v>
       </c>
       <c r="L84" t="n">
-        <v>206.55</v>
+        <v>222.25</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:53:11</t>
+          <t>09:01:45</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="F85" t="n">
-        <v>9.08</v>
+        <v>10.7</v>
       </c>
       <c r="G85" t="n">
-        <v>331.4</v>
+        <v>319.1</v>
       </c>
       <c r="H85" t="n">
-        <v>27.1</v>
+        <v>30.3</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-111.78</v>
+        <v>-130.61</v>
       </c>
       <c r="K85" t="n">
-        <v>82.03</v>
+        <v>100.56</v>
       </c>
       <c r="L85" t="n">
-        <v>138.65</v>
+        <v>164.84</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:57:58</t>
+          <t>09:05:59</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="F86" t="n">
-        <v>8.529999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G86" t="n">
-        <v>322.5</v>
+        <v>308.2</v>
       </c>
       <c r="H86" t="n">
-        <v>28.1</v>
+        <v>25.8</v>
       </c>
       <c r="I86" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-180.93</v>
+        <v>-232.84</v>
       </c>
       <c r="K86" t="n">
-        <v>-108.99</v>
+        <v>-101.25</v>
       </c>
       <c r="L86" t="n">
-        <v>211.22</v>
+        <v>253.9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:59:55</t>
+          <t>09:08:23</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="F87" t="n">
-        <v>9.539999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G87" t="n">
-        <v>332.2</v>
+        <v>328.5</v>
       </c>
       <c r="H87" t="n">
-        <v>29.4</v>
+        <v>30.7</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>157.04</v>
+        <v>152.74</v>
       </c>
       <c r="K87" t="n">
-        <v>167.07</v>
+        <v>216.24</v>
       </c>
       <c r="L87" t="n">
-        <v>229.3</v>
+        <v>264.75</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:01:19</t>
+          <t>09:09:58</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="F88" t="n">
-        <v>9.18</v>
+        <v>6.98</v>
       </c>
       <c r="G88" t="n">
-        <v>321.3</v>
+        <v>321.2</v>
       </c>
       <c r="H88" t="n">
-        <v>17</v>
+        <v>25.2</v>
       </c>
       <c r="I88" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>188.02</v>
+        <v>190.96</v>
       </c>
       <c r="K88" t="n">
-        <v>-168.78</v>
+        <v>-164.6</v>
       </c>
       <c r="L88" t="n">
-        <v>252.67</v>
+        <v>252.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-39.98</v>
+        <v>-38.31</v>
       </c>
       <c r="K14" t="n">
-        <v>12.65</v>
+        <v>12.12</v>
       </c>
       <c r="L14" t="n">
-        <v>41.93</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>43.88</v>
+        <v>42.98</v>
       </c>
       <c r="K15" t="n">
-        <v>29.57</v>
+        <v>28.96</v>
       </c>
       <c r="L15" t="n">
-        <v>52.91</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>98.09</v>
+        <v>103.64</v>
       </c>
       <c r="K16" t="n">
-        <v>-42.87</v>
+        <v>-45.3</v>
       </c>
       <c r="L16" t="n">
-        <v>107.04</v>
+        <v>113.1</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-64.65000000000001</v>
+        <v>-67.13</v>
       </c>
       <c r="K17" t="n">
-        <v>-16.92</v>
+        <v>-17.57</v>
       </c>
       <c r="L17" t="n">
-        <v>66.81999999999999</v>
+        <v>69.39</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>25.8</v>
+        <v>24.72</v>
       </c>
       <c r="K18" t="n">
-        <v>-79.84999999999999</v>
+        <v>-76.53</v>
       </c>
       <c r="L18" t="n">
-        <v>83.92</v>
+        <v>80.42</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>35.16</v>
+        <v>37.77</v>
       </c>
       <c r="K19" t="n">
-        <v>112.78</v>
+        <v>121.13</v>
       </c>
       <c r="L19" t="n">
-        <v>118.13</v>
+        <v>126.88</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-75.54000000000001</v>
+        <v>-79.81999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>67.47</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>101.29</v>
+        <v>107.02</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>87.79000000000001</v>
+        <v>84.13</v>
       </c>
       <c r="K21" t="n">
-        <v>-52.35</v>
+        <v>-50.17</v>
       </c>
       <c r="L21" t="n">
-        <v>102.21</v>
+        <v>97.95</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-12.99</v>
+        <v>-12.45</v>
       </c>
       <c r="K22" t="n">
-        <v>121.38</v>
+        <v>116.32</v>
       </c>
       <c r="L22" t="n">
-        <v>122.07</v>
+        <v>116.98</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-61.48</v>
+        <v>-66.04000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>137.51</v>
+        <v>147.7</v>
       </c>
       <c r="L23" t="n">
-        <v>150.63</v>
+        <v>161.79</v>
       </c>
     </row>
     <row r="24">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-248.99</v>
+        <v>-263.09</v>
       </c>
       <c r="K26" t="n">
-        <v>22.98</v>
+        <v>24.28</v>
       </c>
       <c r="L26" t="n">
-        <v>250.05</v>
+        <v>264.2</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>122.98</v>
+        <v>125.39</v>
       </c>
       <c r="K27" t="n">
-        <v>-199.64</v>
+        <v>-203.55</v>
       </c>
       <c r="L27" t="n">
-        <v>234.48</v>
+        <v>239.07</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-238.73</v>
+        <v>-256.69</v>
       </c>
       <c r="K28" t="n">
-        <v>123.19</v>
+        <v>132.46</v>
       </c>
       <c r="L28" t="n">
-        <v>268.64</v>
+        <v>288.85</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>48.54</v>
+        <v>51.29</v>
       </c>
       <c r="K29" t="n">
-        <v>-34.39</v>
+        <v>-36.34</v>
       </c>
       <c r="L29" t="n">
-        <v>59.49</v>
+        <v>62.86</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.11</v>
+        <v>-3.94</v>
       </c>
       <c r="K30" t="n">
-        <v>-66.8</v>
+        <v>-64.02</v>
       </c>
       <c r="L30" t="n">
-        <v>66.93000000000001</v>
+        <v>64.14</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-47.63</v>
+        <v>-45.65</v>
       </c>
       <c r="K31" t="n">
-        <v>-23.56</v>
+        <v>-22.58</v>
       </c>
       <c r="L31" t="n">
-        <v>53.14</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-19.35</v>
+        <v>-20.45</v>
       </c>
       <c r="K32" t="n">
-        <v>80.06</v>
+        <v>84.59</v>
       </c>
       <c r="L32" t="n">
-        <v>82.36</v>
+        <v>87.03</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>29.22</v>
+        <v>29.79</v>
       </c>
       <c r="K33" t="n">
-        <v>65.76000000000001</v>
+        <v>67.05</v>
       </c>
       <c r="L33" t="n">
-        <v>71.95999999999999</v>
+        <v>73.37</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>45.92</v>
+        <v>44.96</v>
       </c>
       <c r="K34" t="n">
-        <v>27.35</v>
+        <v>26.77</v>
       </c>
       <c r="L34" t="n">
-        <v>53.44</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>25.32</v>
+        <v>26.75</v>
       </c>
       <c r="K35" t="n">
-        <v>-95.78</v>
+        <v>-101.2</v>
       </c>
       <c r="L35" t="n">
-        <v>99.06999999999999</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>15.64</v>
+        <v>15.95</v>
       </c>
       <c r="K36" t="n">
-        <v>-114.64</v>
+        <v>-116.89</v>
       </c>
       <c r="L36" t="n">
-        <v>115.7</v>
+        <v>117.97</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-51.5</v>
+        <v>-52.51</v>
       </c>
       <c r="K37" t="n">
-        <v>-56.05</v>
+        <v>-57.15</v>
       </c>
       <c r="L37" t="n">
-        <v>76.12</v>
+        <v>77.61</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>219.42</v>
+        <v>235.67</v>
       </c>
       <c r="K38" t="n">
-        <v>150.52</v>
+        <v>161.67</v>
       </c>
       <c r="L38" t="n">
-        <v>266.08</v>
+        <v>285.79</v>
       </c>
     </row>
     <row r="39">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-194.62</v>
+        <v>-209.15</v>
       </c>
       <c r="K40" t="n">
-        <v>124.7</v>
+        <v>134.01</v>
       </c>
       <c r="L40" t="n">
-        <v>231.14</v>
+        <v>248.4</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-244.58</v>
+        <v>-254.19</v>
       </c>
       <c r="K41" t="n">
-        <v>153.07</v>
+        <v>159.08</v>
       </c>
       <c r="L41" t="n">
-        <v>288.53</v>
+        <v>299.87</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>20.39</v>
+        <v>19.97</v>
       </c>
       <c r="K42" t="n">
-        <v>252.71</v>
+        <v>247.55</v>
       </c>
       <c r="L42" t="n">
-        <v>253.53</v>
+        <v>248.36</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-168.68</v>
+        <v>-161.65</v>
       </c>
       <c r="K43" t="n">
-        <v>-98.34999999999999</v>
+        <v>-94.26000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>195.26</v>
+        <v>187.12</v>
       </c>
     </row>
     <row r="44">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-111.29</v>
+        <v>-119.49</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.26</v>
+        <v>-1.35</v>
       </c>
       <c r="L45" t="n">
-        <v>111.3</v>
+        <v>119.49</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>16.2</v>
+        <v>16.47</v>
       </c>
       <c r="K46" t="n">
-        <v>-56.98</v>
+        <v>-57.93</v>
       </c>
       <c r="L46" t="n">
-        <v>59.24</v>
+        <v>60.22</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>48.1</v>
+        <v>46.09</v>
       </c>
       <c r="K47" t="n">
-        <v>-71.29000000000001</v>
+        <v>-68.31</v>
       </c>
       <c r="L47" t="n">
-        <v>86</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-92.83</v>
+        <v>-96.36</v>
       </c>
       <c r="K48" t="n">
-        <v>-10.44</v>
+        <v>-10.84</v>
       </c>
       <c r="L48" t="n">
-        <v>93.42</v>
+        <v>96.97</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-72.42</v>
+        <v>-70.94</v>
       </c>
       <c r="K49" t="n">
-        <v>17.28</v>
+        <v>16.93</v>
       </c>
       <c r="L49" t="n">
-        <v>74.45</v>
+        <v>72.93000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-85.75</v>
+        <v>-90.59999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-54.36</v>
+        <v>-57.43</v>
       </c>
       <c r="L50" t="n">
-        <v>101.52</v>
+        <v>107.27</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>93.17</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-61.99</v>
+        <v>-61.94</v>
       </c>
       <c r="L51" t="n">
-        <v>111.91</v>
+        <v>111.83</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-19.22</v>
+        <v>-20.29</v>
       </c>
       <c r="K52" t="n">
-        <v>125.02</v>
+        <v>131.98</v>
       </c>
       <c r="L52" t="n">
-        <v>126.49</v>
+        <v>133.53</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-106.7</v>
+        <v>-102.25</v>
       </c>
       <c r="K53" t="n">
-        <v>38.62</v>
+        <v>37.01</v>
       </c>
       <c r="L53" t="n">
-        <v>113.47</v>
+        <v>108.75</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>98.38</v>
+        <v>102.16</v>
       </c>
       <c r="K54" t="n">
-        <v>169.07</v>
+        <v>175.57</v>
       </c>
       <c r="L54" t="n">
-        <v>195.6</v>
+        <v>203.13</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>146.62</v>
+        <v>157.56</v>
       </c>
       <c r="K55" t="n">
-        <v>-51.63</v>
+        <v>-55.49</v>
       </c>
       <c r="L55" t="n">
-        <v>155.44</v>
+        <v>167.05</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-161.04</v>
+        <v>-170.38</v>
       </c>
       <c r="K56" t="n">
-        <v>144.14</v>
+        <v>152.5</v>
       </c>
       <c r="L56" t="n">
-        <v>216.12</v>
+        <v>228.66</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-93.47</v>
+        <v>-98.76000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>176.46</v>
+        <v>186.44</v>
       </c>
       <c r="L57" t="n">
-        <v>199.68</v>
+        <v>210.99</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>215.07</v>
+        <v>231</v>
       </c>
       <c r="K58" t="n">
-        <v>198.26</v>
+        <v>212.94</v>
       </c>
       <c r="L58" t="n">
-        <v>292.51</v>
+        <v>314.18</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>57.98</v>
+        <v>56.79</v>
       </c>
       <c r="K59" t="n">
-        <v>-44.29</v>
+        <v>-43.39</v>
       </c>
       <c r="L59" t="n">
-        <v>72.95999999999999</v>
+        <v>71.47</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-47.61</v>
+        <v>-46.61</v>
       </c>
       <c r="K60" t="n">
-        <v>-74.69</v>
+        <v>-73.11</v>
       </c>
       <c r="L60" t="n">
-        <v>88.56999999999999</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-54.41</v>
+        <v>-52.14</v>
       </c>
       <c r="K61" t="n">
-        <v>50.18</v>
+        <v>48.09</v>
       </c>
       <c r="L61" t="n">
-        <v>74.01000000000001</v>
+        <v>70.93000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>89.19</v>
+        <v>93.89</v>
       </c>
       <c r="K62" t="n">
-        <v>11.31</v>
+        <v>11.91</v>
       </c>
       <c r="L62" t="n">
-        <v>89.90000000000001</v>
+        <v>94.64</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-90.34999999999999</v>
+        <v>-90.20999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-11.87</v>
+        <v>-11.85</v>
       </c>
       <c r="L63" t="n">
-        <v>91.12</v>
+        <v>90.98</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>75.33</v>
+        <v>73.73</v>
       </c>
       <c r="K64" t="n">
-        <v>24.06</v>
+        <v>23.55</v>
       </c>
       <c r="L64" t="n">
-        <v>79.08</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>130.08</v>
+        <v>137.16</v>
       </c>
       <c r="K65" t="n">
-        <v>30.9</v>
+        <v>32.58</v>
       </c>
       <c r="L65" t="n">
-        <v>133.69</v>
+        <v>140.98</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>61.9</v>
+        <v>64.27</v>
       </c>
       <c r="K66" t="n">
-        <v>-25.68</v>
+        <v>-26.66</v>
       </c>
       <c r="L66" t="n">
-        <v>67.01000000000001</v>
+        <v>69.58</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-41.08</v>
+        <v>-44.1</v>
       </c>
       <c r="K67" t="n">
-        <v>119.67</v>
+        <v>128.46</v>
       </c>
       <c r="L67" t="n">
-        <v>126.53</v>
+        <v>135.81</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>-38.65</v>
+        <v>-39.43</v>
       </c>
       <c r="K68" t="n">
-        <v>-62.24</v>
+        <v>-63.49</v>
       </c>
       <c r="L68" t="n">
-        <v>73.27</v>
+        <v>74.73999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-110.68</v>
+        <v>-108.43</v>
       </c>
       <c r="K69" t="n">
-        <v>74.18000000000001</v>
+        <v>72.67</v>
       </c>
       <c r="L69" t="n">
-        <v>133.24</v>
+        <v>130.53</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-98.51000000000001</v>
+        <v>-105.81</v>
       </c>
       <c r="K70" t="n">
-        <v>-104.36</v>
+        <v>-112.09</v>
       </c>
       <c r="L70" t="n">
-        <v>143.51</v>
+        <v>154.14</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>72.09</v>
+        <v>75.13</v>
       </c>
       <c r="K71" t="n">
-        <v>115.09</v>
+        <v>119.93</v>
       </c>
       <c r="L71" t="n">
-        <v>135.8</v>
+        <v>141.52</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-210.31</v>
+        <v>-201.55</v>
       </c>
       <c r="K72" t="n">
-        <v>-99.15000000000001</v>
+        <v>-95.02</v>
       </c>
       <c r="L72" t="n">
-        <v>232.51</v>
+        <v>222.82</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-184.63</v>
+        <v>-181.5</v>
       </c>
       <c r="K73" t="n">
-        <v>18.2</v>
+        <v>17.89</v>
       </c>
       <c r="L73" t="n">
-        <v>185.52</v>
+        <v>182.38</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-75.89</v>
+        <v>-77.37</v>
       </c>
       <c r="K74" t="n">
-        <v>-45.98</v>
+        <v>-46.88</v>
       </c>
       <c r="L74" t="n">
-        <v>88.73</v>
+        <v>90.47</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>26.33</v>
+        <v>25.71</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.9</v>
+        <v>-0.88</v>
       </c>
       <c r="L75" t="n">
-        <v>26.35</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>29.58</v>
+        <v>31.15</v>
       </c>
       <c r="K76" t="n">
-        <v>-29.14</v>
+        <v>-30.68</v>
       </c>
       <c r="L76" t="n">
-        <v>41.52</v>
+        <v>43.72</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>62.62</v>
+        <v>61.13</v>
       </c>
       <c r="K77" t="n">
-        <v>28.4</v>
+        <v>27.72</v>
       </c>
       <c r="L77" t="n">
-        <v>68.76000000000001</v>
+        <v>67.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-28.54</v>
+        <v>-27.87</v>
       </c>
       <c r="K78" t="n">
-        <v>90.01000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>94.43000000000001</v>
+        <v>92.20999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>36.28</v>
+        <v>37.59</v>
       </c>
       <c r="K79" t="n">
-        <v>-54.58</v>
+        <v>-56.54</v>
       </c>
       <c r="L79" t="n">
-        <v>65.54000000000001</v>
+        <v>67.89</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>-122.88</v>
+        <v>-129.71</v>
       </c>
       <c r="K80" t="n">
-        <v>79.34999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>146.28</v>
+        <v>154.41</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-145.76</v>
+        <v>-151.27</v>
       </c>
       <c r="K81" t="n">
-        <v>-54.09</v>
+        <v>-56.13</v>
       </c>
       <c r="L81" t="n">
-        <v>155.47</v>
+        <v>161.35</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-34.03</v>
+        <v>-33.31</v>
       </c>
       <c r="K82" t="n">
-        <v>135.57</v>
+        <v>132.74</v>
       </c>
       <c r="L82" t="n">
-        <v>139.78</v>
+        <v>136.85</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-98.22</v>
+        <v>-94.18000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-115.8</v>
+        <v>-111.04</v>
       </c>
       <c r="L83" t="n">
-        <v>151.84</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>176.29</v>
+        <v>183.14</v>
       </c>
       <c r="K84" t="n">
-        <v>135.34</v>
+        <v>140.59</v>
       </c>
       <c r="L84" t="n">
-        <v>222.25</v>
+        <v>230.88</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-130.61</v>
+        <v>-130.72</v>
       </c>
       <c r="K85" t="n">
-        <v>100.56</v>
+        <v>100.65</v>
       </c>
       <c r="L85" t="n">
-        <v>164.84</v>
+        <v>164.98</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-232.84</v>
+        <v>-237.67</v>
       </c>
       <c r="K86" t="n">
-        <v>-101.25</v>
+        <v>-103.36</v>
       </c>
       <c r="L86" t="n">
-        <v>253.9</v>
+        <v>259.17</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>152.74</v>
+        <v>156.32</v>
       </c>
       <c r="K87" t="n">
-        <v>216.24</v>
+        <v>221.3</v>
       </c>
       <c r="L87" t="n">
-        <v>264.75</v>
+        <v>270.94</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>190.96</v>
+        <v>195.41</v>
       </c>
       <c r="K88" t="n">
-        <v>-164.6</v>
+        <v>-168.43</v>
       </c>
       <c r="L88" t="n">
-        <v>252.1</v>
+        <v>257.98</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="F14" t="n">
-        <v>6.49</v>
+        <v>7.62</v>
       </c>
       <c r="G14" t="n">
-        <v>324.7</v>
+        <v>325.2</v>
       </c>
       <c r="H14" t="n">
-        <v>25.8</v>
+        <v>59.9</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-38.31</v>
+        <v>24.86</v>
       </c>
       <c r="K14" t="n">
-        <v>12.12</v>
+        <v>-32.9</v>
       </c>
       <c r="L14" t="n">
-        <v>40.19</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:31:38</t>
+          <t>05:31:16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="F15" t="n">
-        <v>9.35</v>
+        <v>6.88</v>
       </c>
       <c r="G15" t="n">
-        <v>328.2</v>
+        <v>324.5</v>
       </c>
       <c r="H15" t="n">
-        <v>27.2</v>
+        <v>41.6</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>42.98</v>
+        <v>14.33</v>
       </c>
       <c r="K15" t="n">
-        <v>28.96</v>
+        <v>49.85</v>
       </c>
       <c r="L15" t="n">
-        <v>51.83</v>
+        <v>51.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:33:16</t>
+          <t>05:33:37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="F16" t="n">
-        <v>8.539999999999999</v>
+        <v>7.26</v>
       </c>
       <c r="G16" t="n">
-        <v>321.7</v>
+        <v>308.8</v>
       </c>
       <c r="H16" t="n">
-        <v>25.2</v>
+        <v>18.9</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>103.64</v>
+        <v>-36.7</v>
       </c>
       <c r="K16" t="n">
-        <v>-45.3</v>
+        <v>26.6</v>
       </c>
       <c r="L16" t="n">
-        <v>113.1</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:37:22</t>
+          <t>05:38:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="F17" t="n">
-        <v>6.63</v>
+        <v>7.58</v>
       </c>
       <c r="G17" t="n">
-        <v>325</v>
+        <v>325.4</v>
       </c>
       <c r="H17" t="n">
-        <v>28.8</v>
+        <v>31.9</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-67.13</v>
+        <v>-66.73999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-17.57</v>
+        <v>20.06</v>
       </c>
       <c r="L17" t="n">
-        <v>69.39</v>
+        <v>69.69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:39:26</t>
+          <t>05:39:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="F18" t="n">
-        <v>5.83</v>
+        <v>7.14</v>
       </c>
       <c r="G18" t="n">
-        <v>329.7</v>
+        <v>322.5</v>
       </c>
       <c r="H18" t="n">
-        <v>21.9</v>
+        <v>63.3</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>24.72</v>
+        <v>30.45</v>
       </c>
       <c r="K18" t="n">
-        <v>-76.53</v>
+        <v>63.18</v>
       </c>
       <c r="L18" t="n">
-        <v>80.42</v>
+        <v>70.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:40:54</t>
+          <t>05:41:37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.54</v>
+        <v>3.12</v>
       </c>
       <c r="F19" t="n">
-        <v>2.84</v>
+        <v>7.31</v>
       </c>
       <c r="G19" t="n">
-        <v>330.3</v>
+        <v>327</v>
       </c>
       <c r="H19" t="n">
-        <v>19.1</v>
+        <v>34.9</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>37.77</v>
+        <v>28.93</v>
       </c>
       <c r="K19" t="n">
-        <v>121.13</v>
+        <v>66.83</v>
       </c>
       <c r="L19" t="n">
-        <v>126.88</v>
+        <v>72.81999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:44:52</t>
+          <t>05:45:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.32</v>
+        <v>3.13</v>
       </c>
       <c r="F20" t="n">
-        <v>3.06</v>
+        <v>10.7</v>
       </c>
       <c r="G20" t="n">
-        <v>321.9</v>
+        <v>313.2</v>
       </c>
       <c r="H20" t="n">
-        <v>28.1</v>
+        <v>50.6</v>
       </c>
       <c r="I20" t="n">
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-79.81999999999999</v>
+        <v>-62.48</v>
       </c>
       <c r="K20" t="n">
-        <v>71.29000000000001</v>
+        <v>-78.15000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>107.02</v>
+        <v>100.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:46:48</t>
+          <t>05:47:39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.57</v>
+        <v>3.48</v>
       </c>
       <c r="F21" t="n">
-        <v>6.09</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>323.1</v>
+        <v>325.8</v>
       </c>
       <c r="H21" t="n">
-        <v>32.8</v>
+        <v>53.5</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>84.13</v>
+        <v>129.8</v>
       </c>
       <c r="K21" t="n">
-        <v>-50.17</v>
+        <v>4.97</v>
       </c>
       <c r="L21" t="n">
-        <v>97.95</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:47:46</t>
+          <t>05:49:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.98</v>
+        <v>3.13</v>
       </c>
       <c r="F22" t="n">
-        <v>10.44</v>
+        <v>7.24</v>
       </c>
       <c r="G22" t="n">
-        <v>325</v>
+        <v>320.8</v>
       </c>
       <c r="H22" t="n">
-        <v>28.2</v>
+        <v>27.9</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-12.45</v>
+        <v>23.72</v>
       </c>
       <c r="K22" t="n">
-        <v>116.32</v>
+        <v>-93</v>
       </c>
       <c r="L22" t="n">
-        <v>116.98</v>
+        <v>95.98</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:52:04</t>
+          <t>05:53:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.02</v>
+        <v>2.25</v>
       </c>
       <c r="F23" t="n">
-        <v>7.04</v>
+        <v>5.02</v>
       </c>
       <c r="G23" t="n">
-        <v>317.6</v>
+        <v>322.1</v>
       </c>
       <c r="H23" t="n">
-        <v>20.8</v>
+        <v>43.8</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-66.04000000000001</v>
+        <v>114.32</v>
       </c>
       <c r="K23" t="n">
-        <v>147.7</v>
+        <v>25.6</v>
       </c>
       <c r="L23" t="n">
-        <v>161.79</v>
+        <v>117.15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:53:14</t>
+          <t>05:54:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.29</v>
+        <v>3.35</v>
       </c>
       <c r="F24" t="n">
-        <v>5.79</v>
+        <v>10.01</v>
       </c>
       <c r="G24" t="n">
-        <v>325</v>
+        <v>332.5</v>
       </c>
       <c r="H24" t="n">
-        <v>24.5</v>
+        <v>8.4</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>-167.08</v>
+        <v>-113.16</v>
       </c>
       <c r="K24" t="n">
-        <v>82.61</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>186.39</v>
+        <v>145.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:54:21</t>
+          <t>05:56:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="F25" t="n">
-        <v>6.59</v>
+        <v>8.26</v>
       </c>
       <c r="G25" t="n">
-        <v>336.5</v>
+        <v>323.5</v>
       </c>
       <c r="H25" t="n">
-        <v>27.3</v>
+        <v>18.1</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-156.19</v>
+        <v>113.16</v>
       </c>
       <c r="K25" t="n">
-        <v>53.88</v>
+        <v>161.01</v>
       </c>
       <c r="L25" t="n">
-        <v>165.23</v>
+        <v>196.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:59:27</t>
+          <t>06:01:39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="F26" t="n">
-        <v>9.08</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>328</v>
+        <v>314.3</v>
       </c>
       <c r="H26" t="n">
-        <v>14.5</v>
+        <v>40.8</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-263.09</v>
+        <v>-42.5</v>
       </c>
       <c r="K26" t="n">
-        <v>24.28</v>
+        <v>192.37</v>
       </c>
       <c r="L26" t="n">
-        <v>264.2</v>
+        <v>197.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:00:38</t>
+          <t>06:04:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.17</v>
+        <v>2.6</v>
       </c>
       <c r="F27" t="n">
-        <v>9.630000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="G27" t="n">
-        <v>316.7</v>
+        <v>334.6</v>
       </c>
       <c r="H27" t="n">
-        <v>26.6</v>
+        <v>39</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>125.39</v>
+        <v>-48.56</v>
       </c>
       <c r="K27" t="n">
-        <v>-203.55</v>
+        <v>99.38</v>
       </c>
       <c r="L27" t="n">
-        <v>239.07</v>
+        <v>110.61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:01:58</t>
+          <t>06:05:34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.37</v>
+        <v>2.82</v>
       </c>
       <c r="F28" t="n">
-        <v>8.82</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>322.4</v>
+        <v>322.1</v>
       </c>
       <c r="H28" t="n">
-        <v>19.6</v>
+        <v>10.4</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-256.69</v>
+        <v>-100.16</v>
       </c>
       <c r="K28" t="n">
-        <v>132.46</v>
+        <v>-93.77</v>
       </c>
       <c r="L28" t="n">
-        <v>288.85</v>
+        <v>137.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:14:26</t>
+          <t>06:15:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="F29" t="n">
-        <v>9.83</v>
+        <v>9.4</v>
       </c>
       <c r="G29" t="n">
-        <v>336.6</v>
+        <v>320.8</v>
       </c>
       <c r="H29" t="n">
-        <v>27.8</v>
+        <v>48.9</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>51.29</v>
+        <v>-22.32</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.34</v>
+        <v>41.06</v>
       </c>
       <c r="L29" t="n">
-        <v>62.86</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:16:15</t>
+          <t>06:16:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.91</v>
+        <v>3.51</v>
       </c>
       <c r="F30" t="n">
-        <v>8.75</v>
+        <v>6.27</v>
       </c>
       <c r="G30" t="n">
-        <v>329.7</v>
+        <v>311.4</v>
       </c>
       <c r="H30" t="n">
-        <v>23.2</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.94</v>
+        <v>-52.37</v>
       </c>
       <c r="K30" t="n">
-        <v>-64.02</v>
+        <v>-44.06</v>
       </c>
       <c r="L30" t="n">
-        <v>64.14</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:17:06</t>
+          <t>06:18:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="F31" t="n">
-        <v>7.17</v>
+        <v>7.08</v>
       </c>
       <c r="G31" t="n">
-        <v>330.2</v>
+        <v>316.6</v>
       </c>
       <c r="H31" t="n">
-        <v>24.3</v>
+        <v>31.7</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-45.65</v>
+        <v>-10.55</v>
       </c>
       <c r="K31" t="n">
-        <v>-22.58</v>
+        <v>-52.08</v>
       </c>
       <c r="L31" t="n">
-        <v>50.93</v>
+        <v>53.13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:21:41</t>
+          <t>06:24:18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.76</v>
+        <v>3.19</v>
       </c>
       <c r="F32" t="n">
-        <v>7.29</v>
+        <v>10.38</v>
       </c>
       <c r="G32" t="n">
-        <v>319.3</v>
+        <v>323.8</v>
       </c>
       <c r="H32" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-20.45</v>
+        <v>-37.08</v>
       </c>
       <c r="K32" t="n">
-        <v>84.59</v>
+        <v>54.6</v>
       </c>
       <c r="L32" t="n">
-        <v>87.03</v>
+        <v>66.01000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:22:46</t>
+          <t>06:26:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="F33" t="n">
-        <v>8.289999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="G33" t="n">
-        <v>327.6</v>
+        <v>311.4</v>
       </c>
       <c r="H33" t="n">
-        <v>26.8</v>
+        <v>29.2</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>29.79</v>
+        <v>48.39</v>
       </c>
       <c r="K33" t="n">
-        <v>67.05</v>
+        <v>-71.13</v>
       </c>
       <c r="L33" t="n">
-        <v>73.37</v>
+        <v>86.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:23:18</t>
+          <t>06:27:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="F34" t="n">
-        <v>7.41</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>312.9</v>
+        <v>318.7</v>
       </c>
       <c r="H34" t="n">
-        <v>22.1</v>
+        <v>63.1</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>44.96</v>
+        <v>-72.36</v>
       </c>
       <c r="K34" t="n">
-        <v>26.77</v>
+        <v>-34.61</v>
       </c>
       <c r="L34" t="n">
-        <v>52.33</v>
+        <v>80.20999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:28:46</t>
+          <t>06:33:13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.37</v>
+        <v>3.07</v>
       </c>
       <c r="F35" t="n">
-        <v>4.92</v>
+        <v>7.66</v>
       </c>
       <c r="G35" t="n">
-        <v>317.1</v>
+        <v>319.1</v>
       </c>
       <c r="H35" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>26.75</v>
+        <v>105.36</v>
       </c>
       <c r="K35" t="n">
-        <v>-101.2</v>
+        <v>-71.37</v>
       </c>
       <c r="L35" t="n">
-        <v>104.68</v>
+        <v>127.26</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:30:32</t>
+          <t>06:35:35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="F36" t="n">
-        <v>9</v>
+        <v>9.58</v>
       </c>
       <c r="G36" t="n">
-        <v>338.1</v>
+        <v>312.4</v>
       </c>
       <c r="H36" t="n">
-        <v>29.2</v>
+        <v>42</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>15.95</v>
+        <v>111.82</v>
       </c>
       <c r="K36" t="n">
-        <v>-116.89</v>
+        <v>-18.05</v>
       </c>
       <c r="L36" t="n">
-        <v>117.97</v>
+        <v>113.27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:31:36</t>
+          <t>06:36:41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="F37" t="n">
-        <v>9.08</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>316.9</v>
+        <v>322.6</v>
       </c>
       <c r="H37" t="n">
-        <v>30.4</v>
+        <v>38.2</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-52.51</v>
+        <v>-118.46</v>
       </c>
       <c r="K37" t="n">
-        <v>-57.15</v>
+        <v>66.67</v>
       </c>
       <c r="L37" t="n">
-        <v>77.61</v>
+        <v>135.94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:36:27</t>
+          <t>06:40:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.95</v>
+        <v>3.17</v>
       </c>
       <c r="F38" t="n">
-        <v>10.7</v>
+        <v>7.66</v>
       </c>
       <c r="G38" t="n">
-        <v>325</v>
+        <v>307.2</v>
       </c>
       <c r="H38" t="n">
-        <v>27.6</v>
+        <v>55.5</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>235.67</v>
+        <v>-158.77</v>
       </c>
       <c r="K38" t="n">
-        <v>161.67</v>
+        <v>32.44</v>
       </c>
       <c r="L38" t="n">
-        <v>285.79</v>
+        <v>162.05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:37:36</t>
+          <t>06:41:31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="F39" t="n">
-        <v>7.69</v>
+        <v>8.06</v>
       </c>
       <c r="G39" t="n">
-        <v>327.1</v>
+        <v>326.1</v>
       </c>
       <c r="H39" t="n">
-        <v>23.6</v>
+        <v>43.8</v>
       </c>
       <c r="I39" t="n">
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-152.46</v>
+        <v>140.15</v>
       </c>
       <c r="K39" t="n">
-        <v>-89.56999999999999</v>
+        <v>72.42</v>
       </c>
       <c r="L39" t="n">
-        <v>176.82</v>
+        <v>157.75</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:39:42</t>
+          <t>06:43:02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.71</v>
+        <v>2.9</v>
       </c>
       <c r="F40" t="n">
-        <v>10.7</v>
+        <v>8.75</v>
       </c>
       <c r="G40" t="n">
-        <v>321.5</v>
+        <v>323.3</v>
       </c>
       <c r="H40" t="n">
-        <v>30.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-209.15</v>
+        <v>-12.59</v>
       </c>
       <c r="K40" t="n">
-        <v>134.01</v>
+        <v>160.99</v>
       </c>
       <c r="L40" t="n">
-        <v>248.4</v>
+        <v>161.48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:45:19</t>
+          <t>06:47:37</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="F41" t="n">
-        <v>9.85</v>
+        <v>8.44</v>
       </c>
       <c r="G41" t="n">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="H41" t="n">
-        <v>25.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-254.19</v>
+        <v>-151.85</v>
       </c>
       <c r="K41" t="n">
-        <v>159.08</v>
+        <v>160.9</v>
       </c>
       <c r="L41" t="n">
-        <v>299.87</v>
+        <v>221.24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:46:47</t>
+          <t>06:48:35</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.19</v>
+        <v>2.87</v>
       </c>
       <c r="F42" t="n">
-        <v>5.25</v>
+        <v>7.52</v>
       </c>
       <c r="G42" t="n">
-        <v>335.2</v>
+        <v>320.9</v>
       </c>
       <c r="H42" t="n">
-        <v>25.9</v>
+        <v>56</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J42" t="n">
-        <v>19.97</v>
+        <v>152.79</v>
       </c>
       <c r="K42" t="n">
-        <v>247.55</v>
+        <v>22.07</v>
       </c>
       <c r="L42" t="n">
-        <v>248.36</v>
+        <v>154.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:49:00</t>
+          <t>06:50:03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.19</v>
+        <v>2.85</v>
       </c>
       <c r="F43" t="n">
-        <v>8.01</v>
+        <v>6.33</v>
       </c>
       <c r="G43" t="n">
-        <v>307.1</v>
+        <v>328.1</v>
       </c>
       <c r="H43" t="n">
-        <v>23.7</v>
+        <v>26.7</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-161.65</v>
+        <v>-8.5</v>
       </c>
       <c r="K43" t="n">
-        <v>-94.26000000000001</v>
+        <v>158.66</v>
       </c>
       <c r="L43" t="n">
-        <v>187.12</v>
+        <v>158.89</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:00:31</t>
+          <t>07:01:28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.89</v>
+        <v>3.36</v>
       </c>
       <c r="F44" t="n">
-        <v>10.7</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>310.3</v>
+        <v>316.1</v>
       </c>
       <c r="H44" t="n">
-        <v>34.8</v>
+        <v>53.5</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-55.22</v>
+        <v>29.54</v>
       </c>
       <c r="K44" t="n">
-        <v>52.6</v>
+        <v>40.29</v>
       </c>
       <c r="L44" t="n">
-        <v>76.26000000000001</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:02:26</t>
+          <t>07:02:14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="F45" t="n">
-        <v>9.359999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G45" t="n">
-        <v>328</v>
+        <v>336.3</v>
       </c>
       <c r="H45" t="n">
-        <v>32.9</v>
+        <v>47.2</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>-119.49</v>
+        <v>-50.02</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.35</v>
+        <v>35.19</v>
       </c>
       <c r="L45" t="n">
-        <v>119.49</v>
+        <v>61.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:05:01</t>
+          <t>07:04:42</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1972,31 +1972,31 @@
         <v>3.87</v>
       </c>
       <c r="F46" t="n">
-        <v>7.64</v>
+        <v>10.7</v>
       </c>
       <c r="G46" t="n">
-        <v>314</v>
+        <v>333.1</v>
       </c>
       <c r="H46" t="n">
-        <v>25.1</v>
+        <v>55.2</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>16.47</v>
+        <v>-76.09</v>
       </c>
       <c r="K46" t="n">
-        <v>-57.93</v>
+        <v>-13.32</v>
       </c>
       <c r="L46" t="n">
-        <v>60.22</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:08:53</t>
+          <t>07:10:39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.28</v>
+        <v>2.56</v>
       </c>
       <c r="F47" t="n">
-        <v>7.3</v>
+        <v>5.87</v>
       </c>
       <c r="G47" t="n">
-        <v>308.1</v>
+        <v>328.2</v>
       </c>
       <c r="H47" t="n">
-        <v>29.8</v>
+        <v>64</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>46.09</v>
+        <v>52.07</v>
       </c>
       <c r="K47" t="n">
-        <v>-68.31</v>
+        <v>-44.45</v>
       </c>
       <c r="L47" t="n">
-        <v>82.40000000000001</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:10:37</t>
+          <t>07:11:59</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.34</v>
+        <v>2.77</v>
       </c>
       <c r="F48" t="n">
-        <v>10.7</v>
+        <v>6.48</v>
       </c>
       <c r="G48" t="n">
-        <v>322.2</v>
+        <v>323.7</v>
       </c>
       <c r="H48" t="n">
-        <v>25.5</v>
+        <v>47.6</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-96.36</v>
+        <v>-48.44</v>
       </c>
       <c r="K48" t="n">
-        <v>-10.84</v>
+        <v>-28.34</v>
       </c>
       <c r="L48" t="n">
-        <v>96.97</v>
+        <v>56.12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:12:19</t>
+          <t>07:12:42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="F49" t="n">
-        <v>10.19</v>
+        <v>7.84</v>
       </c>
       <c r="G49" t="n">
-        <v>324.7</v>
+        <v>323.1</v>
       </c>
       <c r="H49" t="n">
-        <v>23.4</v>
+        <v>61.6</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-70.94</v>
+        <v>20.25</v>
       </c>
       <c r="K49" t="n">
-        <v>16.93</v>
+        <v>66.87</v>
       </c>
       <c r="L49" t="n">
-        <v>72.93000000000001</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:17:54</t>
+          <t>07:17:35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="F50" t="n">
-        <v>6.29</v>
+        <v>7.5</v>
       </c>
       <c r="G50" t="n">
-        <v>317.4</v>
+        <v>319</v>
       </c>
       <c r="H50" t="n">
-        <v>32</v>
+        <v>59.3</v>
       </c>
       <c r="I50" t="n">
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-90.59999999999999</v>
+        <v>100.07</v>
       </c>
       <c r="K50" t="n">
-        <v>-57.43</v>
+        <v>-65.48999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>107.27</v>
+        <v>119.59</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:19:05</t>
+          <t>07:18:42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.66</v>
+        <v>2.86</v>
       </c>
       <c r="F51" t="n">
-        <v>10.61</v>
+        <v>5.68</v>
       </c>
       <c r="G51" t="n">
-        <v>323.5</v>
+        <v>323.6</v>
       </c>
       <c r="H51" t="n">
-        <v>25.2</v>
+        <v>56.5</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>93.09999999999999</v>
+        <v>-88.34</v>
       </c>
       <c r="K51" t="n">
-        <v>-61.94</v>
+        <v>-12.65</v>
       </c>
       <c r="L51" t="n">
-        <v>111.83</v>
+        <v>89.23999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:19:43</t>
+          <t>07:21:01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="F52" t="n">
-        <v>10.52</v>
+        <v>10.7</v>
       </c>
       <c r="G52" t="n">
-        <v>323.8</v>
+        <v>330.4</v>
       </c>
       <c r="H52" t="n">
-        <v>29.4</v>
+        <v>33.6</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-20.29</v>
+        <v>18.05</v>
       </c>
       <c r="K52" t="n">
-        <v>131.98</v>
+        <v>-102.62</v>
       </c>
       <c r="L52" t="n">
-        <v>133.53</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:24:02</t>
+          <t>07:24:57</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="F53" t="n">
-        <v>8.76</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>338.1</v>
+        <v>310.1</v>
       </c>
       <c r="H53" t="n">
-        <v>26</v>
+        <v>40.9</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-102.25</v>
+        <v>-40.78</v>
       </c>
       <c r="K53" t="n">
-        <v>37.01</v>
+        <v>126.63</v>
       </c>
       <c r="L53" t="n">
-        <v>108.75</v>
+        <v>133.04</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:25:56</t>
+          <t>07:27:19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.92</v>
+        <v>3.31</v>
       </c>
       <c r="F54" t="n">
-        <v>7.32</v>
+        <v>7.92</v>
       </c>
       <c r="G54" t="n">
-        <v>323.3</v>
+        <v>320.8</v>
       </c>
       <c r="H54" t="n">
-        <v>30.9</v>
+        <v>10.6</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>102.16</v>
+        <v>131.76</v>
       </c>
       <c r="K54" t="n">
-        <v>175.57</v>
+        <v>58.68</v>
       </c>
       <c r="L54" t="n">
-        <v>203.13</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:27:35</t>
+          <t>07:28:14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.69</v>
+        <v>2.84</v>
       </c>
       <c r="F55" t="n">
-        <v>9.550000000000001</v>
+        <v>6.77</v>
       </c>
       <c r="G55" t="n">
-        <v>321.5</v>
+        <v>319.3</v>
       </c>
       <c r="H55" t="n">
-        <v>27.4</v>
+        <v>29.4</v>
       </c>
       <c r="I55" t="n">
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>157.56</v>
+        <v>-23.15</v>
       </c>
       <c r="K55" t="n">
-        <v>-55.49</v>
+        <v>156.86</v>
       </c>
       <c r="L55" t="n">
-        <v>167.05</v>
+        <v>158.56</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:31:27</t>
+          <t>07:32:47</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2392,31 +2392,31 @@
         <v>3.4</v>
       </c>
       <c r="F56" t="n">
-        <v>7.64</v>
+        <v>7.17</v>
       </c>
       <c r="G56" t="n">
-        <v>314.7</v>
+        <v>323.9</v>
       </c>
       <c r="H56" t="n">
-        <v>26.4</v>
+        <v>56.1</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-170.38</v>
+        <v>-153.58</v>
       </c>
       <c r="K56" t="n">
-        <v>152.5</v>
+        <v>-72.3</v>
       </c>
       <c r="L56" t="n">
-        <v>228.66</v>
+        <v>169.75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:32:54</t>
+          <t>07:33:33</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="F57" t="n">
-        <v>9.24</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>332.7</v>
+        <v>322</v>
       </c>
       <c r="H57" t="n">
-        <v>28.1</v>
+        <v>57.6</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-98.76000000000001</v>
+        <v>-235.61</v>
       </c>
       <c r="K57" t="n">
-        <v>186.44</v>
+        <v>117.37</v>
       </c>
       <c r="L57" t="n">
-        <v>210.99</v>
+        <v>263.23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:34:58</t>
+          <t>07:36:04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.74</v>
+        <v>3.29</v>
       </c>
       <c r="F58" t="n">
-        <v>10.7</v>
+        <v>7.93</v>
       </c>
       <c r="G58" t="n">
-        <v>322.6</v>
+        <v>324.2</v>
       </c>
       <c r="H58" t="n">
-        <v>25.9</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>231</v>
+        <v>-47.02</v>
       </c>
       <c r="K58" t="n">
-        <v>212.94</v>
+        <v>221.55</v>
       </c>
       <c r="L58" t="n">
-        <v>314.18</v>
+        <v>226.48</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:43:48</t>
+          <t>07:45:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.73</v>
+        <v>3.19</v>
       </c>
       <c r="F59" t="n">
-        <v>10.7</v>
+        <v>9.9</v>
       </c>
       <c r="G59" t="n">
-        <v>325.9</v>
+        <v>323.7</v>
       </c>
       <c r="H59" t="n">
-        <v>21.8</v>
+        <v>48.4</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>56.79</v>
+        <v>-5.42</v>
       </c>
       <c r="K59" t="n">
-        <v>-43.39</v>
+        <v>54.69</v>
       </c>
       <c r="L59" t="n">
-        <v>71.47</v>
+        <v>54.96</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:45:45</t>
+          <t>07:46:25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="F60" t="n">
-        <v>8.720000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="G60" t="n">
-        <v>324.4</v>
+        <v>312.3</v>
       </c>
       <c r="H60" t="n">
-        <v>32.3</v>
+        <v>97.2</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-46.61</v>
+        <v>-40.81</v>
       </c>
       <c r="K60" t="n">
-        <v>-73.11</v>
+        <v>59.53</v>
       </c>
       <c r="L60" t="n">
-        <v>86.7</v>
+        <v>72.18000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:47:54</t>
+          <t>07:48:16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.01</v>
+        <v>3.48</v>
       </c>
       <c r="F61" t="n">
-        <v>10.23</v>
+        <v>9.52</v>
       </c>
       <c r="G61" t="n">
-        <v>317.9</v>
+        <v>325.2</v>
       </c>
       <c r="H61" t="n">
-        <v>32.7</v>
+        <v>35.1</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-52.14</v>
+        <v>-49.49</v>
       </c>
       <c r="K61" t="n">
-        <v>48.09</v>
+        <v>17.7</v>
       </c>
       <c r="L61" t="n">
-        <v>70.93000000000001</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:53:25</t>
+          <t>07:51:59</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.02</v>
+        <v>2.88</v>
       </c>
       <c r="F62" t="n">
-        <v>10.7</v>
+        <v>6.15</v>
       </c>
       <c r="G62" t="n">
-        <v>312</v>
+        <v>332.8</v>
       </c>
       <c r="H62" t="n">
-        <v>31.5</v>
+        <v>27.1</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>93.89</v>
+        <v>-29.85</v>
       </c>
       <c r="K62" t="n">
-        <v>11.91</v>
+        <v>83.88</v>
       </c>
       <c r="L62" t="n">
-        <v>94.64</v>
+        <v>89.03</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:54:24</t>
+          <t>07:54:11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.56</v>
+        <v>3.62</v>
       </c>
       <c r="F63" t="n">
-        <v>10.7</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>316.2</v>
+        <v>330.9</v>
       </c>
       <c r="H63" t="n">
-        <v>24.3</v>
+        <v>63</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J63" t="n">
-        <v>-90.20999999999999</v>
+        <v>-17.55</v>
       </c>
       <c r="K63" t="n">
-        <v>-11.85</v>
+        <v>92.77</v>
       </c>
       <c r="L63" t="n">
-        <v>90.98</v>
+        <v>94.41</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:57:06</t>
+          <t>07:56:32</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.43</v>
+        <v>3.65</v>
       </c>
       <c r="F64" t="n">
-        <v>10.29</v>
+        <v>10.22</v>
       </c>
       <c r="G64" t="n">
-        <v>322.6</v>
+        <v>325.8</v>
       </c>
       <c r="H64" t="n">
-        <v>36.7</v>
+        <v>16.4</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>73.73</v>
+        <v>-70.39</v>
       </c>
       <c r="K64" t="n">
-        <v>23.55</v>
+        <v>-55.73</v>
       </c>
       <c r="L64" t="n">
-        <v>77.40000000000001</v>
+        <v>89.78</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:01:30</t>
+          <t>08:00:30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.51</v>
+        <v>3.52</v>
       </c>
       <c r="F65" t="n">
-        <v>9.93</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G65" t="n">
         <v>326.6</v>
       </c>
       <c r="H65" t="n">
-        <v>19.1</v>
+        <v>64.2</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>137.16</v>
+        <v>33.26</v>
       </c>
       <c r="K65" t="n">
-        <v>32.58</v>
+        <v>126.72</v>
       </c>
       <c r="L65" t="n">
-        <v>140.98</v>
+        <v>131.01</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:02:46</t>
+          <t>08:02:05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.35</v>
+        <v>3.79</v>
       </c>
       <c r="F66" t="n">
-        <v>10.67</v>
+        <v>10.7</v>
       </c>
       <c r="G66" t="n">
-        <v>315.7</v>
+        <v>316</v>
       </c>
       <c r="H66" t="n">
-        <v>23.2</v>
+        <v>35.9</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J66" t="n">
-        <v>64.27</v>
+        <v>121.8</v>
       </c>
       <c r="K66" t="n">
-        <v>-26.66</v>
+        <v>-65.40000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>69.58</v>
+        <v>138.24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:04:22</t>
+          <t>08:03:47</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2857,28 +2857,28 @@
         <v>10.7</v>
       </c>
       <c r="G67" t="n">
-        <v>319</v>
+        <v>325.2</v>
       </c>
       <c r="H67" t="n">
-        <v>34.7</v>
+        <v>16.5</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-44.1</v>
+        <v>20.78</v>
       </c>
       <c r="K67" t="n">
-        <v>128.46</v>
+        <v>121.67</v>
       </c>
       <c r="L67" t="n">
-        <v>135.81</v>
+        <v>123.44</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:09:19</t>
+          <t>08:09:27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.65</v>
+        <v>3.22</v>
       </c>
       <c r="F68" t="n">
-        <v>9.1</v>
+        <v>10.7</v>
       </c>
       <c r="G68" t="n">
-        <v>338.4</v>
+        <v>322</v>
       </c>
       <c r="H68" t="n">
-        <v>30.7</v>
+        <v>20.2</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-39.43</v>
+        <v>-178.93</v>
       </c>
       <c r="K68" t="n">
-        <v>-63.49</v>
+        <v>4.92</v>
       </c>
       <c r="L68" t="n">
-        <v>74.73999999999999</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:10:27</t>
+          <t>08:11:37</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.34</v>
+        <v>4.64</v>
       </c>
       <c r="F69" t="n">
-        <v>7.94</v>
+        <v>10.7</v>
       </c>
       <c r="G69" t="n">
-        <v>328.6</v>
+        <v>321.9</v>
       </c>
       <c r="H69" t="n">
-        <v>32.8</v>
+        <v>31.4</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-108.43</v>
+        <v>277.38</v>
       </c>
       <c r="K69" t="n">
-        <v>72.67</v>
+        <v>375.14</v>
       </c>
       <c r="L69" t="n">
-        <v>130.53</v>
+        <v>466.55</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:12:22</t>
+          <t>08:13:40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="F70" t="n">
-        <v>6.39</v>
+        <v>10.7</v>
       </c>
       <c r="G70" t="n">
-        <v>326.2</v>
+        <v>309.8</v>
       </c>
       <c r="H70" t="n">
-        <v>29.1</v>
+        <v>43.1</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-105.81</v>
+        <v>-112.02</v>
       </c>
       <c r="K70" t="n">
-        <v>-112.09</v>
+        <v>3.75</v>
       </c>
       <c r="L70" t="n">
-        <v>154.14</v>
+        <v>112.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:16:06</t>
+          <t>08:19:47</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="F71" t="n">
         <v>10.7</v>
       </c>
       <c r="G71" t="n">
-        <v>311.6</v>
+        <v>329.6</v>
       </c>
       <c r="H71" t="n">
-        <v>32.3</v>
+        <v>17.1</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>75.13</v>
+        <v>-24.56</v>
       </c>
       <c r="K71" t="n">
-        <v>119.93</v>
+        <v>229.1</v>
       </c>
       <c r="L71" t="n">
-        <v>141.52</v>
+        <v>230.41</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:18:39</t>
+          <t>08:21:16</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.04</v>
+        <v>3.72</v>
       </c>
       <c r="F72" t="n">
-        <v>8.779999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="G72" t="n">
-        <v>321.6</v>
+        <v>313.2</v>
       </c>
       <c r="H72" t="n">
-        <v>34.1</v>
+        <v>39.9</v>
       </c>
       <c r="I72" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-201.55</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>-95.02</v>
+        <v>-278.77</v>
       </c>
       <c r="L72" t="n">
-        <v>222.82</v>
+        <v>278.91</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:20:10</t>
+          <t>08:23:48</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.68</v>
+        <v>3.92</v>
       </c>
       <c r="F73" t="n">
-        <v>9.050000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G73" t="n">
-        <v>322.2</v>
+        <v>313.3</v>
       </c>
       <c r="H73" t="n">
-        <v>20.9</v>
+        <v>63.7</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-181.5</v>
+        <v>-183.25</v>
       </c>
       <c r="K73" t="n">
-        <v>17.89</v>
+        <v>188.47</v>
       </c>
       <c r="L73" t="n">
-        <v>182.38</v>
+        <v>262.87</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:33:10</t>
+          <t>08:32:52</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.16</v>
+        <v>3.44</v>
       </c>
       <c r="F74" t="n">
         <v>10.7</v>
       </c>
       <c r="G74" t="n">
-        <v>315.6</v>
+        <v>315.5</v>
       </c>
       <c r="H74" t="n">
-        <v>26.7</v>
+        <v>51.1</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-77.37</v>
+        <v>-54.01</v>
       </c>
       <c r="K74" t="n">
-        <v>-46.88</v>
+        <v>26.01</v>
       </c>
       <c r="L74" t="n">
-        <v>90.47</v>
+        <v>59.95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:34:25</t>
+          <t>08:34:54</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.9</v>
+        <v>3.16</v>
       </c>
       <c r="F75" t="n">
         <v>10.7</v>
       </c>
       <c r="G75" t="n">
-        <v>328.7</v>
+        <v>314.5</v>
       </c>
       <c r="H75" t="n">
-        <v>26.3</v>
+        <v>43.5</v>
       </c>
       <c r="I75" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>25.71</v>
+        <v>-17.23</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.88</v>
+        <v>45.1</v>
       </c>
       <c r="L75" t="n">
-        <v>25.73</v>
+        <v>48.28</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:36:13</t>
+          <t>08:36:41</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="F76" t="n">
-        <v>9.619999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="G76" t="n">
-        <v>321.5</v>
+        <v>322</v>
       </c>
       <c r="H76" t="n">
-        <v>31.4</v>
+        <v>40.9</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>31.15</v>
+        <v>-46.67</v>
       </c>
       <c r="K76" t="n">
-        <v>-30.68</v>
+        <v>12.92</v>
       </c>
       <c r="L76" t="n">
-        <v>43.72</v>
+        <v>48.43</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:40:24</t>
+          <t>08:41:45</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.97</v>
+        <v>3.16</v>
       </c>
       <c r="F77" t="n">
-        <v>10.7</v>
+        <v>7.45</v>
       </c>
       <c r="G77" t="n">
-        <v>329.9</v>
+        <v>328.4</v>
       </c>
       <c r="H77" t="n">
-        <v>30.8</v>
+        <v>48.1</v>
       </c>
       <c r="I77" t="n">
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>61.13</v>
+        <v>47.79</v>
       </c>
       <c r="K77" t="n">
-        <v>27.72</v>
+        <v>54.57</v>
       </c>
       <c r="L77" t="n">
-        <v>67.12</v>
+        <v>72.54000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:42:43</t>
+          <t>08:43:56</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.89</v>
+        <v>3.14</v>
       </c>
       <c r="F78" t="n">
-        <v>10.7</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>336.6</v>
+        <v>310</v>
       </c>
       <c r="H78" t="n">
-        <v>33.3</v>
+        <v>51.5</v>
       </c>
       <c r="I78" t="n">
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-27.87</v>
+        <v>-43.28</v>
       </c>
       <c r="K78" t="n">
-        <v>87.90000000000001</v>
+        <v>83.28</v>
       </c>
       <c r="L78" t="n">
-        <v>92.20999999999999</v>
+        <v>93.86</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:44:58</t>
+          <t>08:45:58</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.76</v>
+        <v>3.25</v>
       </c>
       <c r="F79" t="n">
-        <v>10.48</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>318.3</v>
+        <v>315.6</v>
       </c>
       <c r="H79" t="n">
-        <v>26.3</v>
+        <v>55.9</v>
       </c>
       <c r="I79" t="n">
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>37.59</v>
+        <v>-67.52</v>
       </c>
       <c r="K79" t="n">
-        <v>-56.54</v>
+        <v>5.61</v>
       </c>
       <c r="L79" t="n">
-        <v>67.89</v>
+        <v>67.75</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:48:56</t>
+          <t>08:50:10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.8</v>
+        <v>3.16</v>
       </c>
       <c r="F80" t="n">
-        <v>10.7</v>
+        <v>7.76</v>
       </c>
       <c r="G80" t="n">
-        <v>329.6</v>
+        <v>330.8</v>
       </c>
       <c r="H80" t="n">
-        <v>25.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-129.71</v>
+        <v>-81.28</v>
       </c>
       <c r="K80" t="n">
-        <v>83.76000000000001</v>
+        <v>-31.87</v>
       </c>
       <c r="L80" t="n">
-        <v>154.41</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:49:41</t>
+          <t>08:51:39</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.58</v>
+        <v>3.51</v>
       </c>
       <c r="F81" t="n">
-        <v>10.7</v>
+        <v>10.45</v>
       </c>
       <c r="G81" t="n">
-        <v>324.9</v>
+        <v>320.2</v>
       </c>
       <c r="H81" t="n">
-        <v>27.4</v>
+        <v>38.2</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>-151.27</v>
+        <v>-122.1</v>
       </c>
       <c r="K81" t="n">
-        <v>-56.13</v>
+        <v>30.02</v>
       </c>
       <c r="L81" t="n">
-        <v>161.35</v>
+        <v>125.74</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:51:09</t>
+          <t>08:54:29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.53</v>
+        <v>4.64</v>
       </c>
       <c r="F82" t="n">
-        <v>9.460000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="G82" t="n">
-        <v>321.9</v>
+        <v>334.1</v>
       </c>
       <c r="H82" t="n">
-        <v>25.4</v>
+        <v>21.4</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-33.31</v>
+        <v>148.04</v>
       </c>
       <c r="K82" t="n">
-        <v>132.74</v>
+        <v>-86.73</v>
       </c>
       <c r="L82" t="n">
-        <v>136.85</v>
+        <v>171.57</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:57:12</t>
+          <t>08:58:53</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="F83" t="n">
-        <v>10.7</v>
+        <v>10.31</v>
       </c>
       <c r="G83" t="n">
-        <v>317.4</v>
+        <v>323.2</v>
       </c>
       <c r="H83" t="n">
-        <v>23.3</v>
+        <v>49.2</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-94.18000000000001</v>
+        <v>23.16</v>
       </c>
       <c r="K83" t="n">
-        <v>-111.04</v>
+        <v>179.3</v>
       </c>
       <c r="L83" t="n">
-        <v>145.6</v>
+        <v>180.79</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:59:06</t>
+          <t>09:01:05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.54</v>
+        <v>4.29</v>
       </c>
       <c r="F84" t="n">
-        <v>7.12</v>
+        <v>10.7</v>
       </c>
       <c r="G84" t="n">
-        <v>330.5</v>
+        <v>332.6</v>
       </c>
       <c r="H84" t="n">
-        <v>26.2</v>
+        <v>56.4</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>183.14</v>
+        <v>-35.62</v>
       </c>
       <c r="K84" t="n">
-        <v>140.59</v>
+        <v>227.16</v>
       </c>
       <c r="L84" t="n">
-        <v>230.88</v>
+        <v>229.94</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:01:45</t>
+          <t>09:02:29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="F85" t="n">
-        <v>10.7</v>
+        <v>10.04</v>
       </c>
       <c r="G85" t="n">
-        <v>319.1</v>
+        <v>315.6</v>
       </c>
       <c r="H85" t="n">
-        <v>30.3</v>
+        <v>60.9</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-130.72</v>
+        <v>193.24</v>
       </c>
       <c r="K85" t="n">
-        <v>100.65</v>
+        <v>-47.53</v>
       </c>
       <c r="L85" t="n">
-        <v>164.98</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:05:59</t>
+          <t>09:06:44</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.38</v>
+        <v>3.63</v>
       </c>
       <c r="F86" t="n">
-        <v>10.7</v>
+        <v>9.27</v>
       </c>
       <c r="G86" t="n">
-        <v>308.2</v>
+        <v>321.5</v>
       </c>
       <c r="H86" t="n">
-        <v>25.8</v>
+        <v>42.6</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-237.67</v>
+        <v>247.51</v>
       </c>
       <c r="K86" t="n">
-        <v>-103.36</v>
+        <v>152.01</v>
       </c>
       <c r="L86" t="n">
-        <v>259.17</v>
+        <v>290.46</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:08:23</t>
+          <t>09:08:14</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.7</v>
+        <v>3.16</v>
       </c>
       <c r="F87" t="n">
-        <v>10.7</v>
+        <v>6.97</v>
       </c>
       <c r="G87" t="n">
-        <v>328.5</v>
+        <v>323.7</v>
       </c>
       <c r="H87" t="n">
-        <v>30.7</v>
+        <v>34</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>156.32</v>
+        <v>197.26</v>
       </c>
       <c r="K87" t="n">
-        <v>221.3</v>
+        <v>-133.39</v>
       </c>
       <c r="L87" t="n">
-        <v>270.94</v>
+        <v>238.13</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:09:58</t>
+          <t>09:09:23</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="F88" t="n">
-        <v>6.98</v>
+        <v>10.7</v>
       </c>
       <c r="G88" t="n">
-        <v>321.2</v>
+        <v>329.2</v>
       </c>
       <c r="H88" t="n">
-        <v>25.2</v>
+        <v>54.7</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>195.41</v>
+        <v>-216.62</v>
       </c>
       <c r="K88" t="n">
-        <v>-168.43</v>
+        <v>-182.91</v>
       </c>
       <c r="L88" t="n">
-        <v>257.98</v>
+        <v>283.51</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="F14" t="n">
-        <v>7.62</v>
+        <v>5.88</v>
       </c>
       <c r="G14" t="n">
-        <v>325.2</v>
+        <v>322</v>
       </c>
       <c r="H14" t="n">
-        <v>59.9</v>
+        <v>26.6</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>24.86</v>
+        <v>21.54</v>
       </c>
       <c r="K14" t="n">
-        <v>-32.9</v>
+        <v>36.15</v>
       </c>
       <c r="L14" t="n">
-        <v>41.24</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:31:16</t>
+          <t>05:32:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.01</v>
+        <v>2.72</v>
       </c>
       <c r="F15" t="n">
-        <v>6.88</v>
+        <v>6.36</v>
       </c>
       <c r="G15" t="n">
-        <v>324.5</v>
+        <v>329.2</v>
       </c>
       <c r="H15" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>14.33</v>
+        <v>21.29</v>
       </c>
       <c r="K15" t="n">
-        <v>49.85</v>
+        <v>-42.12</v>
       </c>
       <c r="L15" t="n">
-        <v>51.87</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:33:37</t>
+          <t>05:34:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="F16" t="n">
-        <v>7.26</v>
+        <v>8.07</v>
       </c>
       <c r="G16" t="n">
-        <v>308.8</v>
+        <v>330.9</v>
       </c>
       <c r="H16" t="n">
-        <v>18.9</v>
+        <v>55.5</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J16" t="n">
-        <v>-36.7</v>
+        <v>27.76</v>
       </c>
       <c r="K16" t="n">
-        <v>26.6</v>
+        <v>-50.91</v>
       </c>
       <c r="L16" t="n">
-        <v>45.33</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:38:15</t>
+          <t>05:39:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.25</v>
+        <v>3.81</v>
       </c>
       <c r="F17" t="n">
-        <v>7.58</v>
+        <v>6.81</v>
       </c>
       <c r="G17" t="n">
-        <v>325.4</v>
+        <v>325.5</v>
       </c>
       <c r="H17" t="n">
-        <v>31.9</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-66.73999999999999</v>
+        <v>57.54</v>
       </c>
       <c r="K17" t="n">
-        <v>20.06</v>
+        <v>-73.66</v>
       </c>
       <c r="L17" t="n">
-        <v>69.69</v>
+        <v>93.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:39:52</t>
+          <t>05:40:53</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="F18" t="n">
-        <v>7.14</v>
+        <v>7.98</v>
       </c>
       <c r="G18" t="n">
-        <v>322.5</v>
+        <v>328</v>
       </c>
       <c r="H18" t="n">
-        <v>63.3</v>
+        <v>41.1</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>30.45</v>
+        <v>-37.27</v>
       </c>
       <c r="K18" t="n">
-        <v>63.18</v>
+        <v>-49.85</v>
       </c>
       <c r="L18" t="n">
-        <v>70.14</v>
+        <v>62.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:41:37</t>
+          <t>05:42:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="F19" t="n">
-        <v>7.31</v>
+        <v>10.7</v>
       </c>
       <c r="G19" t="n">
-        <v>327</v>
+        <v>315.8</v>
       </c>
       <c r="H19" t="n">
-        <v>34.9</v>
+        <v>59.2</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>28.93</v>
+        <v>31.6</v>
       </c>
       <c r="K19" t="n">
-        <v>66.83</v>
+        <v>85.42</v>
       </c>
       <c r="L19" t="n">
-        <v>72.81999999999999</v>
+        <v>91.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:45:58</t>
+          <t>05:46:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.13</v>
+        <v>2.88</v>
       </c>
       <c r="F20" t="n">
-        <v>10.7</v>
+        <v>5.71</v>
       </c>
       <c r="G20" t="n">
-        <v>313.2</v>
+        <v>332.3</v>
       </c>
       <c r="H20" t="n">
-        <v>50.6</v>
+        <v>41.9</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>-62.48</v>
+        <v>-60.08</v>
       </c>
       <c r="K20" t="n">
-        <v>-78.15000000000001</v>
+        <v>116.36</v>
       </c>
       <c r="L20" t="n">
-        <v>100.05</v>
+        <v>130.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:47:39</t>
+          <t>05:47:08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.48</v>
+        <v>3.23</v>
       </c>
       <c r="F21" t="n">
-        <v>8.800000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="G21" t="n">
-        <v>325.8</v>
+        <v>319</v>
       </c>
       <c r="H21" t="n">
-        <v>53.5</v>
+        <v>73.5</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>129.8</v>
+        <v>39.92</v>
       </c>
       <c r="K21" t="n">
-        <v>4.97</v>
+        <v>120.63</v>
       </c>
       <c r="L21" t="n">
-        <v>129.89</v>
+        <v>127.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:49:19</t>
+          <t>05:49:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="F22" t="n">
-        <v>7.24</v>
+        <v>7.38</v>
       </c>
       <c r="G22" t="n">
-        <v>320.8</v>
+        <v>324.8</v>
       </c>
       <c r="H22" t="n">
-        <v>27.9</v>
+        <v>60.9</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>23.72</v>
+        <v>98.73</v>
       </c>
       <c r="K22" t="n">
-        <v>-93</v>
+        <v>73.03</v>
       </c>
       <c r="L22" t="n">
-        <v>95.98</v>
+        <v>122.81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:53:58</t>
+          <t>05:52:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.25</v>
+        <v>3.21</v>
       </c>
       <c r="F23" t="n">
-        <v>5.02</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>322.1</v>
+        <v>331.3</v>
       </c>
       <c r="H23" t="n">
-        <v>43.8</v>
+        <v>32.6</v>
       </c>
       <c r="I23" t="n">
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>114.32</v>
+        <v>-87.11</v>
       </c>
       <c r="K23" t="n">
-        <v>25.6</v>
+        <v>61.64</v>
       </c>
       <c r="L23" t="n">
-        <v>117.15</v>
+        <v>106.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:54:47</t>
+          <t>05:53:37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="F24" t="n">
-        <v>10.01</v>
+        <v>8.49</v>
       </c>
       <c r="G24" t="n">
-        <v>332.5</v>
+        <v>322</v>
       </c>
       <c r="H24" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="I24" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-113.16</v>
+        <v>-160.48</v>
       </c>
       <c r="K24" t="n">
-        <v>91.84999999999999</v>
+        <v>-53.07</v>
       </c>
       <c r="L24" t="n">
-        <v>145.74</v>
+        <v>169.03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:56:03</t>
+          <t>05:55:10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.38</v>
+        <v>2.88</v>
       </c>
       <c r="F25" t="n">
-        <v>8.26</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>323.5</v>
+        <v>323.2</v>
       </c>
       <c r="H25" t="n">
-        <v>18.1</v>
+        <v>33</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>113.16</v>
+        <v>109.29</v>
       </c>
       <c r="K25" t="n">
-        <v>161.01</v>
+        <v>66.81</v>
       </c>
       <c r="L25" t="n">
-        <v>196.8</v>
+        <v>128.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:01:39</t>
+          <t>06:01:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="F26" t="n">
-        <v>9.380000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G26" t="n">
-        <v>314.3</v>
+        <v>331.3</v>
       </c>
       <c r="H26" t="n">
-        <v>40.8</v>
+        <v>47.3</v>
       </c>
       <c r="I26" t="n">
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-42.5</v>
+        <v>-201.47</v>
       </c>
       <c r="K26" t="n">
-        <v>192.37</v>
+        <v>137.95</v>
       </c>
       <c r="L26" t="n">
-        <v>197.01</v>
+        <v>244.17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:04:18</t>
+          <t>06:02:44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.6</v>
+        <v>3.17</v>
       </c>
       <c r="F27" t="n">
-        <v>9.18</v>
+        <v>9.25</v>
       </c>
       <c r="G27" t="n">
-        <v>334.6</v>
+        <v>319.9</v>
       </c>
       <c r="H27" t="n">
-        <v>39</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-48.56</v>
+        <v>-48.07</v>
       </c>
       <c r="K27" t="n">
-        <v>99.38</v>
+        <v>-296.24</v>
       </c>
       <c r="L27" t="n">
-        <v>110.61</v>
+        <v>300.12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:05:34</t>
+          <t>06:04:37</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.82</v>
+        <v>3.52</v>
       </c>
       <c r="F28" t="n">
-        <v>8.050000000000001</v>
+        <v>10.16</v>
       </c>
       <c r="G28" t="n">
-        <v>322.1</v>
+        <v>326.2</v>
       </c>
       <c r="H28" t="n">
-        <v>10.4</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-100.16</v>
+        <v>-192.22</v>
       </c>
       <c r="K28" t="n">
-        <v>-93.77</v>
+        <v>129.07</v>
       </c>
       <c r="L28" t="n">
-        <v>137.2</v>
+        <v>231.54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:15:21</t>
+          <t>06:14:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.08</v>
+        <v>2.68</v>
       </c>
       <c r="F29" t="n">
-        <v>9.4</v>
+        <v>7.71</v>
       </c>
       <c r="G29" t="n">
-        <v>320.8</v>
+        <v>327.4</v>
       </c>
       <c r="H29" t="n">
-        <v>48.9</v>
+        <v>59.3</v>
       </c>
       <c r="I29" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-22.32</v>
+        <v>30.72</v>
       </c>
       <c r="K29" t="n">
-        <v>41.06</v>
+        <v>35.66</v>
       </c>
       <c r="L29" t="n">
-        <v>46.74</v>
+        <v>47.07</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:16:21</t>
+          <t>06:15:19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.51</v>
+        <v>3.03</v>
       </c>
       <c r="F30" t="n">
-        <v>6.27</v>
+        <v>7.34</v>
       </c>
       <c r="G30" t="n">
-        <v>311.4</v>
+        <v>326.9</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>51.9</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-52.37</v>
+        <v>10.82</v>
       </c>
       <c r="K30" t="n">
-        <v>-44.06</v>
+        <v>-50.14</v>
       </c>
       <c r="L30" t="n">
-        <v>68.44</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:18:13</t>
+          <t>06:16:55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="F31" t="n">
-        <v>7.08</v>
+        <v>9.5</v>
       </c>
       <c r="G31" t="n">
-        <v>316.6</v>
+        <v>319.1</v>
       </c>
       <c r="H31" t="n">
-        <v>31.7</v>
+        <v>56.9</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.55</v>
+        <v>50.07</v>
       </c>
       <c r="K31" t="n">
-        <v>-52.08</v>
+        <v>25.46</v>
       </c>
       <c r="L31" t="n">
-        <v>53.13</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:24:18</t>
+          <t>06:21:43</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="F32" t="n">
-        <v>10.38</v>
+        <v>9.98</v>
       </c>
       <c r="G32" t="n">
-        <v>323.8</v>
+        <v>309.3</v>
       </c>
       <c r="H32" t="n">
-        <v>32</v>
+        <v>57.4</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-37.08</v>
+        <v>25.5</v>
       </c>
       <c r="K32" t="n">
-        <v>54.6</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>66.01000000000001</v>
+        <v>91.92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:26:05</t>
+          <t>06:22:38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.24</v>
+        <v>2.84</v>
       </c>
       <c r="F33" t="n">
-        <v>8.58</v>
+        <v>7.88</v>
       </c>
       <c r="G33" t="n">
-        <v>311.4</v>
+        <v>313.2</v>
       </c>
       <c r="H33" t="n">
-        <v>29.2</v>
+        <v>43.2</v>
       </c>
       <c r="I33" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>48.39</v>
+        <v>17.88</v>
       </c>
       <c r="K33" t="n">
-        <v>-71.13</v>
+        <v>-70.26000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>86.03</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:27:34</t>
+          <t>06:24:41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="F34" t="n">
-        <v>8.970000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="G34" t="n">
-        <v>318.7</v>
+        <v>322.3</v>
       </c>
       <c r="H34" t="n">
-        <v>63.1</v>
+        <v>59</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-72.36</v>
+        <v>-88.67</v>
       </c>
       <c r="K34" t="n">
-        <v>-34.61</v>
+        <v>-8.84</v>
       </c>
       <c r="L34" t="n">
-        <v>80.20999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:33:13</t>
+          <t>06:29:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.07</v>
+        <v>2.99</v>
       </c>
       <c r="F35" t="n">
-        <v>7.66</v>
+        <v>6.97</v>
       </c>
       <c r="G35" t="n">
-        <v>319.1</v>
+        <v>321.6</v>
       </c>
       <c r="H35" t="n">
-        <v>20.9</v>
+        <v>60.7</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>105.36</v>
+        <v>-34.31</v>
       </c>
       <c r="K35" t="n">
-        <v>-71.37</v>
+        <v>103.57</v>
       </c>
       <c r="L35" t="n">
-        <v>127.26</v>
+        <v>109.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:35:35</t>
+          <t>06:30:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="F36" t="n">
-        <v>9.58</v>
+        <v>5.71</v>
       </c>
       <c r="G36" t="n">
-        <v>312.4</v>
+        <v>321.2</v>
       </c>
       <c r="H36" t="n">
-        <v>42</v>
+        <v>40.3</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>111.82</v>
+        <v>-81.56</v>
       </c>
       <c r="K36" t="n">
-        <v>-18.05</v>
+        <v>-73.81</v>
       </c>
       <c r="L36" t="n">
-        <v>113.27</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:36:41</t>
+          <t>06:31:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="F37" t="n">
-        <v>9.550000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="G37" t="n">
-        <v>322.6</v>
+        <v>330.5</v>
       </c>
       <c r="H37" t="n">
-        <v>38.2</v>
+        <v>37</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-118.46</v>
+        <v>-87.20999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>66.67</v>
+        <v>-117.17</v>
       </c>
       <c r="L37" t="n">
-        <v>135.94</v>
+        <v>146.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:40:33</t>
+          <t>06:36:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="F38" t="n">
-        <v>7.66</v>
+        <v>3.45</v>
       </c>
       <c r="G38" t="n">
-        <v>307.2</v>
+        <v>323.4</v>
       </c>
       <c r="H38" t="n">
-        <v>55.5</v>
+        <v>13.5</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-158.77</v>
+        <v>-99.33</v>
       </c>
       <c r="K38" t="n">
-        <v>32.44</v>
+        <v>-142.7</v>
       </c>
       <c r="L38" t="n">
-        <v>162.05</v>
+        <v>173.87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:41:31</t>
+          <t>06:39:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="F39" t="n">
-        <v>8.06</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>326.1</v>
+        <v>318.6</v>
       </c>
       <c r="H39" t="n">
-        <v>43.8</v>
+        <v>62.1</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>140.15</v>
+        <v>-210.47</v>
       </c>
       <c r="K39" t="n">
-        <v>72.42</v>
+        <v>32.53</v>
       </c>
       <c r="L39" t="n">
-        <v>157.75</v>
+        <v>212.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:43:02</t>
+          <t>06:41:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="F40" t="n">
-        <v>8.75</v>
+        <v>10.7</v>
       </c>
       <c r="G40" t="n">
-        <v>323.3</v>
+        <v>318.8</v>
       </c>
       <c r="H40" t="n">
-        <v>72.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.59</v>
+        <v>-336.72</v>
       </c>
       <c r="K40" t="n">
-        <v>160.99</v>
+        <v>-136.55</v>
       </c>
       <c r="L40" t="n">
-        <v>161.48</v>
+        <v>363.35</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:47:37</t>
+          <t>06:46:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="F41" t="n">
-        <v>8.44</v>
+        <v>7.97</v>
       </c>
       <c r="G41" t="n">
-        <v>315</v>
+        <v>308.7</v>
       </c>
       <c r="H41" t="n">
-        <v>95.09999999999999</v>
+        <v>41.7</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J41" t="n">
-        <v>-151.85</v>
+        <v>234.41</v>
       </c>
       <c r="K41" t="n">
-        <v>160.9</v>
+        <v>35.98</v>
       </c>
       <c r="L41" t="n">
-        <v>221.24</v>
+        <v>237.16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:48:35</t>
+          <t>06:47:25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.87</v>
+        <v>3.84</v>
       </c>
       <c r="F42" t="n">
-        <v>7.52</v>
+        <v>10.7</v>
       </c>
       <c r="G42" t="n">
-        <v>320.9</v>
+        <v>331.2</v>
       </c>
       <c r="H42" t="n">
-        <v>56</v>
+        <v>60.5</v>
       </c>
       <c r="I42" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>152.79</v>
+        <v>271.72</v>
       </c>
       <c r="K42" t="n">
-        <v>22.07</v>
+        <v>58.78</v>
       </c>
       <c r="L42" t="n">
-        <v>154.37</v>
+        <v>278.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:50:03</t>
+          <t>06:49:01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.85</v>
+        <v>2.48</v>
       </c>
       <c r="F43" t="n">
-        <v>6.33</v>
+        <v>6.97</v>
       </c>
       <c r="G43" t="n">
-        <v>328.1</v>
+        <v>314.3</v>
       </c>
       <c r="H43" t="n">
-        <v>26.7</v>
+        <v>79.2</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-8.5</v>
+        <v>157.94</v>
       </c>
       <c r="K43" t="n">
-        <v>158.66</v>
+        <v>97.25</v>
       </c>
       <c r="L43" t="n">
-        <v>158.89</v>
+        <v>185.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:01:28</t>
+          <t>07:00:54</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.36</v>
+        <v>3.03</v>
       </c>
       <c r="F44" t="n">
-        <v>9.949999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="G44" t="n">
-        <v>316.1</v>
+        <v>322.8</v>
       </c>
       <c r="H44" t="n">
-        <v>53.5</v>
+        <v>66.5</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>29.54</v>
+        <v>26.15</v>
       </c>
       <c r="K44" t="n">
-        <v>40.29</v>
+        <v>51.27</v>
       </c>
       <c r="L44" t="n">
-        <v>49.95</v>
+        <v>57.56</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:02:14</t>
+          <t>07:03:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.38</v>
+        <v>3.73</v>
       </c>
       <c r="F45" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="G45" t="n">
-        <v>336.3</v>
+        <v>321.3</v>
       </c>
       <c r="H45" t="n">
-        <v>47.2</v>
+        <v>22.4</v>
       </c>
       <c r="I45" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>-50.02</v>
+        <v>4.64</v>
       </c>
       <c r="K45" t="n">
-        <v>35.19</v>
+        <v>-61.03</v>
       </c>
       <c r="L45" t="n">
-        <v>61.16</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:04:42</t>
+          <t>07:03:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.87</v>
+        <v>3.99</v>
       </c>
       <c r="F46" t="n">
-        <v>10.7</v>
+        <v>10.07</v>
       </c>
       <c r="G46" t="n">
-        <v>333.1</v>
+        <v>307.2</v>
       </c>
       <c r="H46" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>-76.09</v>
+        <v>-74.68000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-13.32</v>
+        <v>8.19</v>
       </c>
       <c r="L46" t="n">
-        <v>77.25</v>
+        <v>75.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:10:39</t>
+          <t>07:09:08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="F47" t="n">
-        <v>5.87</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>328.2</v>
+        <v>326.1</v>
       </c>
       <c r="H47" t="n">
-        <v>64</v>
+        <v>43.8</v>
       </c>
       <c r="I47" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>52.07</v>
+        <v>80.91</v>
       </c>
       <c r="K47" t="n">
-        <v>-44.45</v>
+        <v>21.97</v>
       </c>
       <c r="L47" t="n">
-        <v>68.45999999999999</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:11:59</t>
+          <t>07:10:49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="F48" t="n">
-        <v>6.48</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>323.7</v>
+        <v>323.3</v>
       </c>
       <c r="H48" t="n">
-        <v>47.6</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-48.44</v>
+        <v>4.44</v>
       </c>
       <c r="K48" t="n">
-        <v>-28.34</v>
+        <v>86.08</v>
       </c>
       <c r="L48" t="n">
-        <v>56.12</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:12:42</t>
+          <t>07:11:58</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="F49" t="n">
-        <v>7.84</v>
+        <v>8.77</v>
       </c>
       <c r="G49" t="n">
-        <v>323.1</v>
+        <v>315</v>
       </c>
       <c r="H49" t="n">
-        <v>61.6</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>20.25</v>
+        <v>-62.64</v>
       </c>
       <c r="K49" t="n">
-        <v>66.87</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>69.87</v>
+        <v>92.01000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:17:35</t>
+          <t>07:17:01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.17</v>
+        <v>2.96</v>
       </c>
       <c r="F50" t="n">
-        <v>7.5</v>
+        <v>7.91</v>
       </c>
       <c r="G50" t="n">
-        <v>319</v>
+        <v>320.9</v>
       </c>
       <c r="H50" t="n">
-        <v>59.3</v>
+        <v>56</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J50" t="n">
-        <v>100.07</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-65.48999999999999</v>
+        <v>-3.01</v>
       </c>
       <c r="L50" t="n">
-        <v>119.59</v>
+        <v>88.76000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:18:42</t>
+          <t>07:18:38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="F51" t="n">
-        <v>5.68</v>
+        <v>6.72</v>
       </c>
       <c r="G51" t="n">
-        <v>323.6</v>
+        <v>328.1</v>
       </c>
       <c r="H51" t="n">
-        <v>56.5</v>
+        <v>26.7</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-88.34</v>
+        <v>5.7</v>
       </c>
       <c r="K51" t="n">
-        <v>-12.65</v>
+        <v>91.08</v>
       </c>
       <c r="L51" t="n">
-        <v>89.23999999999999</v>
+        <v>91.26000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:21:01</t>
+          <t>07:20:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="F52" t="n">
-        <v>10.7</v>
+        <v>10.23</v>
       </c>
       <c r="G52" t="n">
-        <v>330.4</v>
+        <v>316.1</v>
       </c>
       <c r="H52" t="n">
-        <v>33.6</v>
+        <v>53.5</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>18.05</v>
+        <v>91.59</v>
       </c>
       <c r="K52" t="n">
-        <v>-102.62</v>
+        <v>75.78</v>
       </c>
       <c r="L52" t="n">
-        <v>104.2</v>
+        <v>118.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:24:57</t>
+          <t>07:25:37</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="F53" t="n">
-        <v>9.380000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="G53" t="n">
-        <v>310.1</v>
+        <v>336.3</v>
       </c>
       <c r="H53" t="n">
-        <v>40.9</v>
+        <v>47.2</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-40.78</v>
+        <v>-214.06</v>
       </c>
       <c r="K53" t="n">
-        <v>126.63</v>
+        <v>108.83</v>
       </c>
       <c r="L53" t="n">
-        <v>133.04</v>
+        <v>240.14</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:27:19</t>
+          <t>07:26:41</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.31</v>
+        <v>3.93</v>
       </c>
       <c r="F54" t="n">
-        <v>7.92</v>
+        <v>10.7</v>
       </c>
       <c r="G54" t="n">
-        <v>320.8</v>
+        <v>333.1</v>
       </c>
       <c r="H54" t="n">
-        <v>10.6</v>
+        <v>55.2</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>131.76</v>
+        <v>-281.57</v>
       </c>
       <c r="K54" t="n">
-        <v>58.68</v>
+        <v>-132.78</v>
       </c>
       <c r="L54" t="n">
-        <v>144.24</v>
+        <v>311.31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:28:14</t>
+          <t>07:28:39</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.84</v>
+        <v>2.61</v>
       </c>
       <c r="F55" t="n">
-        <v>6.77</v>
+        <v>6.08</v>
       </c>
       <c r="G55" t="n">
-        <v>319.3</v>
+        <v>328.2</v>
       </c>
       <c r="H55" t="n">
-        <v>29.4</v>
+        <v>64</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J55" t="n">
-        <v>-23.15</v>
+        <v>129.93</v>
       </c>
       <c r="K55" t="n">
-        <v>156.86</v>
+        <v>-124.19</v>
       </c>
       <c r="L55" t="n">
-        <v>158.56</v>
+        <v>179.74</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:32:47</t>
+          <t>07:32:36</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="F56" t="n">
-        <v>7.17</v>
+        <v>6.74</v>
       </c>
       <c r="G56" t="n">
-        <v>323.9</v>
+        <v>323.7</v>
       </c>
       <c r="H56" t="n">
-        <v>56.1</v>
+        <v>47.6</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-153.58</v>
+        <v>-139.23</v>
       </c>
       <c r="K56" t="n">
-        <v>-72.3</v>
+        <v>-128.33</v>
       </c>
       <c r="L56" t="n">
-        <v>169.75</v>
+        <v>189.35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:33:33</t>
+          <t>07:34:07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.22</v>
+        <v>2.97</v>
       </c>
       <c r="F57" t="n">
-        <v>8.859999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>322</v>
+        <v>323.1</v>
       </c>
       <c r="H57" t="n">
-        <v>57.6</v>
+        <v>61.6</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-235.61</v>
+        <v>108.58</v>
       </c>
       <c r="K57" t="n">
-        <v>117.37</v>
+        <v>205.6</v>
       </c>
       <c r="L57" t="n">
-        <v>263.23</v>
+        <v>232.51</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:36:04</t>
+          <t>07:36:24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="F58" t="n">
-        <v>7.93</v>
+        <v>7.74</v>
       </c>
       <c r="G58" t="n">
-        <v>324.2</v>
+        <v>319</v>
       </c>
       <c r="H58" t="n">
-        <v>75.90000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-47.02</v>
+        <v>271.42</v>
       </c>
       <c r="K58" t="n">
-        <v>221.55</v>
+        <v>-196.01</v>
       </c>
       <c r="L58" t="n">
-        <v>226.48</v>
+        <v>334.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:45:15</t>
+          <t>07:46:36</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.19</v>
+        <v>2.94</v>
       </c>
       <c r="F59" t="n">
-        <v>9.9</v>
+        <v>6.03</v>
       </c>
       <c r="G59" t="n">
-        <v>323.7</v>
+        <v>323.6</v>
       </c>
       <c r="H59" t="n">
-        <v>48.4</v>
+        <v>56.5</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.42</v>
+        <v>-47.65</v>
       </c>
       <c r="K59" t="n">
-        <v>54.69</v>
+        <v>-17.12</v>
       </c>
       <c r="L59" t="n">
-        <v>54.96</v>
+        <v>50.63</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:46:25</t>
+          <t>07:47:52</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.26</v>
+        <v>3.62</v>
       </c>
       <c r="F60" t="n">
-        <v>8.19</v>
+        <v>10.7</v>
       </c>
       <c r="G60" t="n">
-        <v>312.3</v>
+        <v>330.4</v>
       </c>
       <c r="H60" t="n">
-        <v>97.2</v>
+        <v>33.6</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-40.81</v>
+        <v>15.93</v>
       </c>
       <c r="K60" t="n">
-        <v>59.53</v>
+        <v>-62.31</v>
       </c>
       <c r="L60" t="n">
-        <v>72.18000000000001</v>
+        <v>64.31999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:48:16</t>
+          <t>07:50:15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.48</v>
+        <v>3.05</v>
       </c>
       <c r="F61" t="n">
-        <v>9.52</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>325.2</v>
+        <v>310.1</v>
       </c>
       <c r="H61" t="n">
-        <v>35.1</v>
+        <v>40.9</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-49.49</v>
+        <v>-9.32</v>
       </c>
       <c r="K61" t="n">
-        <v>17.7</v>
+        <v>51.49</v>
       </c>
       <c r="L61" t="n">
-        <v>52.56</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:51:59</t>
+          <t>07:55:51</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.88</v>
+        <v>3.39</v>
       </c>
       <c r="F62" t="n">
-        <v>6.15</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>332.8</v>
+        <v>320.8</v>
       </c>
       <c r="H62" t="n">
-        <v>27.1</v>
+        <v>10.6</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-29.85</v>
+        <v>82.95</v>
       </c>
       <c r="K62" t="n">
-        <v>83.88</v>
+        <v>16.18</v>
       </c>
       <c r="L62" t="n">
-        <v>89.03</v>
+        <v>84.51000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:54:11</t>
+          <t>07:57:11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.62</v>
+        <v>2.92</v>
       </c>
       <c r="F63" t="n">
-        <v>8.779999999999999</v>
+        <v>7.13</v>
       </c>
       <c r="G63" t="n">
-        <v>330.9</v>
+        <v>319.3</v>
       </c>
       <c r="H63" t="n">
-        <v>63</v>
+        <v>29.4</v>
       </c>
       <c r="I63" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-17.55</v>
+        <v>-1.74</v>
       </c>
       <c r="K63" t="n">
-        <v>92.77</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>94.41</v>
+        <v>93.73</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:56:32</t>
+          <t>07:58:04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.65</v>
+        <v>3.47</v>
       </c>
       <c r="F64" t="n">
-        <v>10.22</v>
+        <v>7.5</v>
       </c>
       <c r="G64" t="n">
-        <v>325.8</v>
+        <v>323.9</v>
       </c>
       <c r="H64" t="n">
-        <v>16.4</v>
+        <v>56.1</v>
       </c>
       <c r="I64" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-70.39</v>
+        <v>-58.92</v>
       </c>
       <c r="K64" t="n">
-        <v>-55.73</v>
+        <v>-48.44</v>
       </c>
       <c r="L64" t="n">
-        <v>89.78</v>
+        <v>76.28</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:00:30</t>
+          <t>08:01:41</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="F65" t="n">
-        <v>8.449999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="G65" t="n">
-        <v>326.6</v>
+        <v>322</v>
       </c>
       <c r="H65" t="n">
-        <v>64.2</v>
+        <v>57.6</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>33.26</v>
+        <v>-159.39</v>
       </c>
       <c r="K65" t="n">
-        <v>126.72</v>
+        <v>57.68</v>
       </c>
       <c r="L65" t="n">
-        <v>131.01</v>
+        <v>169.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:02:05</t>
+          <t>08:04:05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.79</v>
+        <v>3.37</v>
       </c>
       <c r="F66" t="n">
-        <v>10.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>316</v>
+        <v>324.2</v>
       </c>
       <c r="H66" t="n">
-        <v>35.9</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>121.8</v>
+        <v>-14.43</v>
       </c>
       <c r="K66" t="n">
-        <v>-65.40000000000001</v>
+        <v>144.78</v>
       </c>
       <c r="L66" t="n">
-        <v>138.24</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:03:47</t>
+          <t>08:05:10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.61</v>
+        <v>3.24</v>
       </c>
       <c r="F67" t="n">
-        <v>10.7</v>
+        <v>10.14</v>
       </c>
       <c r="G67" t="n">
-        <v>325.2</v>
+        <v>323.7</v>
       </c>
       <c r="H67" t="n">
-        <v>16.5</v>
+        <v>48.4</v>
       </c>
       <c r="I67" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>20.78</v>
+        <v>4.72</v>
       </c>
       <c r="K67" t="n">
-        <v>121.67</v>
+        <v>129.57</v>
       </c>
       <c r="L67" t="n">
-        <v>123.44</v>
+        <v>129.66</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:09:27</t>
+          <t>08:09:42</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.22</v>
+        <v>3.33</v>
       </c>
       <c r="F68" t="n">
-        <v>10.7</v>
+        <v>8.51</v>
       </c>
       <c r="G68" t="n">
-        <v>322</v>
+        <v>312.3</v>
       </c>
       <c r="H68" t="n">
-        <v>20.2</v>
+        <v>97.2</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-178.93</v>
+        <v>-146.13</v>
       </c>
       <c r="K68" t="n">
-        <v>4.92</v>
+        <v>244.77</v>
       </c>
       <c r="L68" t="n">
-        <v>179</v>
+        <v>285.07</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:11:37</t>
+          <t>08:11:24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.64</v>
+        <v>3.54</v>
       </c>
       <c r="F69" t="n">
-        <v>10.7</v>
+        <v>9.81</v>
       </c>
       <c r="G69" t="n">
-        <v>321.9</v>
+        <v>325.2</v>
       </c>
       <c r="H69" t="n">
-        <v>31.4</v>
+        <v>35.1</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>277.38</v>
+        <v>-201.88</v>
       </c>
       <c r="K69" t="n">
-        <v>375.14</v>
+        <v>36.83</v>
       </c>
       <c r="L69" t="n">
-        <v>466.55</v>
+        <v>205.22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:13:40</t>
+          <t>08:13:26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="F70" t="n">
-        <v>10.7</v>
+        <v>6.42</v>
       </c>
       <c r="G70" t="n">
-        <v>309.8</v>
+        <v>332.8</v>
       </c>
       <c r="H70" t="n">
-        <v>43.1</v>
+        <v>27.1</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-112.02</v>
+        <v>-70.68000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>3.75</v>
+        <v>221.43</v>
       </c>
       <c r="L70" t="n">
-        <v>112.08</v>
+        <v>232.44</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:19:47</t>
+          <t>08:17:22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3022,31 +3022,31 @@
         <v>3.68</v>
       </c>
       <c r="F71" t="n">
-        <v>10.7</v>
+        <v>9.08</v>
       </c>
       <c r="G71" t="n">
-        <v>329.6</v>
+        <v>330.9</v>
       </c>
       <c r="H71" t="n">
-        <v>17.1</v>
+        <v>63</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J71" t="n">
-        <v>-24.56</v>
+        <v>-30.29</v>
       </c>
       <c r="K71" t="n">
-        <v>229.1</v>
+        <v>321.72</v>
       </c>
       <c r="L71" t="n">
-        <v>230.41</v>
+        <v>323.14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:21:16</t>
+          <t>08:19:38</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="F72" t="n">
-        <v>9.41</v>
+        <v>10.52</v>
       </c>
       <c r="G72" t="n">
-        <v>313.2</v>
+        <v>325.8</v>
       </c>
       <c r="H72" t="n">
-        <v>39.9</v>
+        <v>16.4</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J72" t="n">
-        <v>-8.960000000000001</v>
+        <v>-184.25</v>
       </c>
       <c r="K72" t="n">
-        <v>-278.77</v>
+        <v>-244.74</v>
       </c>
       <c r="L72" t="n">
-        <v>278.91</v>
+        <v>306.34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:23:48</t>
+          <t>08:21:43</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="F73" t="n">
-        <v>10.7</v>
+        <v>8.73</v>
       </c>
       <c r="G73" t="n">
-        <v>313.3</v>
+        <v>326.6</v>
       </c>
       <c r="H73" t="n">
-        <v>63.7</v>
+        <v>64.2</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-183.25</v>
+        <v>141.37</v>
       </c>
       <c r="K73" t="n">
-        <v>188.47</v>
+        <v>283.28</v>
       </c>
       <c r="L73" t="n">
-        <v>262.87</v>
+        <v>316.59</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:32:52</t>
+          <t>08:32:19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.44</v>
+        <v>3.87</v>
       </c>
       <c r="F74" t="n">
         <v>10.7</v>
       </c>
       <c r="G74" t="n">
-        <v>315.5</v>
+        <v>316</v>
       </c>
       <c r="H74" t="n">
-        <v>51.1</v>
+        <v>35.9</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>-54.01</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>26.01</v>
+        <v>-42.33</v>
       </c>
       <c r="L74" t="n">
-        <v>59.95</v>
+        <v>79.09</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:34:54</t>
+          <t>08:34:39</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.16</v>
+        <v>3.69</v>
       </c>
       <c r="F75" t="n">
         <v>10.7</v>
       </c>
       <c r="G75" t="n">
-        <v>314.5</v>
+        <v>325.2</v>
       </c>
       <c r="H75" t="n">
-        <v>43.5</v>
+        <v>16.5</v>
       </c>
       <c r="I75" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>-17.23</v>
+        <v>25.31</v>
       </c>
       <c r="K75" t="n">
-        <v>45.1</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>48.28</v>
+        <v>70.52</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:36:41</t>
+          <t>08:36:25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="F76" t="n">
-        <v>9.51</v>
+        <v>10.7</v>
       </c>
       <c r="G76" t="n">
         <v>322</v>
       </c>
       <c r="H76" t="n">
-        <v>40.9</v>
+        <v>20.2</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>-46.67</v>
+        <v>-67</v>
       </c>
       <c r="K76" t="n">
-        <v>12.92</v>
+        <v>-11.59</v>
       </c>
       <c r="L76" t="n">
-        <v>48.43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:41:45</t>
+          <t>08:40:40</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.16</v>
+        <v>4.71</v>
       </c>
       <c r="F77" t="n">
-        <v>7.45</v>
+        <v>10.7</v>
       </c>
       <c r="G77" t="n">
-        <v>328.4</v>
+        <v>321.9</v>
       </c>
       <c r="H77" t="n">
-        <v>48.1</v>
+        <v>31.4</v>
       </c>
       <c r="I77" t="n">
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>47.79</v>
+        <v>186.1</v>
       </c>
       <c r="K77" t="n">
-        <v>54.57</v>
+        <v>171.68</v>
       </c>
       <c r="L77" t="n">
-        <v>72.54000000000001</v>
+        <v>253.19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:43:56</t>
+          <t>08:41:46</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.14</v>
+        <v>3.47</v>
       </c>
       <c r="F78" t="n">
-        <v>9.289999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G78" t="n">
-        <v>310</v>
+        <v>309.8</v>
       </c>
       <c r="H78" t="n">
-        <v>51.5</v>
+        <v>43.1</v>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>-43.28</v>
+        <v>41.48</v>
       </c>
       <c r="K78" t="n">
-        <v>83.28</v>
+        <v>-43.51</v>
       </c>
       <c r="L78" t="n">
-        <v>93.86</v>
+        <v>60.11</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:45:58</t>
+          <t>08:43:16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="F79" t="n">
-        <v>9.529999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="G79" t="n">
-        <v>315.6</v>
+        <v>314.7</v>
       </c>
       <c r="H79" t="n">
-        <v>55.9</v>
+        <v>54.9</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-67.52</v>
+        <v>63.07</v>
       </c>
       <c r="K79" t="n">
-        <v>5.61</v>
+        <v>72.27</v>
       </c>
       <c r="L79" t="n">
-        <v>67.75</v>
+        <v>95.92</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:50:10</t>
+          <t>08:47:11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.16</v>
+        <v>3.94</v>
       </c>
       <c r="F80" t="n">
-        <v>7.76</v>
+        <v>10.7</v>
       </c>
       <c r="G80" t="n">
-        <v>330.8</v>
+        <v>330.5</v>
       </c>
       <c r="H80" t="n">
-        <v>79.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-81.28</v>
+        <v>-98.20999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-31.87</v>
+        <v>113.13</v>
       </c>
       <c r="L80" t="n">
-        <v>87.3</v>
+        <v>149.81</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:51:39</t>
+          <t>08:49:07</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.51</v>
+        <v>3.73</v>
       </c>
       <c r="F81" t="n">
-        <v>10.45</v>
+        <v>10.7</v>
       </c>
       <c r="G81" t="n">
-        <v>320.2</v>
+        <v>328.2</v>
       </c>
       <c r="H81" t="n">
-        <v>38.2</v>
+        <v>74.3</v>
       </c>
       <c r="I81" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-122.1</v>
+        <v>157.11</v>
       </c>
       <c r="K81" t="n">
-        <v>30.02</v>
+        <v>-60.02</v>
       </c>
       <c r="L81" t="n">
-        <v>125.74</v>
+        <v>168.18</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:54:29</t>
+          <t>08:50:06</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.64</v>
+        <v>3.81</v>
       </c>
       <c r="F82" t="n">
         <v>10.7</v>
       </c>
       <c r="G82" t="n">
-        <v>334.1</v>
+        <v>317.7</v>
       </c>
       <c r="H82" t="n">
-        <v>21.4</v>
+        <v>40.6</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>148.04</v>
+        <v>115.95</v>
       </c>
       <c r="K82" t="n">
-        <v>-86.73</v>
+        <v>48.12</v>
       </c>
       <c r="L82" t="n">
-        <v>171.57</v>
+        <v>125.54</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:58:53</t>
+          <t>08:53:49</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="F83" t="n">
-        <v>10.31</v>
+        <v>9.92</v>
       </c>
       <c r="G83" t="n">
-        <v>323.2</v>
+        <v>329.3</v>
       </c>
       <c r="H83" t="n">
-        <v>49.2</v>
+        <v>21</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>23.16</v>
+        <v>-236.64</v>
       </c>
       <c r="K83" t="n">
-        <v>179.3</v>
+        <v>39.36</v>
       </c>
       <c r="L83" t="n">
-        <v>180.79</v>
+        <v>239.89</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:01:05</t>
+          <t>08:55:40</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.29</v>
+        <v>3.35</v>
       </c>
       <c r="F84" t="n">
-        <v>10.7</v>
+        <v>9.32</v>
       </c>
       <c r="G84" t="n">
-        <v>332.6</v>
+        <v>327.5</v>
       </c>
       <c r="H84" t="n">
-        <v>56.4</v>
+        <v>42.1</v>
       </c>
       <c r="I84" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-35.62</v>
+        <v>111.27</v>
       </c>
       <c r="K84" t="n">
-        <v>227.16</v>
+        <v>172.66</v>
       </c>
       <c r="L84" t="n">
-        <v>229.94</v>
+        <v>205.41</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:02:29</t>
+          <t>08:57:17</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="F85" t="n">
-        <v>10.04</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>315.6</v>
+        <v>337.7</v>
       </c>
       <c r="H85" t="n">
-        <v>60.9</v>
+        <v>19.8</v>
       </c>
       <c r="I85" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>193.24</v>
+        <v>141.06</v>
       </c>
       <c r="K85" t="n">
-        <v>-47.53</v>
+        <v>136.82</v>
       </c>
       <c r="L85" t="n">
-        <v>199</v>
+        <v>196.51</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:06:44</t>
+          <t>09:00:56</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="F86" t="n">
-        <v>9.27</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>321.5</v>
+        <v>313.3</v>
       </c>
       <c r="H86" t="n">
-        <v>42.6</v>
+        <v>47.4</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>247.51</v>
+        <v>204.69</v>
       </c>
       <c r="K86" t="n">
-        <v>152.01</v>
+        <v>186.08</v>
       </c>
       <c r="L86" t="n">
-        <v>290.46</v>
+        <v>276.63</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:08:14</t>
+          <t>09:02:15</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.16</v>
+        <v>3.95</v>
       </c>
       <c r="F87" t="n">
-        <v>6.97</v>
+        <v>9.77</v>
       </c>
       <c r="G87" t="n">
-        <v>323.7</v>
+        <v>333.8</v>
       </c>
       <c r="H87" t="n">
-        <v>34</v>
+        <v>25.8</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J87" t="n">
-        <v>197.26</v>
+        <v>-81.13</v>
       </c>
       <c r="K87" t="n">
-        <v>-133.39</v>
+        <v>337.3</v>
       </c>
       <c r="L87" t="n">
-        <v>238.13</v>
+        <v>346.92</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:09:23</t>
+          <t>09:04:40</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.72</v>
+        <v>3.24</v>
       </c>
       <c r="F88" t="n">
         <v>10.7</v>
       </c>
       <c r="G88" t="n">
-        <v>329.2</v>
+        <v>313.6</v>
       </c>
       <c r="H88" t="n">
-        <v>54.7</v>
+        <v>54.6</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J88" t="n">
-        <v>-216.62</v>
+        <v>-222.19</v>
       </c>
       <c r="K88" t="n">
-        <v>-182.91</v>
+        <v>-218.84</v>
       </c>
       <c r="L88" t="n">
-        <v>283.51</v>
+        <v>311.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="K14" t="n">
-        <v>-51.83</v>
+        <v>-55.25</v>
       </c>
       <c r="L14" t="n">
-        <v>51.88</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>38.74</v>
+        <v>43.94</v>
       </c>
       <c r="K15" t="n">
-        <v>10.04</v>
+        <v>11.39</v>
       </c>
       <c r="L15" t="n">
-        <v>40.02</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-49.79</v>
+        <v>-49.2</v>
       </c>
       <c r="K16" t="n">
-        <v>-50.77</v>
+        <v>-50.17</v>
       </c>
       <c r="L16" t="n">
-        <v>71.11</v>
+        <v>70.27</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-43.41</v>
+        <v>-50.09</v>
       </c>
       <c r="K17" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="L17" t="n">
-        <v>43.43</v>
+        <v>50.11</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-66.02</v>
+        <v>-62.46</v>
       </c>
       <c r="K18" t="n">
-        <v>-51.84</v>
+        <v>-49.05</v>
       </c>
       <c r="L18" t="n">
-        <v>83.94</v>
+        <v>79.42</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>116.79</v>
+        <v>107.55</v>
       </c>
       <c r="K19" t="n">
-        <v>-82.01000000000001</v>
+        <v>-75.52</v>
       </c>
       <c r="L19" t="n">
-        <v>142.71</v>
+        <v>131.42</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-78.31999999999999</v>
+        <v>-84.81999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>69.47</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>104.69</v>
+        <v>113.38</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>79.53</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-49.21</v>
+        <v>-51.5</v>
       </c>
       <c r="L21" t="n">
-        <v>93.53</v>
+        <v>97.89</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-6.77</v>
+        <v>-7.31</v>
       </c>
       <c r="K22" t="n">
-        <v>102.25</v>
+        <v>110.32</v>
       </c>
       <c r="L22" t="n">
-        <v>102.47</v>
+        <v>110.56</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-40.72</v>
+        <v>-47.19</v>
       </c>
       <c r="K23" t="n">
-        <v>109.81</v>
+        <v>127.25</v>
       </c>
       <c r="L23" t="n">
-        <v>117.11</v>
+        <v>135.72</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-155.48</v>
+        <v>-158.64</v>
       </c>
       <c r="K24" t="n">
-        <v>70.42</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>170.69</v>
+        <v>174.16</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-150.74</v>
+        <v>-165.57</v>
       </c>
       <c r="K25" t="n">
-        <v>33.28</v>
+        <v>36.55</v>
       </c>
       <c r="L25" t="n">
-        <v>154.37</v>
+        <v>169.56</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-202.86</v>
+        <v>-230.48</v>
       </c>
       <c r="K26" t="n">
-        <v>-14.95</v>
+        <v>-16.98</v>
       </c>
       <c r="L26" t="n">
-        <v>203.41</v>
+        <v>231.1</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>118.95</v>
+        <v>134.57</v>
       </c>
       <c r="K27" t="n">
-        <v>-176.34</v>
+        <v>-199.5</v>
       </c>
       <c r="L27" t="n">
-        <v>212.71</v>
+        <v>240.64</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-197.51</v>
+        <v>-225.09</v>
       </c>
       <c r="K28" t="n">
-        <v>81.67</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>213.73</v>
+        <v>243.57</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>33.44</v>
+        <v>36.5</v>
       </c>
       <c r="K29" t="n">
-        <v>-25.05</v>
+        <v>-27.35</v>
       </c>
       <c r="L29" t="n">
-        <v>41.78</v>
+        <v>45.61</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.45</v>
+        <v>-3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>-59.9</v>
+        <v>-60.76</v>
       </c>
       <c r="L30" t="n">
-        <v>60</v>
+        <v>60.86</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-43.55</v>
+        <v>-45.91</v>
       </c>
       <c r="K31" t="n">
-        <v>-22.54</v>
+        <v>-23.77</v>
       </c>
       <c r="L31" t="n">
-        <v>49.04</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-15.15</v>
+        <v>-15.84</v>
       </c>
       <c r="K32" t="n">
-        <v>68.11</v>
+        <v>71.2</v>
       </c>
       <c r="L32" t="n">
-        <v>69.78</v>
+        <v>72.94</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>38.01</v>
+        <v>39.24</v>
       </c>
       <c r="K33" t="n">
-        <v>-60.37</v>
+        <v>-62.33</v>
       </c>
       <c r="L33" t="n">
-        <v>71.34</v>
+        <v>73.66</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-96</v>
+        <v>-89.37</v>
       </c>
       <c r="K34" t="n">
-        <v>76.70999999999999</v>
+        <v>71.41</v>
       </c>
       <c r="L34" t="n">
-        <v>122.88</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-72.19</v>
+        <v>-74.84999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-85.02</v>
+        <v>-88.15000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>111.53</v>
+        <v>115.64</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-52.24</v>
+        <v>-61.19</v>
       </c>
       <c r="K36" t="n">
-        <v>-61.16</v>
+        <v>-71.64</v>
       </c>
       <c r="L36" t="n">
-        <v>80.44</v>
+        <v>94.22</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-76.8</v>
+        <v>-86.09999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-50.24</v>
+        <v>-56.32</v>
       </c>
       <c r="L37" t="n">
-        <v>91.77</v>
+        <v>102.89</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>31</v>
       </c>
       <c r="J38" t="n">
-        <v>-114.34</v>
+        <v>-134.03</v>
       </c>
       <c r="K38" t="n">
-        <v>-23.74</v>
+        <v>-27.83</v>
       </c>
       <c r="L38" t="n">
-        <v>116.78</v>
+        <v>136.88</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-92.43000000000001</v>
+        <v>-110.43</v>
       </c>
       <c r="K39" t="n">
-        <v>-57.93</v>
+        <v>-69.20999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>109.08</v>
+        <v>130.32</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>97.08</v>
+        <v>113.93</v>
       </c>
       <c r="K40" t="n">
-        <v>83.8</v>
+        <v>98.34</v>
       </c>
       <c r="L40" t="n">
-        <v>128.25</v>
+        <v>150.5</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>-20.27</v>
+        <v>-24.55</v>
       </c>
       <c r="K41" t="n">
-        <v>-172.35</v>
+        <v>-208.72</v>
       </c>
       <c r="L41" t="n">
-        <v>173.54</v>
+        <v>210.16</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-15.13</v>
+        <v>-17.86</v>
       </c>
       <c r="K42" t="n">
-        <v>174.9</v>
+        <v>206.54</v>
       </c>
       <c r="L42" t="n">
-        <v>175.55</v>
+        <v>207.31</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-172.85</v>
+        <v>-197.08</v>
       </c>
       <c r="K43" t="n">
-        <v>-9.58</v>
+        <v>-10.92</v>
       </c>
       <c r="L43" t="n">
-        <v>173.12</v>
+        <v>197.39</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>21.43</v>
+        <v>23.32</v>
       </c>
       <c r="K44" t="n">
-        <v>-48.99</v>
+        <v>-53.3</v>
       </c>
       <c r="L44" t="n">
-        <v>53.47</v>
+        <v>58.18</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>75.97</v>
+        <v>73.17</v>
       </c>
       <c r="K45" t="n">
-        <v>49.4</v>
+        <v>47.58</v>
       </c>
       <c r="L45" t="n">
-        <v>90.62</v>
+        <v>87.28</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>18.51</v>
+        <v>19.19</v>
       </c>
       <c r="K46" t="n">
-        <v>-41.71</v>
+        <v>-43.25</v>
       </c>
       <c r="L46" t="n">
-        <v>45.63</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>46.44</v>
+        <v>46.56</v>
       </c>
       <c r="K47" t="n">
-        <v>-66.45</v>
+        <v>-66.63</v>
       </c>
       <c r="L47" t="n">
-        <v>81.06999999999999</v>
+        <v>81.28</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-72.88</v>
+        <v>-75.62</v>
       </c>
       <c r="K48" t="n">
-        <v>-10.18</v>
+        <v>-10.56</v>
       </c>
       <c r="L48" t="n">
-        <v>73.59</v>
+        <v>76.36</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-63.09</v>
+        <v>-68.16</v>
       </c>
       <c r="K49" t="n">
-        <v>12.77</v>
+        <v>13.8</v>
       </c>
       <c r="L49" t="n">
-        <v>64.37</v>
+        <v>69.54000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-66.3</v>
+        <v>-73.83</v>
       </c>
       <c r="K50" t="n">
-        <v>-56.05</v>
+        <v>-62.41</v>
       </c>
       <c r="L50" t="n">
-        <v>86.81999999999999</v>
+        <v>96.67</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>77.94</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-57.3</v>
+        <v>-63.77</v>
       </c>
       <c r="L51" t="n">
-        <v>96.73999999999999</v>
+        <v>107.66</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-8.109999999999999</v>
+        <v>-9.16</v>
       </c>
       <c r="K52" t="n">
-        <v>103.34</v>
+        <v>116.72</v>
       </c>
       <c r="L52" t="n">
-        <v>103.65</v>
+        <v>117.08</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-93.28</v>
+        <v>-116.48</v>
       </c>
       <c r="K53" t="n">
-        <v>-24.27</v>
+        <v>-30.31</v>
       </c>
       <c r="L53" t="n">
-        <v>96.38</v>
+        <v>120.35</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>96.78</v>
+        <v>102.02</v>
       </c>
       <c r="K54" t="n">
-        <v>135.37</v>
+        <v>142.7</v>
       </c>
       <c r="L54" t="n">
-        <v>166.41</v>
+        <v>175.42</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>124.4</v>
+        <v>145.14</v>
       </c>
       <c r="K55" t="n">
-        <v>-61.44</v>
+        <v>-71.68000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>138.74</v>
+        <v>161.88</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-122.4</v>
+        <v>-146.26</v>
       </c>
       <c r="K56" t="n">
-        <v>113.08</v>
+        <v>135.12</v>
       </c>
       <c r="L56" t="n">
-        <v>166.64</v>
+        <v>199.12</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-67.17</v>
+        <v>-82.23</v>
       </c>
       <c r="K57" t="n">
-        <v>117.7</v>
+        <v>144.09</v>
       </c>
       <c r="L57" t="n">
-        <v>135.51</v>
+        <v>165.9</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>197.43</v>
+        <v>222.77</v>
       </c>
       <c r="K58" t="n">
-        <v>136.5</v>
+        <v>154.02</v>
       </c>
       <c r="L58" t="n">
-        <v>240.03</v>
+        <v>270.83</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>29</v>
       </c>
       <c r="J59" t="n">
-        <v>47.97</v>
+        <v>47.32</v>
       </c>
       <c r="K59" t="n">
-        <v>-37.08</v>
+        <v>-36.57</v>
       </c>
       <c r="L59" t="n">
-        <v>60.63</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-42.69</v>
+        <v>-41.17</v>
       </c>
       <c r="K60" t="n">
-        <v>-68.3</v>
+        <v>-65.87</v>
       </c>
       <c r="L60" t="n">
-        <v>80.55</v>
+        <v>77.67</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-50.6</v>
+        <v>-50.86</v>
       </c>
       <c r="K61" t="n">
-        <v>47</v>
+        <v>47.24</v>
       </c>
       <c r="L61" t="n">
-        <v>69.06</v>
+        <v>69.42</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>75.17</v>
+        <v>78.95</v>
       </c>
       <c r="K62" t="n">
-        <v>7.67</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>75.56</v>
+        <v>79.36</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-81.03</v>
+        <v>-83.81</v>
       </c>
       <c r="K63" t="n">
-        <v>-12.71</v>
+        <v>-13.14</v>
       </c>
       <c r="L63" t="n">
-        <v>82.02</v>
+        <v>84.84</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>69.06999999999999</v>
+        <v>73.66</v>
       </c>
       <c r="K64" t="n">
-        <v>19.26</v>
+        <v>20.54</v>
       </c>
       <c r="L64" t="n">
-        <v>71.70999999999999</v>
+        <v>76.47</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>125.18</v>
+        <v>139.85</v>
       </c>
       <c r="K65" t="n">
-        <v>10.67</v>
+        <v>11.92</v>
       </c>
       <c r="L65" t="n">
-        <v>125.64</v>
+        <v>140.36</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>63.17</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-36.94</v>
+        <v>-44.46</v>
       </c>
       <c r="L66" t="n">
-        <v>73.18000000000001</v>
+        <v>88.09</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-24.03</v>
+        <v>-27.08</v>
       </c>
       <c r="K67" t="n">
-        <v>97.77</v>
+        <v>110.2</v>
       </c>
       <c r="L67" t="n">
-        <v>100.68</v>
+        <v>113.48</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-7.72</v>
+        <v>-9.58</v>
       </c>
       <c r="K68" t="n">
-        <v>-111.61</v>
+        <v>-138.49</v>
       </c>
       <c r="L68" t="n">
-        <v>111.87</v>
+        <v>138.82</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-102.97</v>
+        <v>-124.21</v>
       </c>
       <c r="K69" t="n">
-        <v>49.22</v>
+        <v>59.38</v>
       </c>
       <c r="L69" t="n">
-        <v>114.13</v>
+        <v>137.68</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-61.76</v>
+        <v>-70.78</v>
       </c>
       <c r="K70" t="n">
-        <v>-108.37</v>
+        <v>-124.2</v>
       </c>
       <c r="L70" t="n">
-        <v>124.74</v>
+        <v>142.95</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>134.94</v>
+        <v>176.02</v>
       </c>
       <c r="K71" t="n">
-        <v>36.26</v>
+        <v>47.3</v>
       </c>
       <c r="L71" t="n">
-        <v>139.73</v>
+        <v>182.27</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-182.54</v>
+        <v>-207.11</v>
       </c>
       <c r="K72" t="n">
-        <v>-122.92</v>
+        <v>-139.47</v>
       </c>
       <c r="L72" t="n">
-        <v>220.07</v>
+        <v>249.69</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-152.91</v>
+        <v>-192.05</v>
       </c>
       <c r="K73" t="n">
-        <v>-34.28</v>
+        <v>-43.06</v>
       </c>
       <c r="L73" t="n">
-        <v>156.7</v>
+        <v>196.81</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>-62.38</v>
+        <v>-61.66</v>
       </c>
       <c r="K74" t="n">
-        <v>-38.54</v>
+        <v>-38.1</v>
       </c>
       <c r="L74" t="n">
-        <v>73.33</v>
+        <v>72.48999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>25.05</v>
+        <v>28.67</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.47</v>
+        <v>-3.97</v>
       </c>
       <c r="L75" t="n">
-        <v>25.29</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>27.77</v>
+        <v>31.81</v>
       </c>
       <c r="K76" t="n">
-        <v>-26.66</v>
+        <v>-30.54</v>
       </c>
       <c r="L76" t="n">
-        <v>38.5</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>58.41</v>
+        <v>65.72</v>
       </c>
       <c r="K77" t="n">
-        <v>21</v>
+        <v>23.63</v>
       </c>
       <c r="L77" t="n">
-        <v>62.07</v>
+        <v>69.84</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-26.35</v>
+        <v>-27.13</v>
       </c>
       <c r="K78" t="n">
-        <v>84.18000000000001</v>
+        <v>86.66</v>
       </c>
       <c r="L78" t="n">
-        <v>88.20999999999999</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>30.59</v>
+        <v>35.01</v>
       </c>
       <c r="K79" t="n">
-        <v>-43.5</v>
+        <v>-49.78</v>
       </c>
       <c r="L79" t="n">
-        <v>53.18</v>
+        <v>60.86</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-99.26000000000001</v>
+        <v>-107.17</v>
       </c>
       <c r="K80" t="n">
-        <v>57.2</v>
+        <v>61.75</v>
       </c>
       <c r="L80" t="n">
-        <v>114.56</v>
+        <v>123.69</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-112.64</v>
+        <v>-117.05</v>
       </c>
       <c r="K81" t="n">
-        <v>-50.4</v>
+        <v>-52.38</v>
       </c>
       <c r="L81" t="n">
-        <v>123.4</v>
+        <v>128.24</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>-26.47</v>
+        <v>-27.63</v>
       </c>
       <c r="K82" t="n">
-        <v>120.01</v>
+        <v>125.26</v>
       </c>
       <c r="L82" t="n">
-        <v>122.9</v>
+        <v>128.27</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-66.3</v>
+        <v>-76.31</v>
       </c>
       <c r="K83" t="n">
-        <v>-128.4</v>
+        <v>-147.78</v>
       </c>
       <c r="L83" t="n">
-        <v>144.51</v>
+        <v>166.31</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>174.77</v>
+        <v>181.59</v>
       </c>
       <c r="K84" t="n">
-        <v>110.1</v>
+        <v>114.4</v>
       </c>
       <c r="L84" t="n">
-        <v>206.55</v>
+        <v>214.62</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-111.78</v>
+        <v>-132.38</v>
       </c>
       <c r="K85" t="n">
-        <v>82.03</v>
+        <v>97.16</v>
       </c>
       <c r="L85" t="n">
-        <v>138.65</v>
+        <v>164.21</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-180.93</v>
+        <v>-208.91</v>
       </c>
       <c r="K86" t="n">
-        <v>-108.99</v>
+        <v>-125.84</v>
       </c>
       <c r="L86" t="n">
-        <v>211.22</v>
+        <v>243.88</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>157.04</v>
+        <v>183.54</v>
       </c>
       <c r="K87" t="n">
-        <v>167.07</v>
+        <v>195.26</v>
       </c>
       <c r="L87" t="n">
-        <v>229.3</v>
+        <v>267.98</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>188.02</v>
+        <v>209.22</v>
       </c>
       <c r="K88" t="n">
-        <v>-168.78</v>
+        <v>-187.81</v>
       </c>
       <c r="L88" t="n">
-        <v>252.67</v>
+        <v>281.15</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-01.xlsx
+++ b/output/2024-05-01.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>2.33</v>
+        <v>2.82</v>
       </c>
       <c r="K14" t="n">
-        <v>-55.25</v>
+        <v>-67.03</v>
       </c>
       <c r="L14" t="n">
-        <v>55.3</v>
+        <v>67.09</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>43.94</v>
+        <v>45.02</v>
       </c>
       <c r="K15" t="n">
-        <v>11.39</v>
+        <v>11.67</v>
       </c>
       <c r="L15" t="n">
-        <v>45.39</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="16">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>107.55</v>
+        <v>109.71</v>
       </c>
       <c r="K19" t="n">
-        <v>-75.52</v>
+        <v>-77.04000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>131.42</v>
+        <v>134.05</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>36.5</v>
+        <v>37.03</v>
       </c>
       <c r="K29" t="n">
-        <v>-27.35</v>
+        <v>-27.75</v>
       </c>
       <c r="L29" t="n">
-        <v>45.61</v>
+        <v>46.27</v>
       </c>
     </row>
     <row r="30">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>23.32</v>
+        <v>26.71</v>
       </c>
       <c r="K44" t="n">
-        <v>-53.3</v>
+        <v>-61.07</v>
       </c>
       <c r="L44" t="n">
-        <v>58.18</v>
+        <v>66.65000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>73.17</v>
+        <v>76.02</v>
       </c>
       <c r="K45" t="n">
-        <v>47.58</v>
+        <v>49.44</v>
       </c>
       <c r="L45" t="n">
-        <v>87.28</v>
+        <v>90.68000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -2026,13 +2026,13 @@
         <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>46.56</v>
+        <v>47.92</v>
       </c>
       <c r="K47" t="n">
-        <v>-66.63</v>
+        <v>-68.56999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>81.28</v>
+        <v>83.65000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-75.62</v>
+        <v>-78.45</v>
       </c>
       <c r="K48" t="n">
-        <v>-10.56</v>
+        <v>-10.96</v>
       </c>
       <c r="L48" t="n">
-        <v>76.36</v>
+        <v>79.22</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-68.16</v>
+        <v>-68.95</v>
       </c>
       <c r="K49" t="n">
-        <v>13.8</v>
+        <v>13.96</v>
       </c>
       <c r="L49" t="n">
-        <v>69.54000000000001</v>
+        <v>70.34</v>
       </c>
     </row>
     <row r="50">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-41.17</v>
+        <v>-43.82</v>
       </c>
       <c r="K60" t="n">
-        <v>-65.87</v>
+        <v>-70.11</v>
       </c>
       <c r="L60" t="n">
-        <v>77.67</v>
+        <v>82.68000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>78.95</v>
+        <v>90.56</v>
       </c>
       <c r="K62" t="n">
-        <v>8.050000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="L62" t="n">
-        <v>79.36</v>
+        <v>91.03</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-83.81</v>
+        <v>-89.7</v>
       </c>
       <c r="K63" t="n">
-        <v>-13.14</v>
+        <v>-14.06</v>
       </c>
       <c r="L63" t="n">
-        <v>84.84</v>
+        <v>90.79000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>73.66</v>
+        <v>77.37</v>
       </c>
       <c r="K64" t="n">
-        <v>20.54</v>
+        <v>21.58</v>
       </c>
       <c r="L64" t="n">
-        <v>76.47</v>
+        <v>80.33</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>-61.66</v>
+        <v>-62.86</v>
       </c>
       <c r="K74" t="n">
-        <v>-38.1</v>
+        <v>-38.84</v>
       </c>
       <c r="L74" t="n">
-        <v>72.48999999999999</v>
+        <v>73.89</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>28.67</v>
+        <v>33.73</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.97</v>
+        <v>-4.67</v>
       </c>
       <c r="L75" t="n">
-        <v>28.94</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>31.81</v>
+        <v>37.81</v>
       </c>
       <c r="K76" t="n">
-        <v>-30.54</v>
+        <v>-36.3</v>
       </c>
       <c r="L76" t="n">
-        <v>44.1</v>
+        <v>52.42</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>65.72</v>
+        <v>74.8</v>
       </c>
       <c r="K77" t="n">
-        <v>23.63</v>
+        <v>26.89</v>
       </c>
       <c r="L77" t="n">
-        <v>69.84</v>
+        <v>79.48999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-27.13</v>
+        <v>-30.5</v>
       </c>
       <c r="K78" t="n">
-        <v>86.66</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>90.8</v>
+        <v>102.1</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>35.01</v>
+        <v>38.59</v>
       </c>
       <c r="K79" t="n">
-        <v>-49.78</v>
+        <v>-54.88</v>
       </c>
       <c r="L79" t="n">
-        <v>60.86</v>
+        <v>67.09</v>
       </c>
     </row>
     <row r="80">
